--- a/reports/analysis/2026-10/2026-10_아넬라로지_성과_및_11-12월_목표.xlsx
+++ b/reports/analysis/2026-10/2026-10_아넬라로지_성과_및_11-12월_목표.xlsx
@@ -17096,7 +17096,7 @@
       </c>
       <c r="H8" s="30" t="inlineStr">
         <is>
-          <t>쇼핑검색은 시간대 입찰 제한(10/14)이 효과였는지 상시 구간 데이터로 검증 후 원복 여부 결정.</t>
+          <t>쇼핑검색은 넾다세일(10/26)부터 24시간 균등 노출로 원복했습니다. 11/8 이후 시간대별 성과와 10/14~25 제한 구간을 비교해 효과를 판단.</t>
         </is>
       </c>
     </row>
@@ -17335,7 +17335,7 @@
       </c>
       <c r="H14" s="30" t="inlineStr">
         <is>
-          <t>쇼핑검색 24시간 균등노출 원복 검토, 파워링크 무전환 지면 제외 후 효율 확인.</t>
+          <t>쇼핑검색은 24시간 균등노출로 원복 완료(10/26~). 파워링크는 시간 제한 유지, 무전환 지면 제외 후 효율 확인.</t>
         </is>
       </c>
     </row>
@@ -17730,7 +17730,7 @@
     <row r="2">
       <c r="A2" s="29" t="inlineStr">
         <is>
-          <t>파워링크·쇼핑검색을 시간대를 지정해 노출한 결과입니다. 수치는 데이터_광고 시트의 SUMIFS 수식이며 대행사 보고 수치와 일치합니다.</t>
+          <t>파워링크·쇼핑검색을 시간대를 지정해 노출한 결과입니다(노출 제외 0~3시, 17~24시, 두 매체 동일, 10/14 시작). 쇼핑검색은 10/26 넾다세일부터 24시간 균등 노출로 원복했습니다. 수치는 데이터_광고 시트의 SUMIFS 수식이며 대행사 보고 수치와 일치합니다.</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18121,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>참고: 넾다세일 시작 후 3일 (10/26~10/28) 아넬라 쇼핑검색 ROAS</t>
+          <t>참고: 24시간 원복 후 3일 (10/26~10/28, 넾다세일 겹침) 아넬라 쇼핑검색 ROAS</t>
         </is>
       </c>
       <c r="B27" s="45" t="n"/>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="G27" s="29" t="inlineStr">
         <is>
-          <t>행사 영향이 포함된 값이라 시간 제한 효과와 직접 비교하기는 어렵습니다.</t>
+          <t>원복과 넾다세일이 같은 날 시작돼 원복 효과만 따로 볼 수 없습니다. 11/8 이후 상시 구간과 비교가 필요합니다.</t>
         </is>
       </c>
     </row>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="B32" s="30" t="inlineStr">
         <is>
-          <t>넾다세일 기간(~11/8) 24시간 균등 노출로 원복 제안. 이후 시간대별 성과를 함께 확인.</t>
+          <t>넾다세일부터(10/26) 24시간 균등 노출로 원복 완료. 이후 시간대별 성과를 함께 확인.</t>
         </is>
       </c>
       <c r="C32" s="46" t="n"/>
@@ -18198,14 +18198,14 @@
       <c r="E32" s="45" t="n"/>
       <c r="G32" s="33" t="inlineStr">
         <is>
-          <t>유입 규모(광고비·클릭 약 +1%)는 유지됐지만 전환율, 매출(-24%), ROAS(490%→368%)가 하락. 노출 제외 시간에도 구매가 발생. 넾다세일로 검색·구매 수요가 커질 가능성이 있어 낮 시간대까지 확보. 시간대별 입찰 비중 조정 기능은 확인되지 않음. 확인할 점: 시간대별 구매 수치는 대행사 보고 기준이며 이 워크북에는 시간대 데이터가 없습니다.</t>
+          <t>유입 규모(광고비·클릭 약 +1%)는 유지됐지만 전환율, 매출(-24%), ROAS(490%→368%)가 하락. 노출 제외 시간에도 구매가 발생. 넾다세일로 검색·구매 수요가 커질 가능성이 있어 낮 시간대까지 확보. 시간대별 입찰 비중 조정 기능은 확인되지 않음. 확인할 점: 시간대별 구매 수치는 대행사 보고 기준이며 이 워크북에는 시간대 데이터가 없습니다. 10/26 이후는 원복과 넾다세일이 겹쳐 원복 효과만 따로 보기 어렵습니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="29" t="inlineStr">
         <is>
-          <t>출처: 노출 시간 제한 결과 정리는 대행사 코멘트(사용자 전달, 2026-10-29). 시간 설정은 10/14 시작. 노출 제외 시간대는 4주차 주간 리포트 기준 0~3시, 17~24시이며 매체별 상세 설정은 확인 필요.</t>
+          <t>출처: 노출 시간 제한 결과 정리는 대행사 코멘트(사용자 전달, 2026-10-29). 시간 설정은 10/14 시작. 노출 제외 시간대는 0~3시, 17~24시로 파워링크·쇼핑검색 동일(사용자 확인).</t>
         </is>
       </c>
     </row>
@@ -21716,7 +21716,7 @@
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
-          <t>쇼핑검색을 24시간 균등 노출로 원복하고, 이후 시간대별 성과를 함께 확인. 과자(떡뻥) 캠페인은 롱테일 검색어 중심으로 정리.</t>
+          <t>넾다세일(10/26)부터 24시간 균등 노출로 원복 완료. 이후 시간대별 성과를 함께 확인. 과자(떡뻥) 캠페인은 롱테일 검색어 중심으로 정리.</t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
@@ -21731,7 +21731,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>원복 완료</t>
         </is>
       </c>
     </row>

--- a/reports/analysis/2026-10/2026-10_아넬라로지_성과_및_11-12월_목표.xlsx
+++ b/reports/analysis/2026-10/2026-10_아넬라로지_성과_및_11-12월_목표.xlsx
@@ -837,19 +837,19 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4">
-        <f>"· 아넬라: 28일 ROAS "&amp;TEXT('10월_실적'!G31,"#,##0%")&amp;"로 KPI 하한("&amp;TEXT('10월_실적'!C31,"0%")&amp;")의 "&amp;TEXT('10월_실적'!H31,"0%")&amp;". 월말 예상 ROAS "&amp;TEXT('10월_실적'!D38,"#,##0%")&amp;"이나 예산은 일할 대비 "&amp;TEXT('10월_실적'!E13,"0%")&amp;"만 사용했습니다."</f>
+        <f>"· 아넬라: 28일 ROAS "&amp;TEXT('10월_실적'!G31,"#,##0%")&amp;"로 KPI 하한("&amp;TEXT('10월_실적'!C31,"0%")&amp;")의 "&amp;TEXT('10월_실적'!H31,"0%")&amp;". 월말 예상 ROAS "&amp;TEXT('10월_실적'!D38,"#,##0%")&amp;"이나 예산은 일할 대비 "&amp;TEXT('10월_실적'!E13,"0%")&amp;"만 사용."</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4">
-        <f>"· 로지오가닉: 28일 ROAS "&amp;TEXT('10월_실적'!G32,"#,##0%")&amp;"로 하한("&amp;TEXT('10월_실적'!C32,"0%")&amp;")의 "&amp;TEXT('10월_실적'!H32,"0%")&amp;". 메타 스스 이상치 이틀을 빼도 "&amp;TEXT('10월_실적'!D46,"#,##0%")&amp;"로 하한을 넘습니다."</f>
+        <f>"· 로지오가닉: 28일 ROAS "&amp;TEXT('10월_실적'!G32,"#,##0%")&amp;"로 하한("&amp;TEXT('10월_실적'!C32,"0%")&amp;")의 "&amp;TEXT('10월_실적'!H32,"0%")&amp;". 메타 스스 이상치 이틀을 빼도 "&amp;TEXT('10월_실적'!D46,"#,##0%")&amp;"로 하한 상회."</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4">
-        <f>"· 아넬라는 행사 구간 ROAS("&amp;TEXT('주차별_추이'!I11,"#,##0%")&amp;")가 상시 구간("&amp;TEXT('주차별_추이'!H11,"#,##0%")&amp;")의 "&amp;TEXT('주차별_추이'!I11/'주차별_추이'!H11,"0.0")&amp;"배라, 11월 목표는 행사 일정에 좌우됩니다. 하한 달성에 필요한 행사일수는 약 "&amp;TEXT('목표_11-12월'!O30,"0.0")&amp;"일(11월)입니다."</f>
+        <f>"· 아넬라는 행사 구간 ROAS("&amp;TEXT('주차별_추이'!I11,"#,##0%")&amp;")가 상시 구간("&amp;TEXT('주차별_추이'!H11,"#,##0%")&amp;")의 "&amp;TEXT('주차별_추이'!I11/'주차별_추이'!H11,"0.0")&amp;"배로, 11월 목표는 행사 일정에 좌우. 하한 달성 필요 행사일수는 약 "&amp;TEXT('목표_11-12월'!O30,"0.0")&amp;"일(11월)."</f>
         <v/>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>10월 목표가 따로 없어 4분기 KPI 보고안의 ROAS 하한(아넬라 850%, 로지 420%)과 10월 광고예산을 소급 적용했습니다. 스토어 일반 순매출은 공동구매 상품을 제외한 값입니다.</t>
+          <t>10월 목표 부재로 4분기 KPI 보고안의 ROAS 하한(아넬라 850%, 로지 420%)과 10월 광고예산을 소급 적용. 스토어 일반 순매출은 공동구매 상품 제외 값.</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>브랜드검색 ROAS는 월 정액 대비 값입니다. GFA 전환 로지오가닉은 10/26부터 집행했습니다.</t>
+          <t>브랜드검색 ROAS는 월 정액 대비 값. GFA 전환 로지오가닉은 10/26부터 집행.</t>
         </is>
       </c>
     </row>
@@ -1373,31 +1373,31 @@
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="17">
-        <f>"· 아넬라 파워링크 노출 시간 제한(10/14~): 행사가 없는 두 주를 비교하면 광고비 "&amp;TEXT('시간제한_검증'!E7,"+0%;-0%")&amp;"인데 구매는 "&amp;'시간제한_검증'!B10&amp;"건에서 "&amp;'시간제한_검증'!C10&amp;"건으로 유지되고 ROAS는 "&amp;TEXT('시간제한_검증'!B13,"#,##0%")&amp;"에서 "&amp;TEXT('시간제한_검증'!C13,"#,##0%")&amp;"로 올랐습니다."</f>
+        <f>"· 아넬라 파워링크 노출 시간 제한(10/14~): 행사 없는 두 주 비교 시 광고비 "&amp;TEXT('시간제한_검증'!E7,"+0%;-0%")&amp;"에도 구매 "&amp;'시간제한_검증'!B10&amp;"건에서 "&amp;'시간제한_검증'!C10&amp;"건으로 유지, ROAS "&amp;TEXT('시간제한_검증'!B13,"#,##0%")&amp;"에서 "&amp;TEXT('시간제한_검증'!C13,"#,##0%")&amp;"로 상승."</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="17">
-        <f>"· 아넬라 저효율 키워드·지면 정리와 시간 제한으로 일할 예산의 "&amp;TEXT('10월_실적'!E13,"0%")&amp;"만 집행하고도 ROAS가 하한에 근접("&amp;TEXT('10월_실적'!H31,"0%")&amp;")했습니다. 상시 구간에서는 쇼핑검색(ROAS "&amp;TEXT('주차별_추이'!H49,"#,##0%")&amp;")이 파워링크("&amp;TEXT('주차별_추이'!H48,"#,##0%")&amp;")보다 효율이 높았습니다."</f>
+        <f>"· 아넬라 저효율 키워드·지면 정리와 시간 제한으로 일할 예산의 "&amp;TEXT('10월_실적'!E13,"0%")&amp;"만 집행하고도 ROAS가 하한에 근접("&amp;TEXT('10월_실적'!H31,"0%")&amp;"). 상시 구간에서는 쇼핑검색(ROAS "&amp;TEXT('주차별_추이'!H49,"#,##0%")&amp;")이 파워링크("&amp;TEXT('주차별_추이'!H48,"#,##0%")&amp;")보다 효율 높음."</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="17">
-        <f>"· 메타 시크릿링크가 자사몰 매출의 주축입니다. 시크릿특가 상품이 자사몰 매출의 아넬라 "&amp;TEXT('자사몰_매출'!H7,"0%")&amp;", 로지 "&amp;TEXT('자사몰_매출'!H8,"0%")&amp;"를 차지하고, 시크릿특가 매출 기준 ROAS는 아넬라 "&amp;TEXT('자사몰_매출'!G15,"#,##0%")&amp;", 로지 "&amp;TEXT('자사몰_매출'!G16,"#,##0%")&amp;"입니다."</f>
+        <f>"· 메타 시크릿링크가 자사몰 매출의 주축. 시크릿특가 상품이 자사몰 매출의 아넬라 "&amp;TEXT('자사몰_매출'!H7,"0%")&amp;", 로지 "&amp;TEXT('자사몰_매출'!H8,"0%")&amp;"를 차지, 시크릿특가 매출 기준 ROAS는 아넬라 "&amp;TEXT('자사몰_매출'!G15,"#,##0%")&amp;", 로지 "&amp;TEXT('자사몰_매출'!G16,"#,##0%")&amp;"."</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="17">
-        <f>"· 로지오가닉은 행사 영향이 작은 가운데 하한을 상회(ROAS "&amp;TEXT('10월_실적'!G32,"#,##0%")&amp;", 이상치 제외 "&amp;TEXT('10월_실적'!D46,"#,##0%")&amp;")했고, 메타 자사몰 과자 시크릿링크가 10월 내내 안정적("&amp;TEXT('10월_실적'!M24,"#,##0%")&amp;")이었습니다."</f>
+        <f>"· 로지오가닉은 행사 영향이 작은 가운데 하한 상회(ROAS "&amp;TEXT('10월_실적'!G32,"#,##0%")&amp;", 이상치 제외 "&amp;TEXT('10월_실적'!D46,"#,##0%")&amp;"), 메타 자사몰 과자 시크릿링크는 10월 내내 안정적("&amp;TEXT('10월_실적'!M24,"#,##0%")&amp;")."</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="18">
-        <f>"· 아넬라 상시 구간 ROAS "&amp;TEXT('주차별_추이'!H11,"#,##0%")&amp;"로 하한("&amp;TEXT('10월_실적'!C31,"0%")&amp;")의 절반 수준. 4주차(10/19~25)는 전 매체 ROAS가 하락했습니다. 보완: 상시 소재 교체, 시간대 입찰 원복 검토, 저효율 정리 효과 검증."</f>
+        <f>"· 아넬라 상시 구간 ROAS "&amp;TEXT('주차별_추이'!H11,"#,##0%")&amp;"로 하한("&amp;TEXT('10월_실적'!C31,"0%")&amp;")의 절반 수준. 4주차(10/19~25) 전 매체 ROAS 하락. 보완: 상시 소재 교체, 쇼핑검색 24시간 원복 후 성과 확인, 저효율 정리 효과 검증."</f>
         <v/>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="18">
-        <f>"· 로지오가닉 메타 스스 10/24~25 전환값이 같은 이틀 스토어 결제의 "&amp;TEXT('점검'!D15,"0.0")&amp;"배. 집계 이슈 가능성이 있어 확인 전까지 목표 산정에서 제외했습니다."</f>
+        <f>"· 로지오가닉 메타 스스 10/24~25 전환값이 같은 이틀 스토어 결제의 "&amp;TEXT('점검'!D15,"0.0")&amp;"배. 집계 이슈 가능성으로 확인 전까지 목표 산정에서 제외."</f>
         <v/>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="2">
-        <f>"가정: 11월 행사일수 "&amp;'목표_11-12월'!B6&amp;"/"&amp;'목표_11-12월'!C6&amp;"/"&amp;'목표_11-12월'!D6&amp;"일(보수/기준/도전), 12월 "&amp;'목표_11-12월'!B7&amp;"/"&amp;'목표_11-12월'!C7&amp;"/"&amp;'목표_11-12월'!D7&amp;"일. 11월 확정은 넾다세일 8일뿐이고 나머지는 영업팀 일정에 따라 수정합니다."</f>
+        <f>"가정: 11월 행사일수 "&amp;'목표_11-12월'!B6&amp;"/"&amp;'목표_11-12월'!C6&amp;"/"&amp;'목표_11-12월'!D6&amp;"일(보수/기준/도전), 12월 "&amp;'목표_11-12월'!B7&amp;"/"&amp;'목표_11-12월'!C7&amp;"/"&amp;'목표_11-12월'!D7&amp;"일. 11월 확정 일정은 넾다세일 8일뿐, 나머지는 영업팀 일정에 따라 수정."</f>
         <v/>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="2">
-        <f>"목표 매출은 예산 100% 사용 가정입니다(10월 소진율: 아넬라 "&amp;TEXT('10월_실적'!E13,"0%")&amp;", 로지 "&amp;TEXT('10월_실적'!E25,"0%")&amp;"). 아넬라는 기준 시나리오에서도 하한에 못 미치므로, 하한을 유지하려면 행사일 확보가, 행사가 부족하면 하한 조정 논의가 필요합니다."</f>
+        <f>"목표 매출은 예산 100% 사용 가정(10월 소진율: 아넬라 "&amp;TEXT('10월_실적'!E13,"0%")&amp;", 로지 "&amp;TEXT('10월_실적'!E25,"0%")&amp;"). 아넬라는 기준 시나리오에서도 하한 미달로, 하한 유지 시 행사일 확보 필요. 행사 부족 시 하한 조정 논의 필요."</f>
         <v/>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>· 블랙프라이데이·12월 행사 일정 (영업팀). 확정되면 목표 시트의 행사일수만 바꾸면 목표가 다시 계산됩니다.</t>
+          <t>· 블랙프라이데이·12월 행사 일정 (영업팀). 확정 시 목표 시트의 행사일수만 수정하면 목표 자동 재계산.</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>· 10/29~10/31 확정 실적. 확정되면 월말 예상을 실적으로 교체합니다.</t>
+          <t>· 10/29~10/31 확정 실적. 확정 시 월말 예상을 실적으로 교체.</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>· 아넬라 GFA 전환의 귀속 지연(노출 0인 날의 전환). 확인 전까지 이 매체의 행사 구간 ROAS는 높게 나올 수 있습니다.</t>
+          <t>· 아넬라 GFA 전환의 귀속 지연(노출 0인 날의 전환). 확인 전까지 해당 매체 행사 구간 ROAS는 높게 나올 가능성.</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="21" t="inlineStr">
         <is>
-          <t>자사몰 매출은 파일의 판매합계 기준(만원)입니다. 파일에 기간이 없어 10월 전체로 보았고, 10/28까지인지 확인이 필요합니다. 아넬라·로지 전품목 맛보기팩(공통)은 브랜드별 합계에서 제외했습니다.</t>
+          <t>자사몰 매출은 파일의 판매합계 기준(만원). 파일에 기간 표기가 없어 10월 전체로 간주, 10/28까지 여부 확인 필요. 아넬라·로지 전품목 맛보기팩(공통)은 브랜드별 합계에서 제외.</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>근거 열은 10월 데이터 또는 사용자 전달 사항입니다. 상태가 "제안"인 항목은 담당·일정 확인이 필요합니다.</t>
+          <t>근거 열은 10월 데이터 또는 사용자 전달 사항. 상태가 "제안"인 항목은 담당·일정 확인 필요.</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>파란 글씨·노란 칸 = 입력값(수정 가능), 검정 = 수식. 다른 시트의 계산은 모두 이 시트와 데이터 시트를 참조합니다.</t>
+          <t>파란 글씨·노란 칸 = 입력값(수정 가능), 검정 = 수식. 다른 시트의 계산은 모두 이 시트와 데이터 시트 참조.</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>팀장 확인이 필요한 데이터 이슈와, 목표 산정에 쓰는 보정값입니다.</t>
+          <t>팀장 확인 필요 데이터 이슈 및 목표 산정용 보정값.</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>해석: 같은 이틀 로지 스토어 전체 결제(공구 포함)보다 메타가 보고한 전환값이 큽니다. 실제 주문이 아닌 전환 집계 이슈(협력광고 연동·중복 집계 등) 가능성이 있어 메타·네이버 협력광고 담당에게 확인이 필요합니다. 11~12월 목표 산정에서는 이 이틀을 제외합니다(목표 시트의 보정 스위치).</t>
+          <t>해석: 같은 이틀 로지 스토어 전체 결제(공구 포함)보다 메타 보고 전환값이 큼. 실제 주문이 아닌 전환 집계 이슈(협력광고 연동·중복 집계 등) 가능성. 메타·네이버 협력광고 담당 확인 필요. 11~12월 목표 산정에서는 이 이틀 제외(목표 시트의 보정 스위치).</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="G21" s="21" t="inlineStr">
         <is>
-          <t>아넬라 스토어에는 공동구매 상품이 없습니다.</t>
+          <t>아넬라 스토어는 공동구매 상품 없음.</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="G22" s="62" t="inlineStr">
         <is>
-          <t>순매출 대비 귀속 매출이 100%에 가까우면 일반상품 매출 대부분이 광고에 귀속된 것이며, 귀속 기준이 달라 100% 초과도 가능합니다.</t>
+          <t>순매출 대비 귀속 매출이 100%에 가까우면 일반상품 매출 대부분이 광고 귀속. 귀속 기준 차이로 100% 초과 가능.</t>
         </is>
       </c>
     </row>
@@ -4071,14 +4071,14 @@
     <row r="34">
       <c r="A34" s="21" t="inlineStr">
         <is>
-          <t>추석세일 종료(9/22) 후에도 10월에 구매가 귀속됨. 월 합계에는 포함했고 일별 ROAS는 쓰지 않았습니다.</t>
+          <t>추석세일 종료(9/22) 후에도 10월에 구매가 귀속됨. 월 합계에는 포함, 일별 ROAS는 미사용.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="21" t="inlineStr">
         <is>
-          <t>노출 0인 날에도 전환이 잡히므로, 행사 구간 아넬라 GFA 전환 ROAS(주차별_추이 시트)는 실제보다 높을 수 있습니다.</t>
+          <t>노출 0인 날에도 전환이 잡히므로, 행사 구간 아넬라 GFA 전환 ROAS(주차별_추이 시트)는 실제보다 높을 가능성.</t>
         </is>
       </c>
     </row>
@@ -4092,28 +4092,28 @@
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>· 광고비는 리포트 원본 값입니다. 네이버 VAT 포함 여부는 기존 주간·월간 리포트와 같은 방식으로 맞췄으며, 예산표(VAT 미포함)와의 정확한 대응은 확인이 필요합니다.</t>
+          <t>· 광고비는 리포트 원본 값. 네이버 VAT 포함 여부는 기존 주간·월간 리포트와 동일 방식으로 처리, 예산표(VAT 미포함)와의 정확한 대응은 확인 필요.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>· 매출은 매체가 보고한 구매(구매완료) 귀속 매출이라 스마트스토어 결제금액과 같지 않습니다.</t>
+          <t>· 매출은 매체가 보고한 구매(구매완료) 귀속 매출이라 스마트스토어 결제금액과 불일치.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>· 아넬라 GFA 상시 소재는 10/26~10/28 노출이 없는 날에도 전환이 잡혀 귀속 지연으로 봅니다(사용자 확인).</t>
+          <t>· 아넬라 GFA 상시 소재는 10/26~10/28 노출이 없는 날에도 전환이 잡혀 귀속 지연으로 판단(사용자 확인).</t>
         </is>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>· 자사몰 매출 파일에는 기간이 없어 10월 전체로 보았습니다. 판매합계가 쿠폰·할인 반영 실결제인지, 10/28까지인지 확인이 필요합니다.</t>
+          <t>· 자사몰 매출 파일에 기간 표기가 없어 10월 전체로 간주. 판매합계의 쿠폰·할인 반영 여부(실결제 기준), 10/28까지 여부 확인 필요.</t>
         </is>
       </c>
     </row>
@@ -16382,7 +16382,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>금액 단위 만원(별도 표기 제외). 10월 목표는 별도로 세워진 것이 없어, 4분기 KPI 보고안의 ROAS 하한과 10월 광고예산을 적용한 소급 기준입니다.</t>
+          <t>금액 단위 만원(별도 표기 제외). 10월 목표는 별도 설정이 없어 4분기 KPI 보고안의 ROAS 하한과 10월 광고예산을 적용한 소급 기준.</t>
         </is>
       </c>
     </row>
@@ -17639,7 +17639,7 @@
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>브랜드검색은 월 정액을 일할 안분한 값이고, 예산표(네이버 VAT 미포함)에는 포함돼 있지 않습니다. 합계 광고비·ROAS는 브랜드검색 정액을 포함한 값으로 주간·월간 리포트와 같은 기준입니다.</t>
+          <t>브랜드검색은 월 정액을 일할 안분한 값이며 예산표(네이버 VAT 미포함)에는 미포함. 합계 광고비·ROAS는 브랜드검색 정액을 포함한 값으로 주간·월간 리포트와 동일 기준.</t>
         </is>
       </c>
     </row>
@@ -17817,7 +17817,7 @@
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>월 광고비 계획 = 10월 예산 합계 + 브랜드검색 정액(31일분). 합계 행의 ROAS 하한은 브랜드별 목표 매출을 계획 광고비로 가중한 값입니다.</t>
+          <t>월 광고비 계획 = 10월 예산 합계 + 브랜드검색 정액(31일분). 합계 행의 ROAS 하한은 브랜드별 목표 매출을 계획 광고비로 가중한 값.</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>월말 예상 광고비·매출 = 28일 누계 + 10/26~28 일평균 × 잔여일수. 10/26~28이 넾다세일 구간이라 상시 구간보다 높게 잡힐 수 있습니다. KPI 목표 주문은 4분기 KPI 보고안의 월 환산값입니다.</t>
+          <t>월말 예상 광고비·매출 = 28일 누계 + 10/26~28 일평균 × 잔여일수. 10/26~28이 넾다세일 구간이라 상시 구간 대비 높게 산출될 가능성. KPI 목표 주문은 4분기 KPI 보고안의 월 환산값.</t>
         </is>
       </c>
     </row>
@@ -18177,7 +18177,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>예산은 가정 시트의 입력값을 참조합니다. 12월은 11월 유지 가정입니다. 10월 집행은 10/1~10/28(28일) 광고비이고, 일할 대비 소진율은 10월 예산을 28/31로 환산한 값 대비입니다.</t>
+          <t>예산은 가정 시트 입력값 참조. 12월은 11월 유지 가정. 10월 집행은 10/1~10/28(28일) 광고비이며, 일할 대비 소진율은 10월 예산을 28/31로 환산한 값 대비.</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       <c r="H13" s="15" t="inlineStr"/>
       <c r="I13" s="39" t="inlineStr">
         <is>
-          <t>예산표에는 포함되지 않는 정액 상품입니다(월 88만원을 일수로 안분).</t>
+          <t>예산표에 미포함된 정액 상품(월 88만원을 일수로 안분).</t>
         </is>
       </c>
     </row>
@@ -18905,7 +18905,7 @@
       <c r="H24" s="15" t="inlineStr"/>
       <c r="I24" s="39" t="inlineStr">
         <is>
-          <t>예산표에는 포함되지 않는 정액 상품입니다(월 88만원을 일수로 안분).</t>
+          <t>예산표에 미포함된 정액 상품(월 88만원을 일수로 안분).</t>
         </is>
       </c>
     </row>
@@ -19085,7 +19085,7 @@
     <row r="33">
       <c r="A33" s="21" t="inlineStr">
         <is>
-          <t>KPI안의 10월 예산(1,300 / 900)은 실행 예산에 브랜드검색 정액을 더한 값과 거의 일치합니다. 아넬라 11~12월은 KPI안보다 낮고, 로지오가닉은 KPI안보다 높게 편성돼 있습니다.</t>
+          <t>KPI안의 10월 예산(1,300 / 900)은 실행 예산에 브랜드검색 정액을 더한 값과 거의 일치. 아넬라 11~12월은 KPI안 대비 낮고, 로지오가닉은 KPI안 대비 높게 편성.</t>
         </is>
       </c>
     </row>
@@ -19099,28 +19099,28 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>· 넾다세일(10/26~11/8, 아넬라·로지 모두)부터 메타는 인스타그램 지면만 고정으로 운영합니다.</t>
+          <t>· 넾다세일(10/26~11/8, 아넬라·로지 모두)부터 메타 인스타그램 지면 고정 운영.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>· 10월 중순부터 효율이 낮은 키워드·지면은 OFF 또는 감액 중입니다.</t>
+          <t>· 10월 중순부터 효율이 낮은 키워드·지면 OFF 또는 감액 중.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>· 넾다세일부터 메타 광고 상품은 상시 상품(아넬라 퓨레 6+6, 로지 쌀과자 8봉)이 아니라 영업팀 주력 상품으로 운영합니다.</t>
+          <t>· 넾다세일부터 메타 광고 상품은 상시 상품(아넬라 퓨레 6+6, 로지 쌀과자 8봉)이 아니라 영업팀 주력 상품으로 운영.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>· 12월 예산은 11월 예산을 유지하는 것으로 보고 있습니다. 블랙프라이데이 등 행사 일정이 정해지면 조정합니다.</t>
+          <t>· 12월 예산은 11월 예산 유지 예정. 블랙프라이데이 등 행사 일정 확정 시 조정.</t>
         </is>
       </c>
     </row>
@@ -19174,7 +19174,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>금액은 만원(네이버 VAT 미포함). 집행·매출은 10/1~10/28(28일) 실적이고, 월말 예상은 28일 누계에 10/26~28 일평균 × 잔여일수를 더한 값입니다. 매출은 매체가 보고한 구매 귀속 매출입니다.</t>
+          <t>금액 단위 만원(네이버 VAT 미포함). 집행·매출은 10/1~10/28(28일) 실적, 월말 예상은 28일 누계에 10/26~28 일평균 × 잔여일수를 더한 값. 매출은 매체 보고 구매 귀속 매출.</t>
         </is>
       </c>
     </row>
@@ -20581,14 +20581,14 @@
     <row r="33">
       <c r="A33" s="21" t="inlineStr">
         <is>
-          <t>브랜드검색은 정액 상품이라 월 예산(88만원×31/30)과 집행이 거의 같고 매출이 커서, 브랜드검색 포함 합계의 ROAS가 높게 나옵니다. 매체별 예산 소진 판단은 예산표 기준(브랜드검색 제외) 합계를 보세요.</t>
+          <t>브랜드검색은 정액 상품이라 월 예산(88만원×31/30)과 집행이 거의 같고 매출이 커서 브랜드검색 포함 합계 ROAS가 높게 산출. 매체별 예산 소진 판단은 예산표 기준(브랜드검색 제외) 합계 기준.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="21" t="inlineStr">
         <is>
-          <t>월말 예상은 넾다세일 구간(10/26~28) 일평균을 3일 더 이은 값입니다. GFA 전환(로지)은 10월 예산이 0이라 소진율이 계산되지 않고, 10/26부터 넾다세일 한정으로 집행됐습니다.</t>
+          <t>월말 예상은 넾다세일 구간(10/26~28) 일평균을 3일 연장한 값. GFA 전환(로지)은 10월 예산이 0이라 소진율 산출 불가, 10/26부터 넾다세일 한정 집행.</t>
         </is>
       </c>
     </row>
@@ -20648,7 +20648,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>금액은 만원. 판매합계는 파일 값 그대로이며, 상품명에 "시크릿 특가"가 붙은 상품은 메타 시크릿링크 광고 유입 상품으로 봅니다. 파일에 기간이 없어 10월로 보았습니다.</t>
+          <t>금액은 만원. 판매합계는 파일 값 그대로이며, 상품명에 "시크릿 특가"가 붙은 상품은 메타 시크릿링크 광고 유입 상품으로 간주. 파일에 기간 표기가 없어 10월로 간주.</t>
         </is>
       </c>
     </row>
@@ -20907,7 +20907,7 @@
     <row r="11">
       <c r="A11" s="21" t="inlineStr">
         <is>
-          <t>브랜드 구분은 상품명에 "아넬라"/"로지오가닉"이 있는지로 나눴습니다. 두 브랜드가 함께 적힌 상품(신규회원 한정 맛보기팩)은 공통으로 따로 뒀습니다.</t>
+          <t>브랜드 구분은 상품명에 "아넬라"/"로지오가닉"이 있는지로 구분. 두 브랜드가 함께 적힌 상품(신규회원 한정 맛보기팩)은 공통으로 분리.</t>
         </is>
       </c>
     </row>
@@ -21059,7 +21059,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="21" t="inlineStr">
         <is>
-          <t>시크릿링크 광고비는 캠페인명에 "시크릿링크"가 들어간 메타 자사몰 캠페인만 합산했습니다(아넬라 웰컴박스 제외). 메타 보고 매출이 실매출보다 큰 것은 귀속 기준 차이(조회 후 전환 등) 또는 환불·할인 반영 차이일 수 있으며, 판매합계가 쿠폰·할인을 반영한 실결제 기준인지는 확인이 필요합니다.</t>
+          <t>시크릿링크 광고비는 캠페인명에 "시크릿링크"가 들어간 메타 자사몰 캠페인만 합산(아넬라 웰컴박스 제외). 메타 보고 매출이 실매출보다 큰 것은 귀속 기준 차이(조회 후 전환 등) 또는 환불·할인 반영 차이로 추정, 판매합계의 쿠폰·할인 반영 여부(실결제 기준) 확인 필요.</t>
         </is>
       </c>
     </row>
@@ -21392,7 +21392,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>모든 값은 데이터 시트의 SUMIFS 수식입니다. 기간 구분은 가정 시트에서 바꿀 수 있습니다. 광고비에는 브랜드검색 정액(일할)이 포함됩니다.</t>
+          <t>모든 값은 데이터 시트 SUMIFS 수식. 기간 구분은 가정 시트에서 변경 가능. 광고비에 브랜드검색 정액(일할) 포함.</t>
         </is>
       </c>
     </row>
@@ -23009,7 +23009,7 @@
     <row r="56">
       <c r="A56" s="21" t="inlineStr">
         <is>
-          <t>광고비가 0이면 "-"로 표시합니다. 브랜드검색은 정액 대비 매출이며, GFA 전환 로지오가닉은 10/26 이후만 집행했습니다.</t>
+          <t>광고비가 0이면 "-"로 표시. 브랜드검색은 정액 대비 매출, GFA 전환 로지오가닉은 10/26 이후만 집행.</t>
         </is>
       </c>
     </row>
@@ -23338,7 +23338,7 @@
     <row r="68">
       <c r="A68" s="21" t="inlineStr">
         <is>
-          <t>광고비가 0이면 "-"로 표시합니다. 브랜드검색은 정액 대비 매출이며, GFA 전환 로지오가닉은 10/26 이후만 집행했습니다.</t>
+          <t>광고비가 0이면 "-"로 표시. 브랜드검색은 정액 대비 매출, GFA 전환 로지오가닉은 10/26 이후만 집행.</t>
         </is>
       </c>
     </row>
@@ -23380,7 +23380,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>값 열은 다른 시트의 수식입니다. "원인"은 주간 리포트와 사용자 설명에서 확인된 운영 이력에 근거하며, 데이터만으로 단정하기 어려운 항목은 "추정"으로 표시했습니다.</t>
+          <t>값 열은 다른 시트 수식. "원인"은 주간 리포트와 사용자 설명에서 확인된 운영 이력에 근거하며, 데이터만으로 단정하기 어려운 항목은 "추정"으로 표시.</t>
         </is>
       </c>
     </row>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="G5" s="32" t="inlineStr">
         <is>
-          <t>노출 제외 시간(0~3시, 17~24시) 설정 후 광고비·클릭이 약 58% 줄었는데 구매는 15건에서 14건으로 거의 유지되고 전환율이 6.1%에서 13.7%로 올랐습니다. 행사가 없는 두 주를 비교한 값이라 행사 영향이 없습니다.</t>
+          <t>노출 제외 시간(0~3시, 17~24시) 설정 후 광고비·클릭 약 58% 감소, 구매는 15건에서 14건으로 거의 유지, 전환율 6.1%에서 13.7%로 상승. 행사 없는 두 주 비교라 행사 영향 없음.</t>
         </is>
       </c>
       <c r="H5" s="32" t="inlineStr">
@@ -23497,7 +23497,7 @@
       </c>
       <c r="G6" s="32" t="inlineStr">
         <is>
-          <t>저효율 키워드·지면 OFF/감액과 노출 시간 제한으로 일할 예산의 약 84%만 집행하고도 ROAS가 하한에 근접했습니다. 이 ROAS에는 행사 구간 영향이 포함돼 있어 마케팅 성과는 상시 구간 지표(미달·보완 항목)로 따로 봅니다.</t>
+          <t>저효율 키워드·지면 OFF/감액과 노출 시간 제한으로 일할 예산의 약 84%만 집행, ROAS는 하한에 근접. 해당 ROAS에 행사 구간 영향이 포함돼 있어 마케팅 성과는 상시 구간 지표(미달·보완 항목)로 별도 판단.</t>
         </is>
       </c>
       <c r="H6" s="32" t="inlineStr">
@@ -23537,7 +23537,7 @@
       </c>
       <c r="G7" s="32" t="inlineStr">
         <is>
-          <t>행사가 없는 구간에서도 쇼핑검색이 광고비 비중이 가장 큰 매체(약 32%)이면서 파워링크보다 효율이 높습니다. 퓨레 캠페인이 매출을 이끌었습니다.</t>
+          <t>행사 없는 구간에서도 쇼핑검색이 광고비 비중 최대 매체(약 32%)이며 파워링크보다 효율 높음. 퓨레 캠페인이 매출 견인.</t>
         </is>
       </c>
       <c r="H7" s="32" t="inlineStr">
@@ -23577,12 +23577,12 @@
       </c>
       <c r="G8" s="32" t="inlineStr">
         <is>
-          <t>자사몰 상품명에 "시크릿 특가"가 붙은 상품이 메타 시크릿링크 광고 유입입니다. 이 상품이 자사몰 매출의 대부분을 차지하고, 시크릿링크 광고가 자사몰 매출을 만드는 핵심 경로입니다.</t>
+          <t>자사몰 상품명에 "시크릿 특가"가 붙은 상품은 메타 시크릿링크 광고 유입 상품. 해당 상품이 자사몰 매출의 대부분을 차지하며 시크릿링크 광고가 자사몰 매출의 핵심 경로.</t>
         </is>
       </c>
       <c r="H8" s="32" t="inlineStr">
         <is>
-          <t>시크릿링크 광고 보고 매출이 실제 시크릿특가 매출보다 큽니다(자사몰_매출 시트). 실매출 기준 ROAS로 판단.</t>
+          <t>시크릿링크 광고 보고 매출이 실제 시크릿특가 매출보다 큼(자사몰_매출 시트). 실매출 기준 ROAS로 판단.</t>
         </is>
       </c>
     </row>
@@ -23617,7 +23617,7 @@
       </c>
       <c r="G9" s="32" t="inlineStr">
         <is>
-          <t>로지 자사몰도 "시크릿 특가" 상품(쌀과자 퍼프 스틱 떡뻥 요거팝)이 매출 1위입니다. 첫구매 전용 상품도 별도 비중이 있습니다(자사몰_매출 시트).</t>
+          <t>로지 자사몰도 "시크릿 특가" 상품(쌀과자 퍼프 스틱 떡뻥 요거팝)이 매출 1위. 첫구매 전용 상품도 별도 비중 존재(자사몰_매출 시트).</t>
         </is>
       </c>
       <c r="H9" s="32" t="inlineStr">
@@ -23657,7 +23657,7 @@
       </c>
       <c r="G10" s="32" t="inlineStr">
         <is>
-          <t>로지는 행사 구간과 상시 구간 ROAS 차이가 작아(주차별_추이 시트: 상시 약 566%, 행사 약 687%) 행사에 덜 의존합니다. 메타 스스(과자 상시)와 메타 자사몰(과자 시크릿링크)이 광고비의 절반 이상을 차지하며 평균을 끌어올렸습니다.</t>
+          <t>로지는 행사·상시 구간 ROAS 차이가 작아(주차별_추이 시트: 상시 약 566%, 행사 약 687%) 행사 의존도 낮음. 메타 스스(과자 상시)와 메타 자사몰(과자 시크릿링크)이 광고비의 절반 이상을 차지하며 평균 ROAS 상승 견인.</t>
         </is>
       </c>
       <c r="H10" s="32" t="inlineStr">
@@ -23697,7 +23697,7 @@
       </c>
       <c r="G11" s="32" t="inlineStr">
         <is>
-          <t>메타 스스 10/24~25를 제외해도 하한을 넘습니다. 즉 성과 달성 판단은 이상치와 무관하게 유지됩니다.</t>
+          <t>메타 스스 10/24~25 제외 시에도 하한 상회. 성과 달성 판단은 이상치와 무관하게 유지.</t>
         </is>
       </c>
       <c r="H11" s="32" t="inlineStr">
@@ -23737,7 +23737,7 @@
       </c>
       <c r="G12" s="32" t="inlineStr">
         <is>
-          <t>10/1~4부터 10/26~28까지 5개 구간 모두 430~750% 범위 유지(주차별 ROAS는 주차별_추이 시트). 시크릿링크 구성이 일관되게 구매를 만들었습니다.</t>
+          <t>10/1~4부터 10/26~28까지 5개 구간 모두 430~750% 범위 유지(주차별 ROAS는 주차별_추이 시트). 시크릿링크 구성이 일관되게 구매 창출.</t>
         </is>
       </c>
       <c r="H12" s="32" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="G13" s="32" t="inlineStr">
         <is>
-          <t>상시 구간 ROAS가 행사 구간의 약 1/3 수준이라, 행사가 없는 주에는 하한을 크게 밑돕니다(주차별_추이 시트).</t>
+          <t>상시 구간 ROAS가 행사 구간의 약 1/3 수준이라 행사 없는 주에는 하한 크게 하회(주차별_추이 시트).</t>
         </is>
       </c>
       <c r="H13" s="32" t="inlineStr">
@@ -23816,7 +23816,7 @@
       </c>
       <c r="G14" s="32" t="inlineStr">
         <is>
-          <t>10/1~4, 10/5~11, 10/19~25의 합산 ROAS. 4주차(10/19~25)는 전 매체 ROAS가 전주 대비 하락했고 전환율이 16.8%에서 7.0%로 내려갔습니다(주간 리포트).</t>
+          <t>10/1~4, 10/5~11, 10/19~25의 합산 ROAS. 4주차(10/19~25)는 전 매체 ROAS 전주 대비 하락, 전환율 16.8%에서 7.0%로 하락(주간 리포트).</t>
         </is>
       </c>
       <c r="H14" s="32" t="inlineStr">
@@ -23855,7 +23855,7 @@
       </c>
       <c r="G15" s="32" t="inlineStr">
         <is>
-          <t>저효율 키워드·지면 OFF/감액, 웰컴박스·기획전 보류로 의도적으로 줄인 영향이 큽니다. GFA는 10/26부터 상시 소재 노출이 거의 없고 넾다세일 소재 중심으로 운영된 것으로 보입니다(추정).</t>
+          <t>저효율 키워드·지면 OFF/감액, 웰컴박스·기획전 보류로 의도적 감액 영향이 큼. GFA는 10/26부터 상시 소재 노출이 거의 없고 넾다세일 소재 중심 운영으로 추정.</t>
         </is>
       </c>
       <c r="H15" s="32" t="inlineStr">
@@ -23895,7 +23895,7 @@
       </c>
       <c r="G16" s="32" t="inlineStr">
         <is>
-          <t>웰컴박스는 신청하기 목적 캠페인이라 구매 ROAS가 거의 나오지 않았고(광고비 약 20만원, 구매 2건), 시크릿링크도 구간이 지날수록 ROAS가 내려왔습니다. 광고 보고 ROAS와 자사몰 실매출 기준 ROAS의 차이는 자사몰_매출 시트 참고.</t>
+          <t>웰컴박스는 신청하기 목적 캠페인이라 구매 ROAS 거의 없음(광고비 약 20만원, 구매 2건), 시크릿링크도 구간 경과에 따라 ROAS 하락. 광고 보고 ROAS와 자사몰 실매출 기준 ROAS 차이는 자사몰_매출 시트 참고.</t>
         </is>
       </c>
       <c r="H16" s="32" t="inlineStr">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="G17" s="32" t="inlineStr">
         <is>
-          <t>월 ROAS는 낮지 않으나 4주차에는 189%까지 떨어졌습니다(주간 리포트). 비교 기준 200%는 주간 리포트의 개선 기준입니다.</t>
+          <t>월 ROAS는 양호하나 4주차 189%까지 하락(주간 리포트). 비교 기준 200%는 주간 리포트의 개선 기준.</t>
         </is>
       </c>
       <c r="H17" s="32" t="inlineStr">
@@ -23974,7 +23974,7 @@
       </c>
       <c r="G18" s="32" t="inlineStr">
         <is>
-          <t>9월 월간 리포트에서도 과자(떡뻥)_일반K 효율이 낮았습니다(ROAS 201%). 대표 단어 경쟁이 강해 증액해도 효율이 희석됩니다.</t>
+          <t>9월 월간 리포트에서도 과자(떡뻥)_일반K 효율 낮음(ROAS 201%). 대표 단어 경쟁이 강해 증액 시 효율 희석.</t>
         </is>
       </c>
       <c r="H18" s="32" t="inlineStr">
@@ -24013,7 +24013,7 @@
       </c>
       <c r="G19" s="32" t="inlineStr">
         <is>
-          <t>3일 집행에서 구매 1건으로 효율이 나오지 않았고, 소재 검토를 위해 HOLD 중입니다.</t>
+          <t>3일 집행에서 구매 1건으로 효율 미확보, 소재 검토를 위해 HOLD 중.</t>
         </is>
       </c>
       <c r="H19" s="32" t="inlineStr">
@@ -24053,7 +24053,7 @@
       </c>
       <c r="G20" s="32" t="inlineStr">
         <is>
-          <t>파워링크 대표K·구매K 그룹의 구매 전환이 줄어든 영향이 큽니다(4주차 주간 리포트). 브랜드검색을 포함하면 검색 전체 ROAS는 올라갑니다.</t>
+          <t>파워링크 대표K·구매K 그룹의 구매 전환 감소 영향이 큼(4주차 주간 리포트). 브랜드검색 포함 시 검색 전체 ROAS 상승.</t>
         </is>
       </c>
       <c r="H20" s="32" t="inlineStr">
@@ -24092,7 +24092,7 @@
       </c>
       <c r="G21" s="32" t="inlineStr">
         <is>
-          <t>3일 집행, 구매 6건으로 표본이 작지만 현재는 광고비를 회수하지 못했습니다.</t>
+          <t>3일 집행, 구매 6건으로 표본은 작으나 현재 광고비 미회수.</t>
         </is>
       </c>
       <c r="H21" s="32" t="inlineStr">
@@ -24131,7 +24131,7 @@
       </c>
       <c r="G22" s="32" t="inlineStr">
         <is>
-          <t>같은 이틀의 로지 스토어 전체 결제(공구 포함)보다 메타 전환값이 큽니다. 실주문이 아닌 집계 이슈 가능성.</t>
+          <t>같은 이틀 로지 스토어 전체 결제(공구 포함)보다 메타 전환값이 큼. 실주문이 아닌 집계 이슈 가능성.</t>
         </is>
       </c>
       <c r="H22" s="32" t="inlineStr">
@@ -24170,7 +24170,7 @@
       </c>
       <c r="G23" s="32" t="inlineStr">
         <is>
-          <t>공동구매 상품(9차 등)을 제외하면 스토어 일반상품 매출은 절반 수준입니다. 광고 귀속 매출은 일반상품 순매출에 가깝습니다.</t>
+          <t>공동구매 상품(9차 등) 제외 시 스토어 일반상품 매출은 절반 수준. 광고 귀속 매출은 일반상품 순매출에 근접.</t>
         </is>
       </c>
       <c r="H23" s="32" t="inlineStr">
@@ -24216,13 +24216,13 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>파워링크·쇼핑검색을 시간대를 지정해 노출한 결과입니다(노출 제외 0~3시, 17~24시, 두 매체 동일, 10/14 시작). 쇼핑검색은 10/26 넾다세일부터 24시간 균등 노출로 원복했습니다. 수치는 데이터_광고 시트의 SUMIFS 수식이며 대행사 보고 수치와 일치합니다.</t>
+          <t>파워링크·쇼핑검색 시간대 지정 노출 결과(노출 제외 0~3시, 17~24시, 두 매체 동일, 10/14 시작). 쇼핑검색은 10/26 넾다세일부터 24시간 균등 노출로 원복. 수치는 데이터_광고 시트 SUMIFS 수식이며 대행사 보고 수치와 일치.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="21">
-        <f>"비교기간 "&amp;TEXT('가정'!B51,"m/d")&amp;"~"&amp;TEXT('가정'!C51,"m/d")&amp;" (10월 2주차, 제한 전) vs 기준기간 "&amp;TEXT('가정'!B53,"m/d")&amp;"~"&amp;TEXT('가정'!C53,"m/d")&amp;" (10월 4주차, 제한 후). 두 기간 모두 상시 구간입니다."</f>
+        <f>"비교기간 "&amp;TEXT('가정'!B51,"m/d")&amp;"~"&amp;TEXT('가정'!C51,"m/d")&amp;" (10월 2주차, 제한 전) vs 기준기간 "&amp;TEXT('가정'!B53,"m/d")&amp;"~"&amp;TEXT('가정'!C53,"m/d")&amp;" (10월 4주차, 제한 후). 두 기간 모두 상시 구간."</f>
         <v/>
       </c>
     </row>
@@ -24617,7 +24617,7 @@
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>원복과 넾다세일이 같은 날 시작돼 원복 효과만 따로 볼 수 없습니다. 11/8 이후 상시 구간과 비교가 필요합니다.</t>
+          <t>원복과 넾다세일이 같은 날 시작되어 원복 효과 분리 불가. 11/8 이후 상시 구간과 비교 필요.</t>
         </is>
       </c>
     </row>
@@ -24664,7 +24664,7 @@
       <c r="E31" s="50" t="n"/>
       <c r="G31" s="39" t="inlineStr">
         <is>
-          <t>광고비·클릭 약 58% 감소, 전환율 상승, ROAS 224%→408%. 매출은 -22%로 유입 감소 폭보다 작아 볼륨은 줄었지만 효율은 개선. 확인할 점: 기준기간에 10/21 저효율 키워드 일예산 감액이 함께 들어 있어 시간 제한만의 효과로 보기는 어렵습니다.</t>
+          <t>광고비·클릭 약 58% 감소, 전환율 상승, ROAS 224%→408%. 매출은 -22%로 유입 감소 폭보다 작아 볼륨은 줄었지만 효율은 개선. 확인 사항: 기준기간에 10/21 저효율 키워드 일예산 감액이 함께 반영되어 시간 제한만의 효과로 보기 어려움.</t>
         </is>
       </c>
     </row>
@@ -24684,7 +24684,7 @@
       <c r="E32" s="50" t="n"/>
       <c r="G32" s="39" t="inlineStr">
         <is>
-          <t>유입 규모(광고비·클릭 약 +1%)는 유지됐지만 전환율, 매출(-24%), ROAS(490%→368%)가 하락. 노출 제외 시간에도 구매가 발생. 넾다세일로 검색·구매 수요가 커질 가능성이 있어 낮 시간대까지 확보. 시간대별 입찰 비중 조정 기능은 확인되지 않음. 확인할 점: 시간대별 구매 수치는 대행사 보고 기준이며 이 워크북에는 시간대 데이터가 없습니다. 10/26 이후는 원복과 넾다세일이 겹쳐 원복 효과만 따로 보기 어렵습니다.</t>
+          <t>유입 규모(광고비·클릭 약 +1%)는 유지됐지만 전환율, 매출(-24%), ROAS(490%→368%)가 하락. 노출 제외 시간에도 구매가 발생. 넾다세일로 검색·구매 수요가 커질 가능성이 있어 낮 시간대까지 확보. 시간대별 입찰 비중 조정 기능은 확인되지 않음. 확인 사항: 시간대별 구매 수치는 대행사 보고 기준이며 이 워크북에는 시간대 데이터 없음. 10/26 이후는 원복과 넾다세일이 겹쳐 원복 효과 분리 불가.</t>
         </is>
       </c>
     </row>
@@ -24748,7 +24748,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10월 실적의 상시 ROAS와 행사 ROAS를 매체별로 구한 뒤, 월별 행사일수에 따라 섞어서 목표 ROAS와 목표 매출을 계산합니다. 노란 칸의 가정을 바꾸면 전체가 다시 계산됩니다.</t>
+          <t>10월 실적의 상시 ROAS·행사 ROAS를 매체별로 산출한 뒤 월별 행사일수에 따라 혼합해 목표 ROAS와 목표 매출 계산. 노란 칸 가정 수정 시 전체 재계산.</t>
         </is>
       </c>
     </row>
@@ -27700,21 +27700,21 @@
     <row r="64">
       <c r="A64" s="21" t="inlineStr">
         <is>
-          <t>통합 ROAS = 스마트스토어 일반상품 순매출 ÷ 스스향 광고비(메타 자사몰 제외). 로지오가닉은 상시 구간에 이상치 이틀이 그대로 포함돼 있어 목표 순매출이 다소 높게 나올 수 있습니다.</t>
+          <t>통합 ROAS = 스마트스토어 일반상품 순매출 ÷ 스스향 광고비(메타 자사몰 제외). 로지오가닉은 상시 구간에 이상치 이틀이 그대로 포함되어 목표 순매출이 다소 높게 산출될 가능성.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="21" t="inlineStr">
         <is>
-          <t>목표 매출·순매출은 예산을 100% 사용한다고 가정한 값입니다. 10월 예산 소진율은 아넬라 약 84%, 로지오가닉 약 80%였습니다(10월_실적 시트).</t>
+          <t>목표 매출·순매출은 예산 100% 사용 가정 값. 10월 예산 소진율은 아넬라 약 84%, 로지오가닉 약 80%(10월_실적 시트).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="21" t="inlineStr">
         <is>
-          <t>아넬라 GFA 전환의 행사 ROAS는 귀속 지연·뷰스루 영향으로 높게 나왔을 가능성이 있어(점검 시트 4번), 이 매체의 목표 매출은 보수적으로 보는 편이 안전합니다.</t>
+          <t>아넬라 GFA 전환의 행사 ROAS는 귀속 지연·뷰스루 영향으로 높게 산출되었을 가능성(점검 시트 4번). 해당 매체 목표 매출은 보수적 접근 권장.</t>
         </is>
       </c>
     </row>

--- a/reports/analysis/2026-10/2026-10_아넬라로지_성과_및_11-12월_목표.xlsx
+++ b/reports/analysis/2026-10/2026-10_아넬라로지_성과_및_11-12월_목표.xlsx
@@ -222,6 +222,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -235,7 +236,6 @@
     <xf numFmtId="169" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -502,7 +502,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Source: 자사몰 10월 매출 CSV(상품 순위별 판매), 사용자 업로드, 2026-10-29. 파일에 기간 표기가 없어 10월 매출로 간주. 브랜드·구분은 상품명 기준 수식(아넬라/로지오가닉 포함 여부, "시크릿 특가"는 메타 시크릿링크 광고 유입 상품이라는 사용자 설명).</t>
+        <t>Source: 자사몰 10월 매출 CSV(상품 순위별 판매), 사용자 업로드, 2026-10-29. 기간 10/1~10/28, 판매합계는 실결제 기준(사용자 확인). 브랜드·구분은 상품명 기준 수식(아넬라/로지오가닉 포함 여부, "시크릿 특가"는 메타 시크릿링크 광고 유입 상품이라는 사용자 설명).</t>
       </text>
     </comment>
   </commentList>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
+    <row r="17" ht="44" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>매체</t>
@@ -1080,30 +1080,50 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>아넬라 광고비</t>
+          <t>아넬라 10월 예산</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
+          <t>아넬라 소진금액</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>아넬라 소진율 (월 예산 대비)</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
           <t>아넬라 매출</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>아넬라 ROAS</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>로지 광고비</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>로지 10월 예산</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>로지 소진금액</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>로지 소진율 (월 예산 대비)</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>로지 매출</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>로지 ROAS</t>
         </is>
@@ -1116,26 +1136,42 @@
         </is>
       </c>
       <c r="B18" s="7">
+        <f>'10월_실적'!B6</f>
+        <v/>
+      </c>
+      <c r="C18" s="7">
         <f>'10월_실적'!D6</f>
         <v/>
       </c>
-      <c r="C18" s="7">
+      <c r="D18" s="16">
+        <f>IF(B18=0,0,C18/B18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="7">
         <f>'10월_실적'!L6</f>
         <v/>
       </c>
-      <c r="D18" s="16">
+      <c r="F18" s="17">
         <f>'10월_실적'!M6</f>
         <v/>
       </c>
-      <c r="E18" s="7">
+      <c r="G18" s="7">
+        <f>'10월_실적'!B18</f>
+        <v/>
+      </c>
+      <c r="H18" s="7">
         <f>'10월_실적'!D18</f>
         <v/>
       </c>
-      <c r="F18" s="7">
+      <c r="I18" s="16">
+        <f>IF(G18=0,0,H18/G18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="7">
         <f>'10월_실적'!L18</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="K18" s="17">
         <f>'10월_실적'!M18</f>
         <v/>
       </c>
@@ -1147,26 +1183,42 @@
         </is>
       </c>
       <c r="B19" s="7">
+        <f>'10월_실적'!B7</f>
+        <v/>
+      </c>
+      <c r="C19" s="7">
         <f>'10월_실적'!D7</f>
         <v/>
       </c>
-      <c r="C19" s="7">
+      <c r="D19" s="16">
+        <f>IF(B19=0,0,C19/B19)</f>
+        <v/>
+      </c>
+      <c r="E19" s="7">
         <f>'10월_실적'!L7</f>
         <v/>
       </c>
-      <c r="D19" s="16">
+      <c r="F19" s="17">
         <f>'10월_실적'!M7</f>
         <v/>
       </c>
-      <c r="E19" s="7">
+      <c r="G19" s="7">
+        <f>'10월_실적'!B19</f>
+        <v/>
+      </c>
+      <c r="H19" s="7">
         <f>'10월_실적'!D19</f>
         <v/>
       </c>
-      <c r="F19" s="7">
+      <c r="I19" s="16">
+        <f>IF(G19=0,0,H19/G19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="7">
         <f>'10월_실적'!L19</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="K19" s="17">
         <f>'10월_실적'!M19</f>
         <v/>
       </c>
@@ -1174,30 +1226,46 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>브랜드검색</t>
+          <t>브랜드검색 (정액)</t>
         </is>
       </c>
       <c r="B20" s="7">
+        <f>'10월_실적'!B8</f>
+        <v/>
+      </c>
+      <c r="C20" s="7">
         <f>'10월_실적'!D8</f>
         <v/>
       </c>
-      <c r="C20" s="7">
+      <c r="D20" s="16">
+        <f>IF(B20=0,0,C20/B20)</f>
+        <v/>
+      </c>
+      <c r="E20" s="7">
         <f>'10월_실적'!L8</f>
         <v/>
       </c>
-      <c r="D20" s="16">
+      <c r="F20" s="17">
         <f>'10월_실적'!M8</f>
         <v/>
       </c>
-      <c r="E20" s="7">
+      <c r="G20" s="7">
+        <f>'10월_실적'!B20</f>
+        <v/>
+      </c>
+      <c r="H20" s="7">
         <f>'10월_실적'!D20</f>
         <v/>
       </c>
-      <c r="F20" s="7">
+      <c r="I20" s="16">
+        <f>IF(G20=0,0,H20/G20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="7">
         <f>'10월_실적'!L20</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="K20" s="17">
         <f>'10월_실적'!M20</f>
         <v/>
       </c>
@@ -1209,26 +1277,42 @@
         </is>
       </c>
       <c r="B21" s="7">
+        <f>'10월_실적'!B9</f>
+        <v/>
+      </c>
+      <c r="C21" s="7">
         <f>'10월_실적'!D9</f>
         <v/>
       </c>
-      <c r="C21" s="7">
+      <c r="D21" s="16">
+        <f>IF(B21=0,0,C21/B21)</f>
+        <v/>
+      </c>
+      <c r="E21" s="7">
         <f>'10월_실적'!L9</f>
         <v/>
       </c>
-      <c r="D21" s="16">
+      <c r="F21" s="17">
         <f>'10월_실적'!M9</f>
         <v/>
       </c>
-      <c r="E21" s="7">
+      <c r="G21" s="7">
+        <f>'10월_실적'!B21</f>
+        <v/>
+      </c>
+      <c r="H21" s="7">
         <f>'10월_실적'!D21</f>
         <v/>
       </c>
-      <c r="F21" s="7">
+      <c r="I21" s="16">
+        <f>IF(G21=0,0,H21/G21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="7">
         <f>'10월_실적'!L21</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="K21" s="17">
         <f>'10월_실적'!M21</f>
         <v/>
       </c>
@@ -1240,26 +1324,42 @@
         </is>
       </c>
       <c r="B22" s="7">
+        <f>'10월_실적'!B10</f>
+        <v/>
+      </c>
+      <c r="C22" s="7">
         <f>'10월_실적'!D10</f>
         <v/>
       </c>
-      <c r="C22" s="7">
+      <c r="D22" s="16">
+        <f>IF(B22=0,0,C22/B22)</f>
+        <v/>
+      </c>
+      <c r="E22" s="7">
         <f>'10월_실적'!L10</f>
         <v/>
       </c>
-      <c r="D22" s="16">
+      <c r="F22" s="17">
         <f>'10월_실적'!M10</f>
         <v/>
       </c>
-      <c r="E22" s="7">
+      <c r="G22" s="7">
+        <f>'10월_실적'!B22</f>
+        <v/>
+      </c>
+      <c r="H22" s="7">
         <f>'10월_실적'!D22</f>
         <v/>
       </c>
-      <c r="F22" s="7">
+      <c r="I22" s="16">
+        <f>IF(G22=0,0,H22/G22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="7">
         <f>'10월_실적'!L22</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="K22" s="17">
         <f>'10월_실적'!M22</f>
         <v/>
       </c>
@@ -1271,26 +1371,42 @@
         </is>
       </c>
       <c r="B23" s="7">
+        <f>'10월_실적'!B11</f>
+        <v/>
+      </c>
+      <c r="C23" s="7">
         <f>'10월_실적'!D11</f>
         <v/>
       </c>
-      <c r="C23" s="7">
+      <c r="D23" s="16">
+        <f>IF(B23=0,0,C23/B23)</f>
+        <v/>
+      </c>
+      <c r="E23" s="7">
         <f>'10월_실적'!L11</f>
         <v/>
       </c>
-      <c r="D23" s="16">
+      <c r="F23" s="17">
         <f>'10월_실적'!M11</f>
         <v/>
       </c>
-      <c r="E23" s="7">
+      <c r="G23" s="7">
+        <f>'10월_실적'!B23</f>
+        <v/>
+      </c>
+      <c r="H23" s="7">
         <f>'10월_실적'!D23</f>
         <v/>
       </c>
-      <c r="F23" s="7">
+      <c r="I23" s="16">
+        <f>IF(G23=0,0,H23/G23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="7">
         <f>'10월_실적'!L23</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="K23" s="17">
         <f>'10월_실적'!M23</f>
         <v/>
       </c>
@@ -1302,26 +1418,42 @@
         </is>
       </c>
       <c r="B24" s="7">
+        <f>'10월_실적'!B12</f>
+        <v/>
+      </c>
+      <c r="C24" s="7">
         <f>'10월_실적'!D12</f>
         <v/>
       </c>
-      <c r="C24" s="7">
+      <c r="D24" s="16">
+        <f>IF(B24=0,0,C24/B24)</f>
+        <v/>
+      </c>
+      <c r="E24" s="7">
         <f>'10월_실적'!L12</f>
         <v/>
       </c>
-      <c r="D24" s="16">
+      <c r="F24" s="17">
         <f>'10월_실적'!M12</f>
         <v/>
       </c>
-      <c r="E24" s="7">
+      <c r="G24" s="7">
+        <f>'10월_실적'!B24</f>
+        <v/>
+      </c>
+      <c r="H24" s="7">
         <f>'10월_실적'!D24</f>
         <v/>
       </c>
-      <c r="F24" s="7">
+      <c r="I24" s="16">
+        <f>IF(G24=0,0,H24/G24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="7">
         <f>'10월_실적'!L24</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="K24" s="17">
         <f>'10월_실적'!M24</f>
         <v/>
       </c>
@@ -1348,20 +1480,35 @@
         <f>SUM(E18:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="12">
-        <f>SUM(F18:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="13">
-        <f>IF(E25=0,0,F25/E25)</f>
+      <c r="F25" s="13">
+        <f>IF(C25=0,0,E25/C25)</f>
+        <v/>
+      </c>
+      <c r="G25" s="12">
+        <f>SUM(G18:G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="12">
+        <f>SUM(H18:H24)</f>
+        <v/>
+      </c>
+      <c r="I25" s="13">
+        <f>IF(G25=0,0,H25/G25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="12">
+        <f>SUM(J18:J24)</f>
+        <v/>
+      </c>
+      <c r="K25" s="13">
+        <f>IF(H25=0,0,J25/H25)</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>브랜드검색 ROAS는 월 정액 대비 값. GFA 전환 로지오가닉은 10/26부터 집행.</t>
-        </is>
+      <c r="A26" s="2">
+        <f>"· 금액 단위 만원. 소진율은 월 예산 대비이며 28/31 일할 기준으로는 아넬라 "&amp;TEXT('10월_실적'!E13,"0%")&amp;", 로지 "&amp;TEXT('10월_실적'!E25,"0%")&amp;". 브랜드검색은 정액이라 예산을 정액(31일분)으로 표시하고 ROAS는 월 정액 대비 값. GFA 전환 로지오가닉은 10월 예산 0, 10/26부터 넾다세일 한정 집행."</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -1372,49 +1519,49 @@
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="17">
+      <c r="A29" s="18">
         <f>"· 아넬라 파워링크 노출 시간 제한(10/14~): 행사 없는 두 주 비교 시 광고비 "&amp;TEXT('시간제한_검증'!E7,"+0%;-0%")&amp;"에도 구매 "&amp;'시간제한_검증'!B10&amp;"건에서 "&amp;'시간제한_검증'!C10&amp;"건으로 유지, ROAS "&amp;TEXT('시간제한_검증'!B13,"#,##0%")&amp;"에서 "&amp;TEXT('시간제한_검증'!C13,"#,##0%")&amp;"로 상승."</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="17">
+      <c r="A30" s="18">
         <f>"· 아넬라 저효율 키워드·지면 정리와 시간 제한으로 일할 예산의 "&amp;TEXT('10월_실적'!E13,"0%")&amp;"만 집행하고도 ROAS가 하한에 근접("&amp;TEXT('10월_실적'!H31,"0%")&amp;"). 상시 구간에서는 쇼핑검색(ROAS "&amp;TEXT('주차별_추이'!H49,"#,##0%")&amp;")이 파워링크("&amp;TEXT('주차별_추이'!H48,"#,##0%")&amp;")보다 효율 높음."</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="17">
+      <c r="A31" s="18">
         <f>"· 메타 시크릿링크가 자사몰 매출의 주축. 시크릿특가 상품이 자사몰 매출의 아넬라 "&amp;TEXT('자사몰_매출'!H7,"0%")&amp;", 로지 "&amp;TEXT('자사몰_매출'!H8,"0%")&amp;"를 차지, 시크릿특가 매출 기준 ROAS는 아넬라 "&amp;TEXT('자사몰_매출'!G15,"#,##0%")&amp;", 로지 "&amp;TEXT('자사몰_매출'!G16,"#,##0%")&amp;"."</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="17">
+      <c r="A32" s="18">
         <f>"· 로지오가닉은 행사 영향이 작은 가운데 하한 상회(ROAS "&amp;TEXT('10월_실적'!G32,"#,##0%")&amp;", 이상치 제외 "&amp;TEXT('10월_실적'!D46,"#,##0%")&amp;"), 메타 자사몰 과자 시크릿링크는 10월 내내 안정적("&amp;TEXT('10월_실적'!M24,"#,##0%")&amp;")."</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="18">
+      <c r="A33" s="19">
         <f>"· 아넬라 상시 구간 ROAS "&amp;TEXT('주차별_추이'!H11,"#,##0%")&amp;"로 하한("&amp;TEXT('10월_실적'!C31,"0%")&amp;")의 절반 수준. 4주차(10/19~25) 전 매체 ROAS 하락. 보완: 상시 소재 교체, 쇼핑검색 24시간 원복 후 성과 확인, 저효율 정리 효과 검증."</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="18">
+      <c r="A34" s="19">
         <f>"· 아넬라 메타 자사몰·카탈로그 효율 하락. 웰컴박스·기획전은 보류 유지, 시크릿링크는 개편 썸네일로 교체, 카탈로그는 주력 상품 중심으로 재구성."</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="18">
+      <c r="A35" s="19">
         <f>"· 로지오가닉 파워링크+쇼핑검색 합산 ROAS "&amp;TEXT('성과분석'!E20,"#,##0%")&amp;"로 하한 미달. 보완: 파워링크 대표K·구매K 점검, 11/8 이후 상시 구간으로 감액 효과 검증."</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="18">
+      <c r="A36" s="19">
         <f>"· 로지오가닉 메타 스스 10/24~25 전환값이 같은 이틀 스토어 결제의 "&amp;TEXT('점검'!D15,"0.0")&amp;"배. 집계 이슈 가능성으로 확인 전까지 목표 산정에서 제외."</f>
         <v/>
       </c>
@@ -1489,7 +1636,7 @@
           <t>아넬라</t>
         </is>
       </c>
-      <c r="B40" s="19" t="inlineStr">
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>11월</t>
         </is>
@@ -1526,7 +1673,7 @@
         <f>'목표_11-12월'!B30</f>
         <v/>
       </c>
-      <c r="K40" s="20">
+      <c r="K40" s="21">
         <f>'목표_11-12월'!O30</f>
         <v/>
       </c>
@@ -1537,7 +1684,7 @@
           <t>아넬라</t>
         </is>
       </c>
-      <c r="B41" s="19" t="inlineStr">
+      <c r="B41" s="20" t="inlineStr">
         <is>
           <t>12월</t>
         </is>
@@ -1574,7 +1721,7 @@
         <f>'목표_11-12월'!B54</f>
         <v/>
       </c>
-      <c r="K41" s="20">
+      <c r="K41" s="21">
         <f>'목표_11-12월'!O54</f>
         <v/>
       </c>
@@ -1585,7 +1732,7 @@
           <t>로지오가닉</t>
         </is>
       </c>
-      <c r="B42" s="19" t="inlineStr">
+      <c r="B42" s="20" t="inlineStr">
         <is>
           <t>11월</t>
         </is>
@@ -1622,7 +1769,7 @@
         <f>'목표_11-12월'!B31</f>
         <v/>
       </c>
-      <c r="K42" s="20">
+      <c r="K42" s="21">
         <f>'목표_11-12월'!O31</f>
         <v/>
       </c>
@@ -1633,7 +1780,7 @@
           <t>로지오가닉</t>
         </is>
       </c>
-      <c r="B43" s="19" t="inlineStr">
+      <c r="B43" s="20" t="inlineStr">
         <is>
           <t>12월</t>
         </is>
@@ -1670,7 +1817,7 @@
         <f>'목표_11-12월'!B55</f>
         <v/>
       </c>
-      <c r="K43" s="20">
+      <c r="K43" s="21">
         <f>'목표_11-12월'!O55</f>
         <v/>
       </c>
@@ -1855,9 +2002,9 @@
       </c>
     </row>
     <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="21" t="inlineStr">
-        <is>
-          <t>자사몰 매출은 파일의 판매합계 기준(만원). 파일에 기간 표기가 없어 10월 전체로 간주, 10/28까지 여부 확인 필요. 아넬라·로지 전품목 맛보기팩(공통)은 브랜드별 합계에서 제외.</t>
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>자사몰 매출은 파일의 판매합계 기준(만원, 실결제 기준), 기간은 10/1~10/28. 아넬라·로지 전품목 맛보기팩(공통)은 브랜드별 합계에서 제외.</t>
         </is>
       </c>
     </row>
@@ -1979,20 +2126,20 @@
       </c>
     </row>
     <row r="5" ht="56" customHeight="1">
-      <c r="A5" s="19" t="n">
+      <c r="A5" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>메타 전체</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>11/1~11/8</t>
         </is>
@@ -2019,20 +2166,20 @@
       </c>
     </row>
     <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="19" t="n">
+      <c r="A6" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>네이버 검색·GFA</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>11/9~</t>
         </is>
@@ -2059,20 +2206,20 @@
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>영업팀 협의</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>11월 1주 내</t>
         </is>
@@ -2099,20 +2246,20 @@
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="19" t="n">
+      <c r="A8" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>메타 파트너십</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>넾다세일 이후</t>
         </is>
@@ -2139,20 +2286,20 @@
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>아넬라</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>네이버 오늘끝딜</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>11월 2주</t>
         </is>
@@ -2179,20 +2326,20 @@
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="19" t="n">
+      <c r="A10" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>아넬라</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>메타 스스</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>차주까지</t>
         </is>
@@ -2219,20 +2366,20 @@
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>아넬라</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>메타 카탈로그</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>11월 1~2주</t>
         </is>
@@ -2259,20 +2406,20 @@
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
-      <c r="A12" s="19" t="n">
+      <c r="A12" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>아넬라</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>메타 자사몰</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>11월 1주</t>
         </is>
@@ -2299,20 +2446,20 @@
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>아넬라</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>GFA 전환</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>소재 검토 후</t>
         </is>
@@ -2339,20 +2486,20 @@
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
-      <c r="A14" s="19" t="n">
+      <c r="A14" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>아넬라</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>쇼핑검색</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>넾다세일 기간(~11/8)</t>
         </is>
@@ -2379,20 +2526,20 @@
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>아넬라</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>파워링크</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>상시</t>
         </is>
@@ -2419,20 +2566,20 @@
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
-      <c r="A16" s="19" t="n">
+      <c r="A16" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>로지오가닉</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>메타 스스</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>차주</t>
         </is>
@@ -2459,20 +2606,20 @@
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="19" t="n">
+      <c r="A17" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>로지오가닉</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>GFA 전환</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>11/1~11/8</t>
         </is>
@@ -2499,20 +2646,20 @@
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
-      <c r="A18" s="19" t="n">
+      <c r="A18" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>로지오가닉</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>메타 자사몰</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>예산 여유 시</t>
         </is>
@@ -2539,20 +2686,20 @@
       </c>
     </row>
     <row r="19" ht="56" customHeight="1">
-      <c r="A19" s="19" t="n">
+      <c r="A19" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>로지오가닉</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>네이버 검색</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>11/9~</t>
         </is>
@@ -2579,20 +2726,20 @@
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
-      <c r="A20" s="19" t="n">
+      <c r="A20" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>12월</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>11월 말</t>
         </is>
@@ -2674,7 +2821,7 @@
       <c r="B5" s="66" t="n">
         <v>46296</v>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>광고 리포트·스마트스토어 파일의 시작일</t>
         </is>
@@ -2689,7 +2836,7 @@
       <c r="B6" s="66" t="n">
         <v>46323</v>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>광고 리포트·스마트스토어 파일의 종료일</t>
         </is>
@@ -2705,7 +2852,7 @@
         <f>B6-B5+1</f>
         <v/>
       </c>
-      <c r="F7" s="21" t="inlineStr"/>
+      <c r="F7" s="22" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
@@ -2716,7 +2863,7 @@
       <c r="B8" s="61" t="n">
         <v>31</v>
       </c>
-      <c r="F8" s="21" t="inlineStr"/>
+      <c r="F8" s="22" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
@@ -2728,7 +2875,7 @@
         <f>B8-B7</f>
         <v/>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>월말 예상치 계산에 사용 (10/29~10/31)</t>
         </is>
@@ -2743,7 +2890,7 @@
       <c r="B10" s="61" t="n">
         <v>30</v>
       </c>
-      <c r="F10" s="21" t="inlineStr"/>
+      <c r="F10" s="22" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
@@ -2754,7 +2901,7 @@
       <c r="B11" s="61" t="n">
         <v>31</v>
       </c>
-      <c r="F11" s="21" t="inlineStr"/>
+      <c r="F11" s="22" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
@@ -2765,7 +2912,7 @@
       <c r="B12" s="43" t="n">
         <v>0.95</v>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>달성률 100% 이상 = 달성, 이 값 이상 = 근접, 미만 = 미달</t>
         </is>
@@ -3194,7 +3341,7 @@
         <f>D32</f>
         <v/>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>출처: 사용자가 전달한 10월·11월 예산 총액. 12월은 11월 유지</t>
         </is>
@@ -3252,7 +3399,7 @@
       <c r="B37" s="61" t="n">
         <v>880000</v>
       </c>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>출처: 9월 월간 리포트 하단 주석 (정액제 2,640,000원/90일을 30일분으로 환산). 주간 리포트의 광고비 집계와 같은 방식</t>
         </is>
@@ -3312,7 +3459,7 @@
       <c r="C42" s="43" t="n">
         <v>4.2</v>
       </c>
-      <c r="F42" s="21" t="inlineStr">
+      <c r="F42" s="22" t="inlineStr">
         <is>
           <t>4분기 KPI 보고안 "ROAS 하한 근거" (8·9월 월간 ROAS가 이 값 이상)</t>
         </is>
@@ -3330,7 +3477,7 @@
       <c r="C43" s="61" t="n">
         <v>1700</v>
       </c>
-      <c r="F43" s="21" t="inlineStr">
+      <c r="F43" s="22" t="inlineStr">
         <is>
           <t>4분기 KPI 보고안 (9월 ROAS 유지 시 월 환산)</t>
         </is>
@@ -3348,7 +3495,7 @@
       <c r="C44" s="61" t="n">
         <v>900</v>
       </c>
-      <c r="F44" s="21" t="inlineStr">
+      <c r="F44" s="22" t="inlineStr">
         <is>
           <t>실행 예산 + 브랜드검색 정액(월 88만원)이 포함된 값</t>
         </is>
@@ -3366,7 +3513,7 @@
       <c r="C45" s="61" t="n">
         <v>800</v>
       </c>
-      <c r="F45" s="21" t="inlineStr"/>
+      <c r="F45" s="22" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
@@ -3380,7 +3527,7 @@
       <c r="C46" s="61" t="n">
         <v>800</v>
       </c>
-      <c r="F46" s="21" t="inlineStr"/>
+      <c r="F46" s="22" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -3827,7 +3974,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>이틀 합계 전환값이 같은 이틀 스토어 결제금액(총)의 몇 배인가</t>
         </is>
@@ -3915,7 +4062,7 @@
         <f>IF(E21+SUMIFS('데이터_SS일별'!$E$2:$E$400,'데이터_SS일별'!$A$2:$A$400,A21,'데이터_SS일별'!$C$2:$C$400,"일반")=0,0,E21/(E21+SUMIFS('데이터_SS일별'!$E$2:$E$400,'데이터_SS일별'!$A$2:$A$400,A21,'데이터_SS일별'!$C$2:$C$400,"일반")))</f>
         <v/>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>아넬라 스토어는 공동구매 상품 없음.</t>
         </is>
@@ -4069,14 +4216,14 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>추석세일 종료(9/22) 후에도 10월에 구매가 귀속됨. 월 합계에는 포함, 일별 ROAS는 미사용.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="21" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>노출 0인 날에도 전환이 잡히므로, 행사 구간 아넬라 GFA 전환 ROAS(주차별_추이 시트)는 실제보다 높을 가능성.</t>
         </is>
@@ -4113,7 +4260,7 @@
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>· 자사몰 매출 파일에 기간 표기가 없어 10월 전체로 간주. 판매합계의 쿠폰·할인 반영 여부(실결제 기준), 10/28까지 여부 확인 필요.</t>
+          <t>· 자사몰 매출 파일의 기간은 10/1~10/28, 판매합계는 실결제 기준(사용자 확인).</t>
         </is>
       </c>
     </row>
@@ -16481,19 +16628,19 @@
           <t>파워링크</t>
         </is>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$4,'가정'!$B$16:$B$27,$A6)</f>
         <v/>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="23">
         <f>B6*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A6)/10000</f>
         <v/>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="16">
         <f>IF(C6=0,0,D6/C6)</f>
         <v/>
       </c>
@@ -16521,7 +16668,7 @@
         <f>IF(G6=0,0,J6/G6)</f>
         <v/>
       </c>
-      <c r="L6" s="22">
+      <c r="L6" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A6)/10000</f>
         <v/>
       </c>
@@ -16548,19 +16695,19 @@
           <t>쇼핑검색</t>
         </is>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$4,'가정'!$B$16:$B$27,$A7)</f>
         <v/>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="23">
         <f>B7*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A7)/10000</f>
         <v/>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="16">
         <f>IF(C7=0,0,D7/C7)</f>
         <v/>
       </c>
@@ -16588,7 +16735,7 @@
         <f>IF(G7=0,0,J7/G7)</f>
         <v/>
       </c>
-      <c r="L7" s="22">
+      <c r="L7" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A7)/10000</f>
         <v/>
       </c>
@@ -16615,19 +16762,19 @@
           <t>브랜드검색</t>
         </is>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="23">
         <f>'가정'!$B$38*'가정'!$B$8/10000</f>
         <v/>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="23">
         <f>B8*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A8)/10000</f>
         <v/>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="16">
         <f>IF(C8=0,0,D8/C8)</f>
         <v/>
       </c>
@@ -16655,7 +16802,7 @@
         <f>IF(G8=0,0,J8/G8)</f>
         <v/>
       </c>
-      <c r="L8" s="22">
+      <c r="L8" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A8)/10000</f>
         <v/>
       </c>
@@ -16682,19 +16829,19 @@
           <t>GFA 카탈로그</t>
         </is>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$4,'가정'!$B$16:$B$27,$A9)</f>
         <v/>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="23">
         <f>B9*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A9)/10000</f>
         <v/>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="16">
         <f>IF(C9=0,0,D9/C9)</f>
         <v/>
       </c>
@@ -16722,7 +16869,7 @@
         <f>IF(G9=0,0,J9/G9)</f>
         <v/>
       </c>
-      <c r="L9" s="22">
+      <c r="L9" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A9)/10000</f>
         <v/>
       </c>
@@ -16749,19 +16896,19 @@
           <t>GFA 전환</t>
         </is>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$4,'가정'!$B$16:$B$27,$A10)</f>
         <v/>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="23">
         <f>B10*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A10)/10000</f>
         <v/>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="16">
         <f>IF(C10=0,0,D10/C10)</f>
         <v/>
       </c>
@@ -16789,7 +16936,7 @@
         <f>IF(G10=0,0,J10/G10)</f>
         <v/>
       </c>
-      <c r="L10" s="22">
+      <c r="L10" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A10)/10000</f>
         <v/>
       </c>
@@ -16816,19 +16963,19 @@
           <t>메타 스스</t>
         </is>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$4,'가정'!$B$16:$B$27,$A11)</f>
         <v/>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="23">
         <f>B11*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A11)/10000</f>
         <v/>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="16">
         <f>IF(C11=0,0,D11/C11)</f>
         <v/>
       </c>
@@ -16856,7 +17003,7 @@
         <f>IF(G11=0,0,J11/G11)</f>
         <v/>
       </c>
-      <c r="L11" s="22">
+      <c r="L11" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A11)/10000</f>
         <v/>
       </c>
@@ -16883,19 +17030,19 @@
           <t>메타 자사몰</t>
         </is>
       </c>
-      <c r="B12" s="22">
+      <c r="B12" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$4,'가정'!$B$16:$B$27,$A12)</f>
         <v/>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="23">
         <f>B12*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A12)/10000</f>
         <v/>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="16">
         <f>IF(C12=0,0,D12/C12)</f>
         <v/>
       </c>
@@ -16923,7 +17070,7 @@
         <f>IF(G12=0,0,J12/G12)</f>
         <v/>
       </c>
-      <c r="L12" s="22">
+      <c r="L12" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A12)/10000</f>
         <v/>
       </c>
@@ -17106,19 +17253,19 @@
           <t>파워링크</t>
         </is>
       </c>
-      <c r="B18" s="22">
+      <c r="B18" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$16,'가정'!$B$16:$B$27,$A18)</f>
         <v/>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="23">
         <f>B18*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$16,'데이터_광고'!$B$2:$B$500,$A18)/10000</f>
         <v/>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="16">
         <f>IF(C18=0,0,D18/C18)</f>
         <v/>
       </c>
@@ -17146,7 +17293,7 @@
         <f>IF(G18=0,0,J18/G18)</f>
         <v/>
       </c>
-      <c r="L18" s="22">
+      <c r="L18" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$16,'데이터_광고'!$B$2:$B$500,$A18)/10000</f>
         <v/>
       </c>
@@ -17173,19 +17320,19 @@
           <t>쇼핑검색</t>
         </is>
       </c>
-      <c r="B19" s="22">
+      <c r="B19" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$16,'가정'!$B$16:$B$27,$A19)</f>
         <v/>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="23">
         <f>B19*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$16,'데이터_광고'!$B$2:$B$500,$A19)/10000</f>
         <v/>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="16">
         <f>IF(C19=0,0,D19/C19)</f>
         <v/>
       </c>
@@ -17213,7 +17360,7 @@
         <f>IF(G19=0,0,J19/G19)</f>
         <v/>
       </c>
-      <c r="L19" s="22">
+      <c r="L19" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$16,'데이터_광고'!$B$2:$B$500,$A19)/10000</f>
         <v/>
       </c>
@@ -17240,19 +17387,19 @@
           <t>브랜드검색</t>
         </is>
       </c>
-      <c r="B20" s="22">
+      <c r="B20" s="23">
         <f>'가정'!$B$38*'가정'!$B$8/10000</f>
         <v/>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="23">
         <f>B20*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$16,'데이터_광고'!$B$2:$B$500,$A20)/10000</f>
         <v/>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="16">
         <f>IF(C20=0,0,D20/C20)</f>
         <v/>
       </c>
@@ -17280,7 +17427,7 @@
         <f>IF(G20=0,0,J20/G20)</f>
         <v/>
       </c>
-      <c r="L20" s="22">
+      <c r="L20" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$16,'데이터_광고'!$B$2:$B$500,$A20)/10000</f>
         <v/>
       </c>
@@ -17307,19 +17454,19 @@
           <t>GFA 카탈로그</t>
         </is>
       </c>
-      <c r="B21" s="22">
+      <c r="B21" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$16,'가정'!$B$16:$B$27,$A21)</f>
         <v/>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="23">
         <f>B21*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$16,'데이터_광고'!$B$2:$B$500,$A21)/10000</f>
         <v/>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="16">
         <f>IF(C21=0,0,D21/C21)</f>
         <v/>
       </c>
@@ -17347,7 +17494,7 @@
         <f>IF(G21=0,0,J21/G21)</f>
         <v/>
       </c>
-      <c r="L21" s="22">
+      <c r="L21" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$16,'데이터_광고'!$B$2:$B$500,$A21)/10000</f>
         <v/>
       </c>
@@ -17374,19 +17521,19 @@
           <t>GFA 전환</t>
         </is>
       </c>
-      <c r="B22" s="22">
+      <c r="B22" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$16,'가정'!$B$16:$B$27,$A22)</f>
         <v/>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="23">
         <f>B22*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$16,'데이터_광고'!$B$2:$B$500,$A22)/10000</f>
         <v/>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="16">
         <f>IF(C22=0,0,D22/C22)</f>
         <v/>
       </c>
@@ -17414,7 +17561,7 @@
         <f>IF(G22=0,0,J22/G22)</f>
         <v/>
       </c>
-      <c r="L22" s="22">
+      <c r="L22" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$16,'데이터_광고'!$B$2:$B$500,$A22)/10000</f>
         <v/>
       </c>
@@ -17441,19 +17588,19 @@
           <t>메타 스스</t>
         </is>
       </c>
-      <c r="B23" s="22">
+      <c r="B23" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$16,'가정'!$B$16:$B$27,$A23)</f>
         <v/>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="23">
         <f>B23*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$16,'데이터_광고'!$B$2:$B$500,$A23)/10000</f>
         <v/>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="16">
         <f>IF(C23=0,0,D23/C23)</f>
         <v/>
       </c>
@@ -17481,7 +17628,7 @@
         <f>IF(G23=0,0,J23/G23)</f>
         <v/>
       </c>
-      <c r="L23" s="22">
+      <c r="L23" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$16,'데이터_광고'!$B$2:$B$500,$A23)/10000</f>
         <v/>
       </c>
@@ -17508,19 +17655,19 @@
           <t>메타 자사몰</t>
         </is>
       </c>
-      <c r="B24" s="22">
+      <c r="B24" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$16,'가정'!$B$16:$B$27,$A24)</f>
         <v/>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="23">
         <f>B24*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$16,'데이터_광고'!$B$2:$B$500,$A24)/10000</f>
         <v/>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="16">
         <f>IF(C24=0,0,D24/C24)</f>
         <v/>
       </c>
@@ -17548,7 +17695,7 @@
         <f>IF(G24=0,0,J24/G24)</f>
         <v/>
       </c>
-      <c r="L24" s="22">
+      <c r="L24" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$16,'데이터_광고'!$B$2:$B$500,$A24)/10000</f>
         <v/>
       </c>
@@ -17703,7 +17850,7 @@
           <t>아넬라</t>
         </is>
       </c>
-      <c r="B31" s="22">
+      <c r="B31" s="23">
         <f>B13</f>
         <v/>
       </c>
@@ -17711,15 +17858,15 @@
         <f>'가정'!B42</f>
         <v/>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="23">
         <f>B31*C31</f>
         <v/>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="23">
         <f>D13</f>
         <v/>
       </c>
-      <c r="F31" s="22">
+      <c r="F31" s="23">
         <f>L13</f>
         <v/>
       </c>
@@ -17742,7 +17889,7 @@
           <t>로지오가닉</t>
         </is>
       </c>
-      <c r="B32" s="22">
+      <c r="B32" s="23">
         <f>B25</f>
         <v/>
       </c>
@@ -17750,15 +17897,15 @@
         <f>'가정'!C42</f>
         <v/>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="23">
         <f>B32*C32</f>
         <v/>
       </c>
-      <c r="E32" s="22">
+      <c r="E32" s="23">
         <f>D25</f>
         <v/>
       </c>
-      <c r="F32" s="22">
+      <c r="F32" s="23">
         <f>L25</f>
         <v/>
       </c>
@@ -17891,11 +18038,11 @@
           <t>아넬라</t>
         </is>
       </c>
-      <c r="B38" s="22">
+      <c r="B38" s="23">
         <f>E31+'주차별_추이'!F15*'가정'!$B$9/10000</f>
         <v/>
       </c>
-      <c r="C38" s="22">
+      <c r="C38" s="23">
         <f>F31+'주차별_추이'!F16*'가정'!$B$9/10000</f>
         <v/>
       </c>
@@ -17938,11 +18085,11 @@
           <t>로지오가닉</t>
         </is>
       </c>
-      <c r="B39" s="22">
+      <c r="B39" s="23">
         <f>E32+'주차별_추이'!F36*'가정'!$B$9/10000</f>
         <v/>
       </c>
-      <c r="C39" s="22">
+      <c r="C39" s="23">
         <f>F32+'주차별_추이'!F37*'가정'!$B$9/10000</f>
         <v/>
       </c>
@@ -18073,11 +18220,11 @@
           <t>원본</t>
         </is>
       </c>
-      <c r="B45" s="22">
+      <c r="B45" s="23">
         <f>E32</f>
         <v/>
       </c>
-      <c r="C45" s="22">
+      <c r="C45" s="23">
         <f>F32</f>
         <v/>
       </c>
@@ -18096,11 +18243,11 @@
           <t>보정 (이상치 이틀 제외)</t>
         </is>
       </c>
-      <c r="B46" s="22">
+      <c r="B46" s="23">
         <f>E32-'점검'!D14/10000</f>
         <v/>
       </c>
-      <c r="C46" s="22">
+      <c r="C46" s="23">
         <f>F32-'점검'!E14/10000</f>
         <v/>
       </c>
@@ -18175,7 +18322,7 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>예산은 가정 시트 입력값 참조. 12월은 11월 유지 가정. 10월 집행은 10/1~10/28(28일) 광고비이며, 일할 대비 소진율은 10월 예산을 28/31로 환산한 값 대비.</t>
         </is>
@@ -18261,11 +18408,11 @@
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A$4,'가정'!$B$16:$B$27,$A6)</f>
         <v/>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="23">
         <f>'10월_실적'!D6</f>
         <v/>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="16">
         <f>IF(B6=0,0,G6/(B6*'가정'!$B$7/'가정'!$B$8))</f>
         <v/>
       </c>
@@ -18301,11 +18448,11 @@
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A$4,'가정'!$B$16:$B$27,$A7)</f>
         <v/>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="23">
         <f>'10월_실적'!D7</f>
         <v/>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="16">
         <f>IF(B7=0,0,G7/(B7*'가정'!$B$7/'가정'!$B$8))</f>
         <v/>
       </c>
@@ -18341,11 +18488,11 @@
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A$4,'가정'!$B$16:$B$27,$A8)</f>
         <v/>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="23">
         <f>'10월_실적'!D9</f>
         <v/>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="16">
         <f>IF(B8=0,0,G8/(B8*'가정'!$B$7/'가정'!$B$8))</f>
         <v/>
       </c>
@@ -18381,11 +18528,11 @@
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A$4,'가정'!$B$16:$B$27,$A9)</f>
         <v/>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="23">
         <f>'10월_실적'!D10</f>
         <v/>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="16">
         <f>IF(B9=0,0,G9/(B9*'가정'!$B$7/'가정'!$B$8))</f>
         <v/>
       </c>
@@ -18421,11 +18568,11 @@
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A$4,'가정'!$B$16:$B$27,$A10)</f>
         <v/>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="23">
         <f>'10월_실적'!D11</f>
         <v/>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="16">
         <f>IF(B10=0,0,G10/(B10*'가정'!$B$7/'가정'!$B$8))</f>
         <v/>
       </c>
@@ -18461,11 +18608,11 @@
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A$4,'가정'!$B$16:$B$27,$A11)</f>
         <v/>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="23">
         <f>'10월_실적'!D12</f>
         <v/>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="16">
         <f>IF(B11=0,0,G11/(B11*'가정'!$B$7/'가정'!$B$8))</f>
         <v/>
       </c>
@@ -18625,11 +18772,11 @@
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A$15,'가정'!$B$16:$B$27,$A17)</f>
         <v/>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="23">
         <f>'10월_실적'!D18</f>
         <v/>
       </c>
-      <c r="H17" s="23">
+      <c r="H17" s="16">
         <f>IF(B17=0,0,G17/(B17*'가정'!$B$7/'가정'!$B$8))</f>
         <v/>
       </c>
@@ -18665,11 +18812,11 @@
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A$15,'가정'!$B$16:$B$27,$A18)</f>
         <v/>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="23">
         <f>'10월_실적'!D19</f>
         <v/>
       </c>
-      <c r="H18" s="23">
+      <c r="H18" s="16">
         <f>IF(B18=0,0,G18/(B18*'가정'!$B$7/'가정'!$B$8))</f>
         <v/>
       </c>
@@ -18705,11 +18852,11 @@
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A$15,'가정'!$B$16:$B$27,$A19)</f>
         <v/>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="23">
         <f>'10월_실적'!D21</f>
         <v/>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="16">
         <f>IF(B19=0,0,G19/(B19*'가정'!$B$7/'가정'!$B$8))</f>
         <v/>
       </c>
@@ -18745,11 +18892,11 @@
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A$15,'가정'!$B$16:$B$27,$A20)</f>
         <v/>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="23">
         <f>'10월_실적'!D22</f>
         <v/>
       </c>
-      <c r="H20" s="23">
+      <c r="H20" s="16">
         <f>IF(B20=0,0,G20/(B20*'가정'!$B$7/'가정'!$B$8))</f>
         <v/>
       </c>
@@ -18785,11 +18932,11 @@
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A$15,'가정'!$B$16:$B$27,$A21)</f>
         <v/>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="23">
         <f>'10월_실적'!D23</f>
         <v/>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="16">
         <f>IF(B21=0,0,G21/(B21*'가정'!$B$7/'가정'!$B$8))</f>
         <v/>
       </c>
@@ -18825,11 +18972,11 @@
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A$15,'가정'!$B$16:$B$27,$A22)</f>
         <v/>
       </c>
-      <c r="G22" s="22">
+      <c r="G22" s="23">
         <f>'10월_실적'!D24</f>
         <v/>
       </c>
-      <c r="H22" s="23">
+      <c r="H22" s="16">
         <f>IF(B22=0,0,G22/(B22*'가정'!$B$7/'가정'!$B$8))</f>
         <v/>
       </c>
@@ -19020,7 +19167,7 @@
         <f>'가정'!B44</f>
         <v/>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="23">
         <f>B12+B13</f>
         <v/>
       </c>
@@ -19033,7 +19180,7 @@
         <f>'가정'!B45</f>
         <v/>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="23">
         <f>C12+C13</f>
         <v/>
       </c>
@@ -19056,7 +19203,7 @@
         <f>'가정'!C44</f>
         <v/>
       </c>
-      <c r="C32" s="22">
+      <c r="C32" s="23">
         <f>B23+B24</f>
         <v/>
       </c>
@@ -19069,7 +19216,7 @@
         <f>'가정'!C45</f>
         <v/>
       </c>
-      <c r="G32" s="22">
+      <c r="G32" s="23">
         <f>C23+C24</f>
         <v/>
       </c>
@@ -19083,7 +19230,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>KPI안의 10월 예산(1,300 / 900)은 실행 예산에 브랜드검색 정액을 더한 값과 거의 일치. 아넬라 11~12월은 KPI안 대비 낮고, 로지오가닉은 KPI안 대비 높게 편성.</t>
         </is>
@@ -19172,7 +19319,7 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>금액 단위 만원(네이버 VAT 미포함). 집행·매출은 10/1~10/28(28일) 실적, 월말 예상은 28일 누계에 10/26~28 일평균 × 잔여일수를 더한 값. 매출은 매체 보고 구매 귀속 매출.</t>
         </is>
@@ -19187,7 +19334,7 @@
       <c r="B3" s="43" t="n">
         <v>1.05</v>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>초과 이상</t>
         </is>
@@ -19195,7 +19342,7 @@
       <c r="D3" s="43" t="n">
         <v>0.8</v>
       </c>
-      <c r="E3" s="21" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>미소진 미만 (월말 예상 소진율 기준)</t>
         </is>
@@ -19291,23 +19438,23 @@
           <t>파워링크</t>
         </is>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$5,'가정'!$B$16:$B$27,$A7)</f>
         <v/>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="23">
         <f>B7*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A7)/10000</f>
         <v/>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="16">
         <f>IF(C7=0,0,D7/C7)</f>
         <v/>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="16">
         <f>IF(B7=0,0,D7/B7)</f>
         <v/>
       </c>
@@ -19315,11 +19462,11 @@
         <f>B7-D7</f>
         <v/>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="23">
         <f>D7+SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A7,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="16">
         <f>IF(B7=0,0,H7/B7)</f>
         <v/>
       </c>
@@ -19327,7 +19474,7 @@
         <f>SUMIFS('데이터_광고'!$H$2:$H$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A7)</f>
         <v/>
       </c>
-      <c r="K7" s="22">
+      <c r="K7" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A7)/10000</f>
         <v/>
       </c>
@@ -19335,7 +19482,7 @@
         <f>IF(D7=0,0,K7/D7)</f>
         <v/>
       </c>
-      <c r="M7" s="22">
+      <c r="M7" s="23">
         <f>K7+SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A7,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
@@ -19354,23 +19501,23 @@
           <t>쇼핑검색</t>
         </is>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$5,'가정'!$B$16:$B$27,$A8)</f>
         <v/>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="23">
         <f>B8*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A8)/10000</f>
         <v/>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="16">
         <f>IF(C8=0,0,D8/C8)</f>
         <v/>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="16">
         <f>IF(B8=0,0,D8/B8)</f>
         <v/>
       </c>
@@ -19378,11 +19525,11 @@
         <f>B8-D8</f>
         <v/>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="23">
         <f>D8+SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A8,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="16">
         <f>IF(B8=0,0,H8/B8)</f>
         <v/>
       </c>
@@ -19390,7 +19537,7 @@
         <f>SUMIFS('데이터_광고'!$H$2:$H$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A8)</f>
         <v/>
       </c>
-      <c r="K8" s="22">
+      <c r="K8" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A8)/10000</f>
         <v/>
       </c>
@@ -19398,7 +19545,7 @@
         <f>IF(D8=0,0,K8/D8)</f>
         <v/>
       </c>
-      <c r="M8" s="22">
+      <c r="M8" s="23">
         <f>K8+SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A8,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
@@ -19417,23 +19564,23 @@
           <t>GFA 카탈로그</t>
         </is>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$5,'가정'!$B$16:$B$27,$A9)</f>
         <v/>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="23">
         <f>B9*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A9)/10000</f>
         <v/>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="16">
         <f>IF(C9=0,0,D9/C9)</f>
         <v/>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="16">
         <f>IF(B9=0,0,D9/B9)</f>
         <v/>
       </c>
@@ -19441,11 +19588,11 @@
         <f>B9-D9</f>
         <v/>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="23">
         <f>D9+SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A9,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="16">
         <f>IF(B9=0,0,H9/B9)</f>
         <v/>
       </c>
@@ -19453,7 +19600,7 @@
         <f>SUMIFS('데이터_광고'!$H$2:$H$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A9)</f>
         <v/>
       </c>
-      <c r="K9" s="22">
+      <c r="K9" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A9)/10000</f>
         <v/>
       </c>
@@ -19461,7 +19608,7 @@
         <f>IF(D9=0,0,K9/D9)</f>
         <v/>
       </c>
-      <c r="M9" s="22">
+      <c r="M9" s="23">
         <f>K9+SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A9,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
@@ -19480,23 +19627,23 @@
           <t>GFA 전환</t>
         </is>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$5,'가정'!$B$16:$B$27,$A10)</f>
         <v/>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="23">
         <f>B10*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A10)/10000</f>
         <v/>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="16">
         <f>IF(C10=0,0,D10/C10)</f>
         <v/>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="16">
         <f>IF(B10=0,0,D10/B10)</f>
         <v/>
       </c>
@@ -19504,11 +19651,11 @@
         <f>B10-D10</f>
         <v/>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="23">
         <f>D10+SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A10,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="16">
         <f>IF(B10=0,0,H10/B10)</f>
         <v/>
       </c>
@@ -19516,7 +19663,7 @@
         <f>SUMIFS('데이터_광고'!$H$2:$H$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A10)</f>
         <v/>
       </c>
-      <c r="K10" s="22">
+      <c r="K10" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A10)/10000</f>
         <v/>
       </c>
@@ -19524,7 +19671,7 @@
         <f>IF(D10=0,0,K10/D10)</f>
         <v/>
       </c>
-      <c r="M10" s="22">
+      <c r="M10" s="23">
         <f>K10+SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A10,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
@@ -19543,23 +19690,23 @@
           <t>메타 스스</t>
         </is>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$5,'가정'!$B$16:$B$27,$A11)</f>
         <v/>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="23">
         <f>B11*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A11)/10000</f>
         <v/>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="16">
         <f>IF(C11=0,0,D11/C11)</f>
         <v/>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="16">
         <f>IF(B11=0,0,D11/B11)</f>
         <v/>
       </c>
@@ -19567,11 +19714,11 @@
         <f>B11-D11</f>
         <v/>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="23">
         <f>D11+SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A11,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="16">
         <f>IF(B11=0,0,H11/B11)</f>
         <v/>
       </c>
@@ -19579,7 +19726,7 @@
         <f>SUMIFS('데이터_광고'!$H$2:$H$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A11)</f>
         <v/>
       </c>
-      <c r="K11" s="22">
+      <c r="K11" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A11)/10000</f>
         <v/>
       </c>
@@ -19587,7 +19734,7 @@
         <f>IF(D11=0,0,K11/D11)</f>
         <v/>
       </c>
-      <c r="M11" s="22">
+      <c r="M11" s="23">
         <f>K11+SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A11,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
@@ -19606,23 +19753,23 @@
           <t>메타 자사몰</t>
         </is>
       </c>
-      <c r="B12" s="22">
+      <c r="B12" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$5,'가정'!$B$16:$B$27,$A12)</f>
         <v/>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="23">
         <f>B12*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A12)/10000</f>
         <v/>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="16">
         <f>IF(C12=0,0,D12/C12)</f>
         <v/>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="16">
         <f>IF(B12=0,0,D12/B12)</f>
         <v/>
       </c>
@@ -19630,11 +19777,11 @@
         <f>B12-D12</f>
         <v/>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="23">
         <f>D12+SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A12,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="16">
         <f>IF(B12=0,0,H12/B12)</f>
         <v/>
       </c>
@@ -19642,7 +19789,7 @@
         <f>SUMIFS('데이터_광고'!$H$2:$H$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A12)</f>
         <v/>
       </c>
-      <c r="K12" s="22">
+      <c r="K12" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A12)/10000</f>
         <v/>
       </c>
@@ -19650,7 +19797,7 @@
         <f>IF(D12=0,0,K12/D12)</f>
         <v/>
       </c>
-      <c r="M12" s="22">
+      <c r="M12" s="23">
         <f>K12+SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,$A12,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
@@ -19669,23 +19816,23 @@
           <t>브랜드검색 (정액, 예산표 외)</t>
         </is>
       </c>
-      <c r="B13" s="22">
+      <c r="B13" s="23">
         <f>'가정'!$B$38*'가정'!$B$8/10000</f>
         <v/>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="23">
         <f>B13*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,"브랜드검색")/10000</f>
         <v/>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="16">
         <f>IF(C13=0,0,D13/C13)</f>
         <v/>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="16">
         <f>IF(B13=0,0,D13/B13)</f>
         <v/>
       </c>
@@ -19693,11 +19840,11 @@
         <f>B13-D13</f>
         <v/>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="23">
         <f>D13+SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,"브랜드검색",'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="16">
         <f>IF(B13=0,0,H13/B13)</f>
         <v/>
       </c>
@@ -19705,7 +19852,7 @@
         <f>SUMIFS('데이터_광고'!$H$2:$H$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,"브랜드검색")</f>
         <v/>
       </c>
-      <c r="K13" s="22">
+      <c r="K13" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,"브랜드검색")/10000</f>
         <v/>
       </c>
@@ -19713,7 +19860,7 @@
         <f>IF(D13=0,0,K13/D13)</f>
         <v/>
       </c>
-      <c r="M13" s="22">
+      <c r="M13" s="23">
         <f>K13+SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$5,'데이터_광고'!$B$2:$B$500,"브랜드검색",'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
@@ -19942,23 +20089,23 @@
           <t>파워링크</t>
         </is>
       </c>
-      <c r="B19" s="22">
+      <c r="B19" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$17,'가정'!$B$16:$B$27,$A19)</f>
         <v/>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="23">
         <f>B19*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A19)/10000</f>
         <v/>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="16">
         <f>IF(C19=0,0,D19/C19)</f>
         <v/>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="16">
         <f>IF(B19=0,0,D19/B19)</f>
         <v/>
       </c>
@@ -19966,11 +20113,11 @@
         <f>B19-D19</f>
         <v/>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="23">
         <f>D19+SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A19,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="16">
         <f>IF(B19=0,0,H19/B19)</f>
         <v/>
       </c>
@@ -19978,7 +20125,7 @@
         <f>SUMIFS('데이터_광고'!$H$2:$H$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A19)</f>
         <v/>
       </c>
-      <c r="K19" s="22">
+      <c r="K19" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A19)/10000</f>
         <v/>
       </c>
@@ -19986,7 +20133,7 @@
         <f>IF(D19=0,0,K19/D19)</f>
         <v/>
       </c>
-      <c r="M19" s="22">
+      <c r="M19" s="23">
         <f>K19+SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A19,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
@@ -20005,23 +20152,23 @@
           <t>쇼핑검색</t>
         </is>
       </c>
-      <c r="B20" s="22">
+      <c r="B20" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$17,'가정'!$B$16:$B$27,$A20)</f>
         <v/>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="23">
         <f>B20*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A20)/10000</f>
         <v/>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="16">
         <f>IF(C20=0,0,D20/C20)</f>
         <v/>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="16">
         <f>IF(B20=0,0,D20/B20)</f>
         <v/>
       </c>
@@ -20029,11 +20176,11 @@
         <f>B20-D20</f>
         <v/>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="23">
         <f>D20+SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A20,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
-      <c r="I20" s="23">
+      <c r="I20" s="16">
         <f>IF(B20=0,0,H20/B20)</f>
         <v/>
       </c>
@@ -20041,7 +20188,7 @@
         <f>SUMIFS('데이터_광고'!$H$2:$H$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A20)</f>
         <v/>
       </c>
-      <c r="K20" s="22">
+      <c r="K20" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A20)/10000</f>
         <v/>
       </c>
@@ -20049,7 +20196,7 @@
         <f>IF(D20=0,0,K20/D20)</f>
         <v/>
       </c>
-      <c r="M20" s="22">
+      <c r="M20" s="23">
         <f>K20+SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A20,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
@@ -20068,23 +20215,23 @@
           <t>GFA 카탈로그</t>
         </is>
       </c>
-      <c r="B21" s="22">
+      <c r="B21" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$17,'가정'!$B$16:$B$27,$A21)</f>
         <v/>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="23">
         <f>B21*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A21)/10000</f>
         <v/>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="16">
         <f>IF(C21=0,0,D21/C21)</f>
         <v/>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="16">
         <f>IF(B21=0,0,D21/B21)</f>
         <v/>
       </c>
@@ -20092,11 +20239,11 @@
         <f>B21-D21</f>
         <v/>
       </c>
-      <c r="H21" s="22">
+      <c r="H21" s="23">
         <f>D21+SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A21,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
-      <c r="I21" s="23">
+      <c r="I21" s="16">
         <f>IF(B21=0,0,H21/B21)</f>
         <v/>
       </c>
@@ -20104,7 +20251,7 @@
         <f>SUMIFS('데이터_광고'!$H$2:$H$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A21)</f>
         <v/>
       </c>
-      <c r="K21" s="22">
+      <c r="K21" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A21)/10000</f>
         <v/>
       </c>
@@ -20112,7 +20259,7 @@
         <f>IF(D21=0,0,K21/D21)</f>
         <v/>
       </c>
-      <c r="M21" s="22">
+      <c r="M21" s="23">
         <f>K21+SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A21,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
@@ -20131,23 +20278,23 @@
           <t>GFA 전환</t>
         </is>
       </c>
-      <c r="B22" s="22">
+      <c r="B22" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$17,'가정'!$B$16:$B$27,$A22)</f>
         <v/>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="23">
         <f>B22*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A22)/10000</f>
         <v/>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="16">
         <f>IF(C22=0,0,D22/C22)</f>
         <v/>
       </c>
-      <c r="F22" s="23">
+      <c r="F22" s="16">
         <f>IF(B22=0,0,D22/B22)</f>
         <v/>
       </c>
@@ -20155,11 +20302,11 @@
         <f>B22-D22</f>
         <v/>
       </c>
-      <c r="H22" s="22">
+      <c r="H22" s="23">
         <f>D22+SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A22,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
-      <c r="I22" s="23">
+      <c r="I22" s="16">
         <f>IF(B22=0,0,H22/B22)</f>
         <v/>
       </c>
@@ -20167,7 +20314,7 @@
         <f>SUMIFS('데이터_광고'!$H$2:$H$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A22)</f>
         <v/>
       </c>
-      <c r="K22" s="22">
+      <c r="K22" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A22)/10000</f>
         <v/>
       </c>
@@ -20175,7 +20322,7 @@
         <f>IF(D22=0,0,K22/D22)</f>
         <v/>
       </c>
-      <c r="M22" s="22">
+      <c r="M22" s="23">
         <f>K22+SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A22,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
@@ -20194,23 +20341,23 @@
           <t>메타 스스</t>
         </is>
       </c>
-      <c r="B23" s="22">
+      <c r="B23" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$17,'가정'!$B$16:$B$27,$A23)</f>
         <v/>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="23">
         <f>B23*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A23)/10000</f>
         <v/>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="16">
         <f>IF(C23=0,0,D23/C23)</f>
         <v/>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="16">
         <f>IF(B23=0,0,D23/B23)</f>
         <v/>
       </c>
@@ -20218,11 +20365,11 @@
         <f>B23-D23</f>
         <v/>
       </c>
-      <c r="H23" s="22">
+      <c r="H23" s="23">
         <f>D23+SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A23,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
-      <c r="I23" s="23">
+      <c r="I23" s="16">
         <f>IF(B23=0,0,H23/B23)</f>
         <v/>
       </c>
@@ -20230,7 +20377,7 @@
         <f>SUMIFS('데이터_광고'!$H$2:$H$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A23)</f>
         <v/>
       </c>
-      <c r="K23" s="22">
+      <c r="K23" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A23)/10000</f>
         <v/>
       </c>
@@ -20238,7 +20385,7 @@
         <f>IF(D23=0,0,K23/D23)</f>
         <v/>
       </c>
-      <c r="M23" s="22">
+      <c r="M23" s="23">
         <f>K23+SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A23,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
@@ -20257,23 +20404,23 @@
           <t>메타 자사몰</t>
         </is>
       </c>
-      <c r="B24" s="22">
+      <c r="B24" s="23">
         <f>SUMIFS('가정'!$C$16:$C$27,'가정'!$A$16:$A$27,$A$17,'가정'!$B$16:$B$27,$A24)</f>
         <v/>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="23">
         <f>B24*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A24)/10000</f>
         <v/>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="16">
         <f>IF(C24=0,0,D24/C24)</f>
         <v/>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="16">
         <f>IF(B24=0,0,D24/B24)</f>
         <v/>
       </c>
@@ -20281,11 +20428,11 @@
         <f>B24-D24</f>
         <v/>
       </c>
-      <c r="H24" s="22">
+      <c r="H24" s="23">
         <f>D24+SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A24,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
-      <c r="I24" s="23">
+      <c r="I24" s="16">
         <f>IF(B24=0,0,H24/B24)</f>
         <v/>
       </c>
@@ -20293,7 +20440,7 @@
         <f>SUMIFS('데이터_광고'!$H$2:$H$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A24)</f>
         <v/>
       </c>
-      <c r="K24" s="22">
+      <c r="K24" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A24)/10000</f>
         <v/>
       </c>
@@ -20301,7 +20448,7 @@
         <f>IF(D24=0,0,K24/D24)</f>
         <v/>
       </c>
-      <c r="M24" s="22">
+      <c r="M24" s="23">
         <f>K24+SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,$A24,'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
@@ -20320,23 +20467,23 @@
           <t>브랜드검색 (정액, 예산표 외)</t>
         </is>
       </c>
-      <c r="B25" s="22">
+      <c r="B25" s="23">
         <f>'가정'!$B$38*'가정'!$B$8/10000</f>
         <v/>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="23">
         <f>B25*'가정'!$B$7/'가정'!$B$8</f>
         <v/>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,"브랜드검색")/10000</f>
         <v/>
       </c>
-      <c r="E25" s="23">
+      <c r="E25" s="16">
         <f>IF(C25=0,0,D25/C25)</f>
         <v/>
       </c>
-      <c r="F25" s="23">
+      <c r="F25" s="16">
         <f>IF(B25=0,0,D25/B25)</f>
         <v/>
       </c>
@@ -20344,11 +20491,11 @@
         <f>B25-D25</f>
         <v/>
       </c>
-      <c r="H25" s="22">
+      <c r="H25" s="23">
         <f>D25+SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,"브랜드검색",'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
-      <c r="I25" s="23">
+      <c r="I25" s="16">
         <f>IF(B25=0,0,H25/B25)</f>
         <v/>
       </c>
@@ -20356,7 +20503,7 @@
         <f>SUMIFS('데이터_광고'!$H$2:$H$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,"브랜드검색")</f>
         <v/>
       </c>
-      <c r="K25" s="22">
+      <c r="K25" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,"브랜드검색")/10000</f>
         <v/>
       </c>
@@ -20364,7 +20511,7 @@
         <f>IF(D25=0,0,K25/D25)</f>
         <v/>
       </c>
-      <c r="M25" s="22">
+      <c r="M25" s="23">
         <f>K25+SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$17,'데이터_광고'!$B$2:$B$500,"브랜드검색",'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/10000/'가정'!$D$54*'가정'!$B$9</f>
         <v/>
       </c>
@@ -20579,14 +20726,14 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>브랜드검색은 정액 상품이라 월 예산(88만원×31/30)과 집행이 거의 같고 매출이 커서 브랜드검색 포함 합계 ROAS가 높게 산출. 매체별 예산 소진 판단은 예산표 기준(브랜드검색 제외) 합계 기준.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>월말 예상은 넾다세일 구간(10/26~28) 일평균을 3일 연장한 값. GFA 전환(로지)은 10월 예산이 0이라 소진율 산출 불가, 10/26부터 넾다세일 한정 집행.</t>
         </is>
@@ -20646,9 +20793,9 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
-        <is>
-          <t>금액은 만원. 판매합계는 파일 값 그대로이며, 상품명에 "시크릿 특가"가 붙은 상품은 메타 시크릿링크 광고 유입 상품으로 간주. 파일에 기간 표기가 없어 10월로 간주.</t>
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>금액은 만원. 판매합계는 파일 값 그대로이며, 상품명에 "시크릿 특가"가 붙은 상품은 메타 시크릿링크 광고 유입 상품으로 간주. 기간은 10/1~10/28, 판매합계는 실결제 기준.</t>
         </is>
       </c>
     </row>
@@ -20738,11 +20885,11 @@
         <f>SUMIFS('데이터_자사몰'!$F$2:$F$300,'데이터_자사몰'!$H$2:$H$300,"아넬라")</f>
         <v/>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="23">
         <f>SUMIFS('데이터_자사몰'!$G$2:$G$300,'데이터_자사몰'!$H$2:$H$300,"아넬라")/10000</f>
         <v/>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="23">
         <f>SUMIFS('데이터_자사몰'!$G$2:$G$300,'데이터_자사몰'!$H$2:$H$300,"아넬라",'데이터_자사몰'!$I$2:$I$300,"시크릿특가")/10000</f>
         <v/>
       </c>
@@ -20750,7 +20897,7 @@
         <f>IF(F7=0,0,G7/F7)</f>
         <v/>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="23">
         <f>SUMIFS('데이터_자사몰'!$G$2:$G$300,'데이터_자사몰'!$H$2:$H$300,"아넬라",'데이터_자사몰'!$I$2:$I$300,"첫구매전용")/10000</f>
         <v/>
       </c>
@@ -20758,7 +20905,7 @@
         <f>IF(F7=0,0,I7/F7)</f>
         <v/>
       </c>
-      <c r="K7" s="22">
+      <c r="K7" s="23">
         <f>F7-G7-I7</f>
         <v/>
       </c>
@@ -20785,11 +20932,11 @@
         <f>SUMIFS('데이터_자사몰'!$F$2:$F$300,'데이터_자사몰'!$H$2:$H$300,"로지오가닉")</f>
         <v/>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="23">
         <f>SUMIFS('데이터_자사몰'!$G$2:$G$300,'데이터_자사몰'!$H$2:$H$300,"로지오가닉")/10000</f>
         <v/>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="23">
         <f>SUMIFS('데이터_자사몰'!$G$2:$G$300,'데이터_자사몰'!$H$2:$H$300,"로지오가닉",'데이터_자사몰'!$I$2:$I$300,"시크릿특가")/10000</f>
         <v/>
       </c>
@@ -20797,7 +20944,7 @@
         <f>IF(F8=0,0,G8/F8)</f>
         <v/>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="23">
         <f>SUMIFS('데이터_자사몰'!$G$2:$G$300,'데이터_자사몰'!$H$2:$H$300,"로지오가닉",'데이터_자사몰'!$I$2:$I$300,"첫구매전용")/10000</f>
         <v/>
       </c>
@@ -20805,7 +20952,7 @@
         <f>IF(F8=0,0,I8/F8)</f>
         <v/>
       </c>
-      <c r="K8" s="22">
+      <c r="K8" s="23">
         <f>F8-G8-I8</f>
         <v/>
       </c>
@@ -20832,11 +20979,11 @@
         <f>SUMIFS('데이터_자사몰'!$F$2:$F$300,'데이터_자사몰'!$H$2:$H$300,"공통")</f>
         <v/>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="23">
         <f>SUMIFS('데이터_자사몰'!$G$2:$G$300,'데이터_자사몰'!$H$2:$H$300,"공통")/10000</f>
         <v/>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="23">
         <f>SUMIFS('데이터_자사몰'!$G$2:$G$300,'데이터_자사몰'!$H$2:$H$300,"공통",'데이터_자사몰'!$I$2:$I$300,"시크릿특가")/10000</f>
         <v/>
       </c>
@@ -20844,7 +20991,7 @@
         <f>IF(F9=0,0,G9/F9)</f>
         <v/>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="23">
         <f>SUMIFS('데이터_자사몰'!$G$2:$G$300,'데이터_자사몰'!$H$2:$H$300,"공통",'데이터_자사몰'!$I$2:$I$300,"첫구매전용")/10000</f>
         <v/>
       </c>
@@ -20852,7 +20999,7 @@
         <f>IF(F9=0,0,I9/F9)</f>
         <v/>
       </c>
-      <c r="K9" s="22">
+      <c r="K9" s="23">
         <f>F9-G9-I9</f>
         <v/>
       </c>
@@ -20905,7 +21052,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>브랜드 구분은 상품명에 "아넬라"/"로지오가닉"이 있는지로 구분. 두 브랜드가 함께 적힌 상품(신규회원 한정 맛보기팩)은 공통으로 분리.</t>
         </is>
@@ -20976,15 +21123,15 @@
           <t>아넬라</t>
         </is>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A15,'데이터_광고'!$B$2:$B$500,"메타 자사몰",'데이터_광고'!$C$2:$C$500,"*시크릿링크*")/10000</f>
         <v/>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A15,'데이터_광고'!$B$2:$B$500,"메타 자사몰",'데이터_광고'!$C$2:$C$500,"*시크릿링크*")/10000</f>
         <v/>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="23">
         <f>G7</f>
         <v/>
       </c>
@@ -21000,11 +21147,11 @@
         <f>IF(B15=0,0,D15/B15)</f>
         <v/>
       </c>
-      <c r="H15" s="22">
+      <c r="H15" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A15,'데이터_광고'!$B$2:$B$500,"메타 자사몰")/10000</f>
         <v/>
       </c>
-      <c r="I15" s="22">
+      <c r="I15" s="23">
         <f>F7</f>
         <v/>
       </c>
@@ -21019,15 +21166,15 @@
           <t>로지오가닉</t>
         </is>
       </c>
-      <c r="B16" s="22">
+      <c r="B16" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A16,'데이터_광고'!$B$2:$B$500,"메타 자사몰",'데이터_광고'!$C$2:$C$500,"*시크릿링크*")/10000</f>
         <v/>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="23">
         <f>SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A16,'데이터_광고'!$B$2:$B$500,"메타 자사몰",'데이터_광고'!$C$2:$C$500,"*시크릿링크*")/10000</f>
         <v/>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="23">
         <f>G8</f>
         <v/>
       </c>
@@ -21043,11 +21190,11 @@
         <f>IF(B16=0,0,D16/B16)</f>
         <v/>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="23">
         <f>SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A16,'데이터_광고'!$B$2:$B$500,"메타 자사몰")/10000</f>
         <v/>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="23">
         <f>F8</f>
         <v/>
       </c>
@@ -21057,9 +21204,9 @@
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="21" t="inlineStr">
-        <is>
-          <t>시크릿링크 광고비는 캠페인명에 "시크릿링크"가 들어간 메타 자사몰 캠페인만 합산(아넬라 웰컴박스 제외). 메타 보고 매출이 실매출보다 큰 것은 귀속 기준 차이(조회 후 전환 등) 또는 환불·할인 반영 차이로 추정, 판매합계의 쿠폰·할인 반영 여부(실결제 기준) 확인 필요.</t>
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>시크릿링크 광고비는 캠페인명에 "시크릿링크"가 들어간 메타 자사몰 캠페인만 합산(아넬라 웰컴박스 제외). 메타 보고 매출이 실매출보다 큰 것은 귀속 기준 차이(조회 후 전환 등) 또는 환불·할인 반영 차이로 추정(판매합계는 실결제 기준).</t>
         </is>
       </c>
     </row>
@@ -21101,7 +21248,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="n">
+      <c r="A22" s="20" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="32">
@@ -21111,21 +21258,21 @@
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
       <c r="E22" s="50" t="n"/>
-      <c r="F22" s="22">
+      <c r="F22" s="23">
         <f>'데이터_자사몰'!G4/10000</f>
         <v/>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="20">
         <f>'데이터_자사몰'!H4</f>
         <v/>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="20">
         <f>'데이터_자사몰'!I4</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="n">
+      <c r="A23" s="20" t="n">
         <v>2</v>
       </c>
       <c r="B23" s="32">
@@ -21135,21 +21282,21 @@
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
       <c r="E23" s="50" t="n"/>
-      <c r="F23" s="22">
+      <c r="F23" s="23">
         <f>'데이터_자사몰'!G2/10000</f>
         <v/>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="20">
         <f>'데이터_자사몰'!H2</f>
         <v/>
       </c>
-      <c r="H23" s="19">
+      <c r="H23" s="20">
         <f>'데이터_자사몰'!I2</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="n">
+      <c r="A24" s="20" t="n">
         <v>3</v>
       </c>
       <c r="B24" s="32">
@@ -21159,21 +21306,21 @@
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
       <c r="E24" s="50" t="n"/>
-      <c r="F24" s="22">
+      <c r="F24" s="23">
         <f>'데이터_자사몰'!G3/10000</f>
         <v/>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="20">
         <f>'데이터_자사몰'!H3</f>
         <v/>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="20">
         <f>'데이터_자사몰'!I3</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="n">
+      <c r="A25" s="20" t="n">
         <v>4</v>
       </c>
       <c r="B25" s="32">
@@ -21183,21 +21330,21 @@
       <c r="C25" s="49" t="n"/>
       <c r="D25" s="49" t="n"/>
       <c r="E25" s="50" t="n"/>
-      <c r="F25" s="22">
+      <c r="F25" s="23">
         <f>'데이터_자사몰'!G9/10000</f>
         <v/>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="20">
         <f>'데이터_자사몰'!H9</f>
         <v/>
       </c>
-      <c r="H25" s="19">
+      <c r="H25" s="20">
         <f>'데이터_자사몰'!I9</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="n">
+      <c r="A26" s="20" t="n">
         <v>5</v>
       </c>
       <c r="B26" s="32">
@@ -21207,21 +21354,21 @@
       <c r="C26" s="49" t="n"/>
       <c r="D26" s="49" t="n"/>
       <c r="E26" s="50" t="n"/>
-      <c r="F26" s="22">
+      <c r="F26" s="23">
         <f>'데이터_자사몰'!G8/10000</f>
         <v/>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="20">
         <f>'데이터_자사몰'!H8</f>
         <v/>
       </c>
-      <c r="H26" s="19">
+      <c r="H26" s="20">
         <f>'데이터_자사몰'!I8</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="n">
+      <c r="A27" s="20" t="n">
         <v>6</v>
       </c>
       <c r="B27" s="32">
@@ -21231,21 +21378,21 @@
       <c r="C27" s="49" t="n"/>
       <c r="D27" s="49" t="n"/>
       <c r="E27" s="50" t="n"/>
-      <c r="F27" s="22">
+      <c r="F27" s="23">
         <f>'데이터_자사몰'!G10/10000</f>
         <v/>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="20">
         <f>'데이터_자사몰'!H10</f>
         <v/>
       </c>
-      <c r="H27" s="19">
+      <c r="H27" s="20">
         <f>'데이터_자사몰'!I10</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="19" t="n">
+      <c r="A28" s="20" t="n">
         <v>7</v>
       </c>
       <c r="B28" s="32">
@@ -21255,21 +21402,21 @@
       <c r="C28" s="49" t="n"/>
       <c r="D28" s="49" t="n"/>
       <c r="E28" s="50" t="n"/>
-      <c r="F28" s="22">
+      <c r="F28" s="23">
         <f>'데이터_자사몰'!G6/10000</f>
         <v/>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="20">
         <f>'데이터_자사몰'!H6</f>
         <v/>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="20">
         <f>'데이터_자사몰'!I6</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="19" t="n">
+      <c r="A29" s="20" t="n">
         <v>8</v>
       </c>
       <c r="B29" s="32">
@@ -21279,21 +21426,21 @@
       <c r="C29" s="49" t="n"/>
       <c r="D29" s="49" t="n"/>
       <c r="E29" s="50" t="n"/>
-      <c r="F29" s="22">
+      <c r="F29" s="23">
         <f>'데이터_자사몰'!G17/10000</f>
         <v/>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="20">
         <f>'데이터_자사몰'!H17</f>
         <v/>
       </c>
-      <c r="H29" s="19">
+      <c r="H29" s="20">
         <f>'데이터_자사몰'!I17</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="n">
+      <c r="A30" s="20" t="n">
         <v>9</v>
       </c>
       <c r="B30" s="32">
@@ -21303,21 +21450,21 @@
       <c r="C30" s="49" t="n"/>
       <c r="D30" s="49" t="n"/>
       <c r="E30" s="50" t="n"/>
-      <c r="F30" s="22">
+      <c r="F30" s="23">
         <f>'데이터_자사몰'!G14/10000</f>
         <v/>
       </c>
-      <c r="G30" s="19">
+      <c r="G30" s="20">
         <f>'데이터_자사몰'!H14</f>
         <v/>
       </c>
-      <c r="H30" s="19">
+      <c r="H30" s="20">
         <f>'데이터_자사몰'!I14</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="n">
+      <c r="A31" s="20" t="n">
         <v>10</v>
       </c>
       <c r="B31" s="32">
@@ -21327,15 +21474,15 @@
       <c r="C31" s="49" t="n"/>
       <c r="D31" s="49" t="n"/>
       <c r="E31" s="50" t="n"/>
-      <c r="F31" s="22">
+      <c r="F31" s="23">
         <f>'데이터_자사몰'!G7/10000</f>
         <v/>
       </c>
-      <c r="G31" s="19">
+      <c r="G31" s="20">
         <f>'데이터_자사몰'!H7</f>
         <v/>
       </c>
-      <c r="H31" s="19">
+      <c r="H31" s="20">
         <f>'데이터_자사몰'!I7</f>
         <v/>
       </c>
@@ -21402,7 +21549,7 @@
           <t>아넬라</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>기간별 광고 성과와 스마트스토어 매출</t>
         </is>
@@ -21456,36 +21603,36 @@
           <t>기간</t>
         </is>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <f>TEXT('가정'!B50,"m/d")&amp;"~"&amp;TEXT('가정'!C50,"m/d")</f>
         <v/>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="20">
         <f>TEXT('가정'!B51,"m/d")&amp;"~"&amp;TEXT('가정'!C51,"m/d")</f>
         <v/>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <f>TEXT('가정'!B52,"m/d")&amp;"~"&amp;TEXT('가정'!C52,"m/d")</f>
         <v/>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <f>TEXT('가정'!B53,"m/d")&amp;"~"&amp;TEXT('가정'!C53,"m/d")</f>
         <v/>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="20">
         <f>TEXT('가정'!B54,"m/d")&amp;"~"&amp;TEXT('가정'!C54,"m/d")</f>
         <v/>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="20">
         <f>TEXT('가정'!B5,"m/d")&amp;"~"&amp;TEXT('가정'!B6,"m/d")</f>
         <v/>
       </c>
-      <c r="H6" s="19" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>상시</t>
         </is>
       </c>
-      <c r="I6" s="19" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>행사</t>
         </is>
@@ -21497,37 +21644,37 @@
           <t>구분</t>
         </is>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="20">
         <f>'가정'!E50</f>
         <v/>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="20">
         <f>'가정'!E51</f>
         <v/>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="20">
         <f>'가정'!E52</f>
         <v/>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="20">
         <f>'가정'!E53</f>
         <v/>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="20">
         <f>'가정'!E54</f>
         <v/>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>상시</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>행사</t>
         </is>
@@ -22046,7 +22193,7 @@
           <t>로지오가닉</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>기간별 광고 성과와 스마트스토어 매출</t>
         </is>
@@ -22100,36 +22247,36 @@
           <t>기간</t>
         </is>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="20">
         <f>TEXT('가정'!B50,"m/d")&amp;"~"&amp;TEXT('가정'!C50,"m/d")</f>
         <v/>
       </c>
-      <c r="C27" s="19">
+      <c r="C27" s="20">
         <f>TEXT('가정'!B51,"m/d")&amp;"~"&amp;TEXT('가정'!C51,"m/d")</f>
         <v/>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="20">
         <f>TEXT('가정'!B52,"m/d")&amp;"~"&amp;TEXT('가정'!C52,"m/d")</f>
         <v/>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="20">
         <f>TEXT('가정'!B53,"m/d")&amp;"~"&amp;TEXT('가정'!C53,"m/d")</f>
         <v/>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="20">
         <f>TEXT('가정'!B54,"m/d")&amp;"~"&amp;TEXT('가정'!C54,"m/d")</f>
         <v/>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="20">
         <f>TEXT('가정'!B5,"m/d")&amp;"~"&amp;TEXT('가정'!B6,"m/d")</f>
         <v/>
       </c>
-      <c r="H27" s="19" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>상시</t>
         </is>
       </c>
-      <c r="I27" s="19" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>행사</t>
         </is>
@@ -22141,37 +22288,37 @@
           <t>구분</t>
         </is>
       </c>
-      <c r="B28" s="19">
+      <c r="B28" s="20">
         <f>'가정'!E50</f>
         <v/>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="20">
         <f>'가정'!E51</f>
         <v/>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="20">
         <f>'가정'!E52</f>
         <v/>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="20">
         <f>'가정'!E53</f>
         <v/>
       </c>
-      <c r="F28" s="19">
+      <c r="F28" s="20">
         <f>'가정'!E54</f>
         <v/>
       </c>
-      <c r="G28" s="19" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H28" s="19" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>상시</t>
         </is>
       </c>
-      <c r="I28" s="19" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>행사</t>
         </is>
@@ -22739,35 +22886,35 @@
           <t>파워링크</t>
         </is>
       </c>
-      <c r="B48" s="23">
+      <c r="B48" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$D$2:$D$500,B$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$D$2:$D$500,B$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$D$2:$D$500,B$47))</f>
         <v/>
       </c>
-      <c r="C48" s="23">
+      <c r="C48" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$D$2:$D$500,C$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$D$2:$D$500,C$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$D$2:$D$500,C$47))</f>
         <v/>
       </c>
-      <c r="D48" s="23">
+      <c r="D48" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$D$2:$D$500,D$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$D$2:$D$500,D$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$D$2:$D$500,D$47))</f>
         <v/>
       </c>
-      <c r="E48" s="23">
+      <c r="E48" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$D$2:$D$500,E$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$D$2:$D$500,E$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$D$2:$D$500,E$47))</f>
         <v/>
       </c>
-      <c r="F48" s="23">
+      <c r="F48" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$D$2:$D$500,F$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$D$2:$D$500,F$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$D$2:$D$500,F$47))</f>
         <v/>
       </c>
-      <c r="G48" s="16">
+      <c r="G48" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48))</f>
         <v/>
       </c>
-      <c r="H48" s="16">
+      <c r="H48" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$J$2:$J$500,"상시")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$J$2:$J$500,"상시")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$J$2:$J$500,"상시"))</f>
         <v/>
       </c>
-      <c r="I48" s="16">
+      <c r="I48" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$J$2:$J$500,"행사")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$J$2:$J$500,"행사")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A48,'데이터_광고'!$J$2:$J$500,"행사"))</f>
         <v/>
       </c>
@@ -22778,35 +22925,35 @@
           <t>쇼핑검색</t>
         </is>
       </c>
-      <c r="B49" s="23">
+      <c r="B49" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$D$2:$D$500,B$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$D$2:$D$500,B$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$D$2:$D$500,B$47))</f>
         <v/>
       </c>
-      <c r="C49" s="23">
+      <c r="C49" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$D$2:$D$500,C$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$D$2:$D$500,C$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$D$2:$D$500,C$47))</f>
         <v/>
       </c>
-      <c r="D49" s="23">
+      <c r="D49" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$D$2:$D$500,D$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$D$2:$D$500,D$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$D$2:$D$500,D$47))</f>
         <v/>
       </c>
-      <c r="E49" s="23">
+      <c r="E49" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$D$2:$D$500,E$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$D$2:$D$500,E$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$D$2:$D$500,E$47))</f>
         <v/>
       </c>
-      <c r="F49" s="23">
+      <c r="F49" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$D$2:$D$500,F$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$D$2:$D$500,F$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$D$2:$D$500,F$47))</f>
         <v/>
       </c>
-      <c r="G49" s="16">
+      <c r="G49" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49))</f>
         <v/>
       </c>
-      <c r="H49" s="16">
+      <c r="H49" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$J$2:$J$500,"상시")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$J$2:$J$500,"상시")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$J$2:$J$500,"상시"))</f>
         <v/>
       </c>
-      <c r="I49" s="16">
+      <c r="I49" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$J$2:$J$500,"행사")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$J$2:$J$500,"행사")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A49,'데이터_광고'!$J$2:$J$500,"행사"))</f>
         <v/>
       </c>
@@ -22817,35 +22964,35 @@
           <t>브랜드검색</t>
         </is>
       </c>
-      <c r="B50" s="23">
+      <c r="B50" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$D$2:$D$500,B$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$D$2:$D$500,B$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$D$2:$D$500,B$47))</f>
         <v/>
       </c>
-      <c r="C50" s="23">
+      <c r="C50" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$D$2:$D$500,C$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$D$2:$D$500,C$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$D$2:$D$500,C$47))</f>
         <v/>
       </c>
-      <c r="D50" s="23">
+      <c r="D50" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$D$2:$D$500,D$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$D$2:$D$500,D$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$D$2:$D$500,D$47))</f>
         <v/>
       </c>
-      <c r="E50" s="23">
+      <c r="E50" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$D$2:$D$500,E$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$D$2:$D$500,E$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$D$2:$D$500,E$47))</f>
         <v/>
       </c>
-      <c r="F50" s="23">
+      <c r="F50" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$D$2:$D$500,F$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$D$2:$D$500,F$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$D$2:$D$500,F$47))</f>
         <v/>
       </c>
-      <c r="G50" s="16">
+      <c r="G50" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50))</f>
         <v/>
       </c>
-      <c r="H50" s="16">
+      <c r="H50" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$J$2:$J$500,"상시")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$J$2:$J$500,"상시")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$J$2:$J$500,"상시"))</f>
         <v/>
       </c>
-      <c r="I50" s="16">
+      <c r="I50" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$J$2:$J$500,"행사")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$J$2:$J$500,"행사")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A50,'데이터_광고'!$J$2:$J$500,"행사"))</f>
         <v/>
       </c>
@@ -22856,35 +23003,35 @@
           <t>GFA 카탈로그</t>
         </is>
       </c>
-      <c r="B51" s="23">
+      <c r="B51" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$D$2:$D$500,B$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$D$2:$D$500,B$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$D$2:$D$500,B$47))</f>
         <v/>
       </c>
-      <c r="C51" s="23">
+      <c r="C51" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$D$2:$D$500,C$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$D$2:$D$500,C$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$D$2:$D$500,C$47))</f>
         <v/>
       </c>
-      <c r="D51" s="23">
+      <c r="D51" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$D$2:$D$500,D$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$D$2:$D$500,D$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$D$2:$D$500,D$47))</f>
         <v/>
       </c>
-      <c r="E51" s="23">
+      <c r="E51" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$D$2:$D$500,E$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$D$2:$D$500,E$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$D$2:$D$500,E$47))</f>
         <v/>
       </c>
-      <c r="F51" s="23">
+      <c r="F51" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$D$2:$D$500,F$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$D$2:$D$500,F$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$D$2:$D$500,F$47))</f>
         <v/>
       </c>
-      <c r="G51" s="16">
+      <c r="G51" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51))</f>
         <v/>
       </c>
-      <c r="H51" s="16">
+      <c r="H51" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$J$2:$J$500,"상시")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$J$2:$J$500,"상시")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$J$2:$J$500,"상시"))</f>
         <v/>
       </c>
-      <c r="I51" s="16">
+      <c r="I51" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$J$2:$J$500,"행사")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$J$2:$J$500,"행사")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A51,'데이터_광고'!$J$2:$J$500,"행사"))</f>
         <v/>
       </c>
@@ -22895,35 +23042,35 @@
           <t>GFA 전환</t>
         </is>
       </c>
-      <c r="B52" s="23">
+      <c r="B52" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$D$2:$D$500,B$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$D$2:$D$500,B$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$D$2:$D$500,B$47))</f>
         <v/>
       </c>
-      <c r="C52" s="23">
+      <c r="C52" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$D$2:$D$500,C$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$D$2:$D$500,C$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$D$2:$D$500,C$47))</f>
         <v/>
       </c>
-      <c r="D52" s="23">
+      <c r="D52" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$D$2:$D$500,D$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$D$2:$D$500,D$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$D$2:$D$500,D$47))</f>
         <v/>
       </c>
-      <c r="E52" s="23">
+      <c r="E52" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$D$2:$D$500,E$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$D$2:$D$500,E$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$D$2:$D$500,E$47))</f>
         <v/>
       </c>
-      <c r="F52" s="23">
+      <c r="F52" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$D$2:$D$500,F$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$D$2:$D$500,F$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$D$2:$D$500,F$47))</f>
         <v/>
       </c>
-      <c r="G52" s="16">
+      <c r="G52" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52))</f>
         <v/>
       </c>
-      <c r="H52" s="16">
+      <c r="H52" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$J$2:$J$500,"상시")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$J$2:$J$500,"상시")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$J$2:$J$500,"상시"))</f>
         <v/>
       </c>
-      <c r="I52" s="16">
+      <c r="I52" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$J$2:$J$500,"행사")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$J$2:$J$500,"행사")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A52,'데이터_광고'!$J$2:$J$500,"행사"))</f>
         <v/>
       </c>
@@ -22934,35 +23081,35 @@
           <t>메타 스스</t>
         </is>
       </c>
-      <c r="B53" s="23">
+      <c r="B53" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$D$2:$D$500,B$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$D$2:$D$500,B$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$D$2:$D$500,B$47))</f>
         <v/>
       </c>
-      <c r="C53" s="23">
+      <c r="C53" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$D$2:$D$500,C$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$D$2:$D$500,C$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$D$2:$D$500,C$47))</f>
         <v/>
       </c>
-      <c r="D53" s="23">
+      <c r="D53" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$D$2:$D$500,D$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$D$2:$D$500,D$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$D$2:$D$500,D$47))</f>
         <v/>
       </c>
-      <c r="E53" s="23">
+      <c r="E53" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$D$2:$D$500,E$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$D$2:$D$500,E$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$D$2:$D$500,E$47))</f>
         <v/>
       </c>
-      <c r="F53" s="23">
+      <c r="F53" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$D$2:$D$500,F$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$D$2:$D$500,F$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$D$2:$D$500,F$47))</f>
         <v/>
       </c>
-      <c r="G53" s="16">
+      <c r="G53" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53))</f>
         <v/>
       </c>
-      <c r="H53" s="16">
+      <c r="H53" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$J$2:$J$500,"상시")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$J$2:$J$500,"상시")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$J$2:$J$500,"상시"))</f>
         <v/>
       </c>
-      <c r="I53" s="16">
+      <c r="I53" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$J$2:$J$500,"행사")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$J$2:$J$500,"행사")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A53,'데이터_광고'!$J$2:$J$500,"행사"))</f>
         <v/>
       </c>
@@ -22973,41 +23120,41 @@
           <t>메타 자사몰</t>
         </is>
       </c>
-      <c r="B54" s="23">
+      <c r="B54" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$D$2:$D$500,B$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$D$2:$D$500,B$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$D$2:$D$500,B$47))</f>
         <v/>
       </c>
-      <c r="C54" s="23">
+      <c r="C54" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$D$2:$D$500,C$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$D$2:$D$500,C$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$D$2:$D$500,C$47))</f>
         <v/>
       </c>
-      <c r="D54" s="23">
+      <c r="D54" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$D$2:$D$500,D$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$D$2:$D$500,D$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$D$2:$D$500,D$47))</f>
         <v/>
       </c>
-      <c r="E54" s="23">
+      <c r="E54" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$D$2:$D$500,E$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$D$2:$D$500,E$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$D$2:$D$500,E$47))</f>
         <v/>
       </c>
-      <c r="F54" s="23">
+      <c r="F54" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$D$2:$D$500,F$47)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$D$2:$D$500,F$47)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$D$2:$D$500,F$47))</f>
         <v/>
       </c>
-      <c r="G54" s="16">
+      <c r="G54" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54))</f>
         <v/>
       </c>
-      <c r="H54" s="16">
+      <c r="H54" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$J$2:$J$500,"상시")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$J$2:$J$500,"상시")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$J$2:$J$500,"상시"))</f>
         <v/>
       </c>
-      <c r="I54" s="16">
+      <c r="I54" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$J$2:$J$500,"행사")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$J$2:$J$500,"행사")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$4,'데이터_광고'!$B$2:$B$500,$A54,'데이터_광고'!$J$2:$J$500,"행사"))</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="21" t="inlineStr">
+      <c r="A56" s="22" t="inlineStr">
         <is>
           <t>광고비가 0이면 "-"로 표시. 브랜드검색은 정액 대비 매출, GFA 전환 로지오가닉은 10/26 이후만 집행.</t>
         </is>
@@ -23068,35 +23215,35 @@
           <t>파워링크</t>
         </is>
       </c>
-      <c r="B60" s="23">
+      <c r="B60" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$D$2:$D$500,B$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$D$2:$D$500,B$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$D$2:$D$500,B$59))</f>
         <v/>
       </c>
-      <c r="C60" s="23">
+      <c r="C60" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$D$2:$D$500,C$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$D$2:$D$500,C$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$D$2:$D$500,C$59))</f>
         <v/>
       </c>
-      <c r="D60" s="23">
+      <c r="D60" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$D$2:$D$500,D$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$D$2:$D$500,D$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$D$2:$D$500,D$59))</f>
         <v/>
       </c>
-      <c r="E60" s="23">
+      <c r="E60" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$D$2:$D$500,E$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$D$2:$D$500,E$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$D$2:$D$500,E$59))</f>
         <v/>
       </c>
-      <c r="F60" s="23">
+      <c r="F60" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$D$2:$D$500,F$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$D$2:$D$500,F$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$D$2:$D$500,F$59))</f>
         <v/>
       </c>
-      <c r="G60" s="16">
+      <c r="G60" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60))</f>
         <v/>
       </c>
-      <c r="H60" s="16">
+      <c r="H60" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$J$2:$J$500,"상시")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$J$2:$J$500,"상시")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$J$2:$J$500,"상시"))</f>
         <v/>
       </c>
-      <c r="I60" s="16">
+      <c r="I60" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$J$2:$J$500,"행사")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$J$2:$J$500,"행사")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A60,'데이터_광고'!$J$2:$J$500,"행사"))</f>
         <v/>
       </c>
@@ -23107,35 +23254,35 @@
           <t>쇼핑검색</t>
         </is>
       </c>
-      <c r="B61" s="23">
+      <c r="B61" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$D$2:$D$500,B$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$D$2:$D$500,B$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$D$2:$D$500,B$59))</f>
         <v/>
       </c>
-      <c r="C61" s="23">
+      <c r="C61" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$D$2:$D$500,C$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$D$2:$D$500,C$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$D$2:$D$500,C$59))</f>
         <v/>
       </c>
-      <c r="D61" s="23">
+      <c r="D61" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$D$2:$D$500,D$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$D$2:$D$500,D$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$D$2:$D$500,D$59))</f>
         <v/>
       </c>
-      <c r="E61" s="23">
+      <c r="E61" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$D$2:$D$500,E$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$D$2:$D$500,E$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$D$2:$D$500,E$59))</f>
         <v/>
       </c>
-      <c r="F61" s="23">
+      <c r="F61" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$D$2:$D$500,F$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$D$2:$D$500,F$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$D$2:$D$500,F$59))</f>
         <v/>
       </c>
-      <c r="G61" s="16">
+      <c r="G61" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61))</f>
         <v/>
       </c>
-      <c r="H61" s="16">
+      <c r="H61" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$J$2:$J$500,"상시")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$J$2:$J$500,"상시")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$J$2:$J$500,"상시"))</f>
         <v/>
       </c>
-      <c r="I61" s="16">
+      <c r="I61" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$J$2:$J$500,"행사")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$J$2:$J$500,"행사")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A61,'데이터_광고'!$J$2:$J$500,"행사"))</f>
         <v/>
       </c>
@@ -23146,35 +23293,35 @@
           <t>브랜드검색</t>
         </is>
       </c>
-      <c r="B62" s="23">
+      <c r="B62" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$D$2:$D$500,B$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$D$2:$D$500,B$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$D$2:$D$500,B$59))</f>
         <v/>
       </c>
-      <c r="C62" s="23">
+      <c r="C62" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$D$2:$D$500,C$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$D$2:$D$500,C$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$D$2:$D$500,C$59))</f>
         <v/>
       </c>
-      <c r="D62" s="23">
+      <c r="D62" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$D$2:$D$500,D$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$D$2:$D$500,D$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$D$2:$D$500,D$59))</f>
         <v/>
       </c>
-      <c r="E62" s="23">
+      <c r="E62" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$D$2:$D$500,E$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$D$2:$D$500,E$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$D$2:$D$500,E$59))</f>
         <v/>
       </c>
-      <c r="F62" s="23">
+      <c r="F62" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$D$2:$D$500,F$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$D$2:$D$500,F$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$D$2:$D$500,F$59))</f>
         <v/>
       </c>
-      <c r="G62" s="16">
+      <c r="G62" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62))</f>
         <v/>
       </c>
-      <c r="H62" s="16">
+      <c r="H62" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$J$2:$J$500,"상시")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$J$2:$J$500,"상시")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$J$2:$J$500,"상시"))</f>
         <v/>
       </c>
-      <c r="I62" s="16">
+      <c r="I62" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$J$2:$J$500,"행사")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$J$2:$J$500,"행사")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A62,'데이터_광고'!$J$2:$J$500,"행사"))</f>
         <v/>
       </c>
@@ -23185,35 +23332,35 @@
           <t>GFA 카탈로그</t>
         </is>
       </c>
-      <c r="B63" s="23">
+      <c r="B63" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$D$2:$D$500,B$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$D$2:$D$500,B$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$D$2:$D$500,B$59))</f>
         <v/>
       </c>
-      <c r="C63" s="23">
+      <c r="C63" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$D$2:$D$500,C$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$D$2:$D$500,C$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$D$2:$D$500,C$59))</f>
         <v/>
       </c>
-      <c r="D63" s="23">
+      <c r="D63" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$D$2:$D$500,D$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$D$2:$D$500,D$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$D$2:$D$500,D$59))</f>
         <v/>
       </c>
-      <c r="E63" s="23">
+      <c r="E63" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$D$2:$D$500,E$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$D$2:$D$500,E$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$D$2:$D$500,E$59))</f>
         <v/>
       </c>
-      <c r="F63" s="23">
+      <c r="F63" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$D$2:$D$500,F$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$D$2:$D$500,F$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$D$2:$D$500,F$59))</f>
         <v/>
       </c>
-      <c r="G63" s="16">
+      <c r="G63" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63))</f>
         <v/>
       </c>
-      <c r="H63" s="16">
+      <c r="H63" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$J$2:$J$500,"상시")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$J$2:$J$500,"상시")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$J$2:$J$500,"상시"))</f>
         <v/>
       </c>
-      <c r="I63" s="16">
+      <c r="I63" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$J$2:$J$500,"행사")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$J$2:$J$500,"행사")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A63,'데이터_광고'!$J$2:$J$500,"행사"))</f>
         <v/>
       </c>
@@ -23224,35 +23371,35 @@
           <t>GFA 전환</t>
         </is>
       </c>
-      <c r="B64" s="23">
+      <c r="B64" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$D$2:$D$500,B$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$D$2:$D$500,B$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$D$2:$D$500,B$59))</f>
         <v/>
       </c>
-      <c r="C64" s="23">
+      <c r="C64" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$D$2:$D$500,C$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$D$2:$D$500,C$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$D$2:$D$500,C$59))</f>
         <v/>
       </c>
-      <c r="D64" s="23">
+      <c r="D64" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$D$2:$D$500,D$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$D$2:$D$500,D$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$D$2:$D$500,D$59))</f>
         <v/>
       </c>
-      <c r="E64" s="23">
+      <c r="E64" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$D$2:$D$500,E$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$D$2:$D$500,E$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$D$2:$D$500,E$59))</f>
         <v/>
       </c>
-      <c r="F64" s="23">
+      <c r="F64" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$D$2:$D$500,F$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$D$2:$D$500,F$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$D$2:$D$500,F$59))</f>
         <v/>
       </c>
-      <c r="G64" s="16">
+      <c r="G64" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64))</f>
         <v/>
       </c>
-      <c r="H64" s="16">
+      <c r="H64" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$J$2:$J$500,"상시")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$J$2:$J$500,"상시")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$J$2:$J$500,"상시"))</f>
         <v/>
       </c>
-      <c r="I64" s="16">
+      <c r="I64" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$J$2:$J$500,"행사")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$J$2:$J$500,"행사")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A64,'데이터_광고'!$J$2:$J$500,"행사"))</f>
         <v/>
       </c>
@@ -23263,35 +23410,35 @@
           <t>메타 스스</t>
         </is>
       </c>
-      <c r="B65" s="23">
+      <c r="B65" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$D$2:$D$500,B$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$D$2:$D$500,B$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$D$2:$D$500,B$59))</f>
         <v/>
       </c>
-      <c r="C65" s="23">
+      <c r="C65" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$D$2:$D$500,C$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$D$2:$D$500,C$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$D$2:$D$500,C$59))</f>
         <v/>
       </c>
-      <c r="D65" s="23">
+      <c r="D65" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$D$2:$D$500,D$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$D$2:$D$500,D$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$D$2:$D$500,D$59))</f>
         <v/>
       </c>
-      <c r="E65" s="23">
+      <c r="E65" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$D$2:$D$500,E$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$D$2:$D$500,E$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$D$2:$D$500,E$59))</f>
         <v/>
       </c>
-      <c r="F65" s="23">
+      <c r="F65" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$D$2:$D$500,F$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$D$2:$D$500,F$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$D$2:$D$500,F$59))</f>
         <v/>
       </c>
-      <c r="G65" s="16">
+      <c r="G65" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65))</f>
         <v/>
       </c>
-      <c r="H65" s="16">
+      <c r="H65" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$J$2:$J$500,"상시")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$J$2:$J$500,"상시")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$J$2:$J$500,"상시"))</f>
         <v/>
       </c>
-      <c r="I65" s="16">
+      <c r="I65" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$J$2:$J$500,"행사")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$J$2:$J$500,"행사")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A65,'데이터_광고'!$J$2:$J$500,"행사"))</f>
         <v/>
       </c>
@@ -23302,41 +23449,41 @@
           <t>메타 자사몰</t>
         </is>
       </c>
-      <c r="B66" s="23">
+      <c r="B66" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$D$2:$D$500,B$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$D$2:$D$500,B$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$D$2:$D$500,B$59))</f>
         <v/>
       </c>
-      <c r="C66" s="23">
+      <c r="C66" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$D$2:$D$500,C$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$D$2:$D$500,C$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$D$2:$D$500,C$59))</f>
         <v/>
       </c>
-      <c r="D66" s="23">
+      <c r="D66" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$D$2:$D$500,D$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$D$2:$D$500,D$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$D$2:$D$500,D$59))</f>
         <v/>
       </c>
-      <c r="E66" s="23">
+      <c r="E66" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$D$2:$D$500,E$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$D$2:$D$500,E$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$D$2:$D$500,E$59))</f>
         <v/>
       </c>
-      <c r="F66" s="23">
+      <c r="F66" s="16">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$D$2:$D$500,F$59)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$D$2:$D$500,F$59)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$D$2:$D$500,F$59))</f>
         <v/>
       </c>
-      <c r="G66" s="16">
+      <c r="G66" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66))</f>
         <v/>
       </c>
-      <c r="H66" s="16">
+      <c r="H66" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$J$2:$J$500,"상시")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$J$2:$J$500,"상시")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$J$2:$J$500,"상시"))</f>
         <v/>
       </c>
-      <c r="I66" s="16">
+      <c r="I66" s="17">
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$J$2:$J$500,"행사")=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$J$2:$J$500,"행사")/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,$A$25,'데이터_광고'!$B$2:$B$500,$A66,'데이터_광고'!$J$2:$J$500,"행사"))</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="21" t="inlineStr">
+      <c r="A68" s="22" t="inlineStr">
         <is>
           <t>광고비가 0이면 "-"로 표시. 브랜드검색은 정액 대비 매출, GFA 전환 로지오가닉은 10/26 이후만 집행.</t>
         </is>
@@ -23432,7 +23579,7 @@
           <t>잘한 점</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>아넬라</t>
         </is>
@@ -23472,7 +23619,7 @@
           <t>잘한 점</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>아넬라</t>
         </is>
@@ -23512,7 +23659,7 @@
           <t>잘한 점</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>아넬라</t>
         </is>
@@ -23552,7 +23699,7 @@
           <t>잘한 점</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>아넬라</t>
         </is>
@@ -23592,7 +23739,7 @@
           <t>잘한 점</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>로지오가닉</t>
         </is>
@@ -23632,7 +23779,7 @@
           <t>잘한 점</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>로지오가닉</t>
         </is>
@@ -23672,7 +23819,7 @@
           <t>잘한 점</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>로지오가닉</t>
         </is>
@@ -23712,7 +23859,7 @@
           <t>잘한 점</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>로지오가닉</t>
         </is>
@@ -23752,7 +23899,7 @@
           <t>미달·보완</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>아넬라</t>
         </is>
@@ -23791,7 +23938,7 @@
           <t>미달·보완</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>아넬라</t>
         </is>
@@ -23831,7 +23978,7 @@
           <t>미달·보완</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>아넬라</t>
         </is>
@@ -23870,7 +24017,7 @@
           <t>미달·보완</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>아넬라</t>
         </is>
@@ -23910,7 +24057,7 @@
           <t>미달·보완</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>아넬라</t>
         </is>
@@ -23949,7 +24096,7 @@
           <t>미달·보완</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>아넬라</t>
         </is>
@@ -23989,7 +24136,7 @@
           <t>미달·보완</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>아넬라</t>
         </is>
@@ -24028,7 +24175,7 @@
           <t>미달·보완</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>로지오가닉</t>
         </is>
@@ -24068,7 +24215,7 @@
           <t>미달·보완</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>로지오가닉</t>
         </is>
@@ -24107,7 +24254,7 @@
           <t>데이터 점검</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>로지오가닉</t>
         </is>
@@ -24146,7 +24293,7 @@
           <t>데이터 점검</t>
         </is>
       </c>
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>로지오가닉</t>
         </is>
@@ -24214,14 +24361,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>파워링크·쇼핑검색 시간대 지정 노출 결과(노출 제외 0~3시, 17~24시, 두 매체 동일, 10/14 시작). 쇼핑검색은 10/26 넾다세일부터 24시간 균등 노출로 원복. 수치는 데이터_광고 시트 SUMIFS 수식이며 대행사 보고 수치와 일치.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21">
+      <c r="A3" s="22">
         <f>"비교기간 "&amp;TEXT('가정'!B51,"m/d")&amp;"~"&amp;TEXT('가정'!C51,"m/d")&amp;" (10월 2주차, 제한 전) vs 기준기간 "&amp;TEXT('가정'!B53,"m/d")&amp;"~"&amp;TEXT('가정'!C53,"m/d")&amp;" (10월 4주차, 제한 후). 두 기간 모두 상시 구간."</f>
         <v/>
       </c>
@@ -24615,7 +24762,7 @@
         <f>IF(SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,"아넬라",'데이터_광고'!$B$2:$B$500,"쇼핑검색",'데이터_광고'!$D$2:$D$500,'가정'!$A$54)=0,0,SUMIFS('데이터_광고'!$I$2:$I$500,'데이터_광고'!$A$2:$A$500,"아넬라",'데이터_광고'!$B$2:$B$500,"쇼핑검색",'데이터_광고'!$D$2:$D$500,'가정'!$A$54)/SUMIFS('데이터_광고'!$E$2:$E$500,'데이터_광고'!$A$2:$A$500,"아넬라",'데이터_광고'!$B$2:$B$500,"쇼핑검색",'데이터_광고'!$D$2:$D$500,'가정'!$A$54))</f>
         <v/>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>원복과 넾다세일이 같은 날 시작되어 원복 효과 분리 불가. 11/8 이후 상시 구간과 비교 필요.</t>
         </is>
@@ -24689,7 +24836,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>출처: 노출 시간 제한 결과 정리는 대행사 코멘트(사용자 전달, 2026-10-29). 시간 설정은 10/14 시작. 노출 제외 시간대는 0~3시, 17~24시로 파워링크·쇼핑검색 동일(사용자 확인).</t>
         </is>
@@ -24837,7 +24984,7 @@
       <c r="B8" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>1이면 로지오가닉 메타 스스의 10/24~25를 상시 ROAS 계산에서 제외 (점검 시트 1번)</t>
         </is>
@@ -24972,39 +25119,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A12,'점검'!$B$14:$B$14,$B12)</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="17">
         <f>IF(C12-G12&gt;0,(D12-H12)/(C12-G12),IF(E12&gt;0,F12/E12,0))</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="17">
         <f>IF(E12&gt;0,F12/E12,I12)</f>
         <v/>
       </c>
-      <c r="K12" s="22">
+      <c r="K12" s="23">
         <f>SUMIFS('가정'!$D$16:$D$27,'가정'!$A$16:$A$27,$A12,'가정'!$B$16:$B$27,$B12)</f>
         <v/>
       </c>
-      <c r="L12" s="16">
+      <c r="L12" s="17">
         <f>($B$6*$J12+('가정'!$B$10-$B$6)*$I12)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="M12" s="16">
+      <c r="M12" s="17">
         <f>($C$6*$J12+('가정'!$B$10-$C$6)*$I12)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="N12" s="16">
+      <c r="N12" s="17">
         <f>($D$6*$J12+('가정'!$B$10-$D$6)*$I12)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="O12" s="22">
+      <c r="O12" s="23">
         <f>$K12*L12</f>
         <v/>
       </c>
-      <c r="P12" s="22">
+      <c r="P12" s="23">
         <f>$K12*M12</f>
         <v/>
       </c>
-      <c r="Q12" s="22">
+      <c r="Q12" s="23">
         <f>$K12*N12</f>
         <v/>
       </c>
@@ -25044,39 +25191,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A13,'점검'!$B$14:$B$14,$B13)</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="17">
         <f>IF(C13-G13&gt;0,(D13-H13)/(C13-G13),IF(E13&gt;0,F13/E13,0))</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="17">
         <f>IF(E13&gt;0,F13/E13,I13)</f>
         <v/>
       </c>
-      <c r="K13" s="22">
+      <c r="K13" s="23">
         <f>SUMIFS('가정'!$D$16:$D$27,'가정'!$A$16:$A$27,$A13,'가정'!$B$16:$B$27,$B13)</f>
         <v/>
       </c>
-      <c r="L13" s="16">
+      <c r="L13" s="17">
         <f>($B$6*$J13+('가정'!$B$10-$B$6)*$I13)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="M13" s="16">
+      <c r="M13" s="17">
         <f>($C$6*$J13+('가정'!$B$10-$C$6)*$I13)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="N13" s="16">
+      <c r="N13" s="17">
         <f>($D$6*$J13+('가정'!$B$10-$D$6)*$I13)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="O13" s="22">
+      <c r="O13" s="23">
         <f>$K13*L13</f>
         <v/>
       </c>
-      <c r="P13" s="22">
+      <c r="P13" s="23">
         <f>$K13*M13</f>
         <v/>
       </c>
-      <c r="Q13" s="22">
+      <c r="Q13" s="23">
         <f>$K13*N13</f>
         <v/>
       </c>
@@ -25116,39 +25263,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A14,'점검'!$B$14:$B$14,$B14)</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="17">
         <f>IF(C14-G14&gt;0,(D14-H14)/(C14-G14),IF(E14&gt;0,F14/E14,0))</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="17">
         <f>IF(E14&gt;0,F14/E14,I14)</f>
         <v/>
       </c>
-      <c r="K14" s="22">
+      <c r="K14" s="23">
         <f>'가정'!$B$38*'가정'!$B$10/10000</f>
         <v/>
       </c>
-      <c r="L14" s="16">
+      <c r="L14" s="17">
         <f>($B$6*$J14+('가정'!$B$10-$B$6)*$I14)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="M14" s="16">
+      <c r="M14" s="17">
         <f>($C$6*$J14+('가정'!$B$10-$C$6)*$I14)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="N14" s="16">
+      <c r="N14" s="17">
         <f>($D$6*$J14+('가정'!$B$10-$D$6)*$I14)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="O14" s="22">
+      <c r="O14" s="23">
         <f>$K14*L14</f>
         <v/>
       </c>
-      <c r="P14" s="22">
+      <c r="P14" s="23">
         <f>$K14*M14</f>
         <v/>
       </c>
-      <c r="Q14" s="22">
+      <c r="Q14" s="23">
         <f>$K14*N14</f>
         <v/>
       </c>
@@ -25188,39 +25335,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A15,'점검'!$B$14:$B$14,$B15)</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="17">
         <f>IF(C15-G15&gt;0,(D15-H15)/(C15-G15),IF(E15&gt;0,F15/E15,0))</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="17">
         <f>IF(E15&gt;0,F15/E15,I15)</f>
         <v/>
       </c>
-      <c r="K15" s="22">
+      <c r="K15" s="23">
         <f>SUMIFS('가정'!$D$16:$D$27,'가정'!$A$16:$A$27,$A15,'가정'!$B$16:$B$27,$B15)</f>
         <v/>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="17">
         <f>($B$6*$J15+('가정'!$B$10-$B$6)*$I15)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="M15" s="16">
+      <c r="M15" s="17">
         <f>($C$6*$J15+('가정'!$B$10-$C$6)*$I15)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="N15" s="16">
+      <c r="N15" s="17">
         <f>($D$6*$J15+('가정'!$B$10-$D$6)*$I15)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="O15" s="22">
+      <c r="O15" s="23">
         <f>$K15*L15</f>
         <v/>
       </c>
-      <c r="P15" s="22">
+      <c r="P15" s="23">
         <f>$K15*M15</f>
         <v/>
       </c>
-      <c r="Q15" s="22">
+      <c r="Q15" s="23">
         <f>$K15*N15</f>
         <v/>
       </c>
@@ -25260,39 +25407,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A16,'점검'!$B$14:$B$14,$B16)</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="17">
         <f>IF(C16-G16&gt;0,(D16-H16)/(C16-G16),IF(E16&gt;0,F16/E16,0))</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="17">
         <f>IF(E16&gt;0,F16/E16,I16)</f>
         <v/>
       </c>
-      <c r="K16" s="22">
+      <c r="K16" s="23">
         <f>SUMIFS('가정'!$D$16:$D$27,'가정'!$A$16:$A$27,$A16,'가정'!$B$16:$B$27,$B16)</f>
         <v/>
       </c>
-      <c r="L16" s="16">
+      <c r="L16" s="17">
         <f>($B$6*$J16+('가정'!$B$10-$B$6)*$I16)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="M16" s="16">
+      <c r="M16" s="17">
         <f>($C$6*$J16+('가정'!$B$10-$C$6)*$I16)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="N16" s="16">
+      <c r="N16" s="17">
         <f>($D$6*$J16+('가정'!$B$10-$D$6)*$I16)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="O16" s="22">
+      <c r="O16" s="23">
         <f>$K16*L16</f>
         <v/>
       </c>
-      <c r="P16" s="22">
+      <c r="P16" s="23">
         <f>$K16*M16</f>
         <v/>
       </c>
-      <c r="Q16" s="22">
+      <c r="Q16" s="23">
         <f>$K16*N16</f>
         <v/>
       </c>
@@ -25332,39 +25479,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A17,'점검'!$B$14:$B$14,$B17)</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="17">
         <f>IF(C17-G17&gt;0,(D17-H17)/(C17-G17),IF(E17&gt;0,F17/E17,0))</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="17">
         <f>IF(E17&gt;0,F17/E17,I17)</f>
         <v/>
       </c>
-      <c r="K17" s="22">
+      <c r="K17" s="23">
         <f>SUMIFS('가정'!$D$16:$D$27,'가정'!$A$16:$A$27,$A17,'가정'!$B$16:$B$27,$B17)</f>
         <v/>
       </c>
-      <c r="L17" s="16">
+      <c r="L17" s="17">
         <f>($B$6*$J17+('가정'!$B$10-$B$6)*$I17)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="M17" s="16">
+      <c r="M17" s="17">
         <f>($C$6*$J17+('가정'!$B$10-$C$6)*$I17)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="N17" s="16">
+      <c r="N17" s="17">
         <f>($D$6*$J17+('가정'!$B$10-$D$6)*$I17)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="O17" s="22">
+      <c r="O17" s="23">
         <f>$K17*L17</f>
         <v/>
       </c>
-      <c r="P17" s="22">
+      <c r="P17" s="23">
         <f>$K17*M17</f>
         <v/>
       </c>
-      <c r="Q17" s="22">
+      <c r="Q17" s="23">
         <f>$K17*N17</f>
         <v/>
       </c>
@@ -25404,39 +25551,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A18,'점검'!$B$14:$B$14,$B18)</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="17">
         <f>IF(C18-G18&gt;0,(D18-H18)/(C18-G18),IF(E18&gt;0,F18/E18,0))</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="17">
         <f>IF(E18&gt;0,F18/E18,I18)</f>
         <v/>
       </c>
-      <c r="K18" s="22">
+      <c r="K18" s="23">
         <f>SUMIFS('가정'!$D$16:$D$27,'가정'!$A$16:$A$27,$A18,'가정'!$B$16:$B$27,$B18)</f>
         <v/>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="17">
         <f>($B$6*$J18+('가정'!$B$10-$B$6)*$I18)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="17">
         <f>($C$6*$J18+('가정'!$B$10-$C$6)*$I18)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="N18" s="16">
+      <c r="N18" s="17">
         <f>($D$6*$J18+('가정'!$B$10-$D$6)*$I18)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="O18" s="22">
+      <c r="O18" s="23">
         <f>$K18*L18</f>
         <v/>
       </c>
-      <c r="P18" s="22">
+      <c r="P18" s="23">
         <f>$K18*M18</f>
         <v/>
       </c>
-      <c r="Q18" s="22">
+      <c r="Q18" s="23">
         <f>$K18*N18</f>
         <v/>
       </c>
@@ -25524,39 +25671,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A20,'점검'!$B$14:$B$14,$B20)</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="17">
         <f>IF(C20-G20&gt;0,(D20-H20)/(C20-G20),IF(E20&gt;0,F20/E20,0))</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="17">
         <f>IF(E20&gt;0,F20/E20,I20)</f>
         <v/>
       </c>
-      <c r="K20" s="22">
+      <c r="K20" s="23">
         <f>SUMIFS('가정'!$D$16:$D$27,'가정'!$A$16:$A$27,$A20,'가정'!$B$16:$B$27,$B20)</f>
         <v/>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="17">
         <f>($B$6*$J20+('가정'!$B$10-$B$6)*$I20)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="M20" s="16">
+      <c r="M20" s="17">
         <f>($C$6*$J20+('가정'!$B$10-$C$6)*$I20)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="N20" s="16">
+      <c r="N20" s="17">
         <f>($D$6*$J20+('가정'!$B$10-$D$6)*$I20)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="O20" s="22">
+      <c r="O20" s="23">
         <f>$K20*L20</f>
         <v/>
       </c>
-      <c r="P20" s="22">
+      <c r="P20" s="23">
         <f>$K20*M20</f>
         <v/>
       </c>
-      <c r="Q20" s="22">
+      <c r="Q20" s="23">
         <f>$K20*N20</f>
         <v/>
       </c>
@@ -25596,39 +25743,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A21,'점검'!$B$14:$B$14,$B21)</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="17">
         <f>IF(C21-G21&gt;0,(D21-H21)/(C21-G21),IF(E21&gt;0,F21/E21,0))</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="17">
         <f>IF(E21&gt;0,F21/E21,I21)</f>
         <v/>
       </c>
-      <c r="K21" s="22">
+      <c r="K21" s="23">
         <f>SUMIFS('가정'!$D$16:$D$27,'가정'!$A$16:$A$27,$A21,'가정'!$B$16:$B$27,$B21)</f>
         <v/>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="17">
         <f>($B$6*$J21+('가정'!$B$10-$B$6)*$I21)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="M21" s="16">
+      <c r="M21" s="17">
         <f>($C$6*$J21+('가정'!$B$10-$C$6)*$I21)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="N21" s="16">
+      <c r="N21" s="17">
         <f>($D$6*$J21+('가정'!$B$10-$D$6)*$I21)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="O21" s="22">
+      <c r="O21" s="23">
         <f>$K21*L21</f>
         <v/>
       </c>
-      <c r="P21" s="22">
+      <c r="P21" s="23">
         <f>$K21*M21</f>
         <v/>
       </c>
-      <c r="Q21" s="22">
+      <c r="Q21" s="23">
         <f>$K21*N21</f>
         <v/>
       </c>
@@ -25668,39 +25815,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A22,'점검'!$B$14:$B$14,$B22)</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="17">
         <f>IF(C22-G22&gt;0,(D22-H22)/(C22-G22),IF(E22&gt;0,F22/E22,0))</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="17">
         <f>IF(E22&gt;0,F22/E22,I22)</f>
         <v/>
       </c>
-      <c r="K22" s="22">
+      <c r="K22" s="23">
         <f>'가정'!$B$38*'가정'!$B$10/10000</f>
         <v/>
       </c>
-      <c r="L22" s="16">
+      <c r="L22" s="17">
         <f>($B$6*$J22+('가정'!$B$10-$B$6)*$I22)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="M22" s="16">
+      <c r="M22" s="17">
         <f>($C$6*$J22+('가정'!$B$10-$C$6)*$I22)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="N22" s="16">
+      <c r="N22" s="17">
         <f>($D$6*$J22+('가정'!$B$10-$D$6)*$I22)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="O22" s="22">
+      <c r="O22" s="23">
         <f>$K22*L22</f>
         <v/>
       </c>
-      <c r="P22" s="22">
+      <c r="P22" s="23">
         <f>$K22*M22</f>
         <v/>
       </c>
-      <c r="Q22" s="22">
+      <c r="Q22" s="23">
         <f>$K22*N22</f>
         <v/>
       </c>
@@ -25740,39 +25887,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A23,'점검'!$B$14:$B$14,$B23)</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="17">
         <f>IF(C23-G23&gt;0,(D23-H23)/(C23-G23),IF(E23&gt;0,F23/E23,0))</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="17">
         <f>IF(E23&gt;0,F23/E23,I23)</f>
         <v/>
       </c>
-      <c r="K23" s="22">
+      <c r="K23" s="23">
         <f>SUMIFS('가정'!$D$16:$D$27,'가정'!$A$16:$A$27,$A23,'가정'!$B$16:$B$27,$B23)</f>
         <v/>
       </c>
-      <c r="L23" s="16">
+      <c r="L23" s="17">
         <f>($B$6*$J23+('가정'!$B$10-$B$6)*$I23)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="M23" s="16">
+      <c r="M23" s="17">
         <f>($C$6*$J23+('가정'!$B$10-$C$6)*$I23)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="N23" s="16">
+      <c r="N23" s="17">
         <f>($D$6*$J23+('가정'!$B$10-$D$6)*$I23)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="O23" s="22">
+      <c r="O23" s="23">
         <f>$K23*L23</f>
         <v/>
       </c>
-      <c r="P23" s="22">
+      <c r="P23" s="23">
         <f>$K23*M23</f>
         <v/>
       </c>
-      <c r="Q23" s="22">
+      <c r="Q23" s="23">
         <f>$K23*N23</f>
         <v/>
       </c>
@@ -25812,39 +25959,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A24,'점검'!$B$14:$B$14,$B24)</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="17">
         <f>IF(C24-G24&gt;0,(D24-H24)/(C24-G24),IF(E24&gt;0,F24/E24,0))</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="17">
         <f>IF(E24&gt;0,F24/E24,I24)</f>
         <v/>
       </c>
-      <c r="K24" s="22">
+      <c r="K24" s="23">
         <f>SUMIFS('가정'!$D$16:$D$27,'가정'!$A$16:$A$27,$A24,'가정'!$B$16:$B$27,$B24)</f>
         <v/>
       </c>
-      <c r="L24" s="16">
+      <c r="L24" s="17">
         <f>($B$6*$J24+('가정'!$B$10-$B$6)*$I24)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="M24" s="16">
+      <c r="M24" s="17">
         <f>($C$6*$J24+('가정'!$B$10-$C$6)*$I24)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="N24" s="16">
+      <c r="N24" s="17">
         <f>($D$6*$J24+('가정'!$B$10-$D$6)*$I24)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="O24" s="22">
+      <c r="O24" s="23">
         <f>$K24*L24</f>
         <v/>
       </c>
-      <c r="P24" s="22">
+      <c r="P24" s="23">
         <f>$K24*M24</f>
         <v/>
       </c>
-      <c r="Q24" s="22">
+      <c r="Q24" s="23">
         <f>$K24*N24</f>
         <v/>
       </c>
@@ -25884,39 +26031,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A25,'점검'!$B$14:$B$14,$B25)</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="17">
         <f>IF(C25-G25&gt;0,(D25-H25)/(C25-G25),IF(E25&gt;0,F25/E25,0))</f>
         <v/>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="17">
         <f>IF(E25&gt;0,F25/E25,I25)</f>
         <v/>
       </c>
-      <c r="K25" s="22">
+      <c r="K25" s="23">
         <f>SUMIFS('가정'!$D$16:$D$27,'가정'!$A$16:$A$27,$A25,'가정'!$B$16:$B$27,$B25)</f>
         <v/>
       </c>
-      <c r="L25" s="16">
+      <c r="L25" s="17">
         <f>($B$6*$J25+('가정'!$B$10-$B$6)*$I25)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="M25" s="16">
+      <c r="M25" s="17">
         <f>($C$6*$J25+('가정'!$B$10-$C$6)*$I25)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="N25" s="16">
+      <c r="N25" s="17">
         <f>($D$6*$J25+('가정'!$B$10-$D$6)*$I25)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="O25" s="22">
+      <c r="O25" s="23">
         <f>$K25*L25</f>
         <v/>
       </c>
-      <c r="P25" s="22">
+      <c r="P25" s="23">
         <f>$K25*M25</f>
         <v/>
       </c>
-      <c r="Q25" s="22">
+      <c r="Q25" s="23">
         <f>$K25*N25</f>
         <v/>
       </c>
@@ -25956,39 +26103,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A26,'점검'!$B$14:$B$14,$B26)</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="17">
         <f>IF(C26-G26&gt;0,(D26-H26)/(C26-G26),IF(E26&gt;0,F26/E26,0))</f>
         <v/>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="17">
         <f>IF(E26&gt;0,F26/E26,I26)</f>
         <v/>
       </c>
-      <c r="K26" s="22">
+      <c r="K26" s="23">
         <f>SUMIFS('가정'!$D$16:$D$27,'가정'!$A$16:$A$27,$A26,'가정'!$B$16:$B$27,$B26)</f>
         <v/>
       </c>
-      <c r="L26" s="16">
+      <c r="L26" s="17">
         <f>($B$6*$J26+('가정'!$B$10-$B$6)*$I26)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="M26" s="16">
+      <c r="M26" s="17">
         <f>($C$6*$J26+('가정'!$B$10-$C$6)*$I26)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="N26" s="16">
+      <c r="N26" s="17">
         <f>($D$6*$J26+('가정'!$B$10-$D$6)*$I26)/'가정'!$B$10</f>
         <v/>
       </c>
-      <c r="O26" s="22">
+      <c r="O26" s="23">
         <f>$K26*L26</f>
         <v/>
       </c>
-      <c r="P26" s="22">
+      <c r="P26" s="23">
         <f>$K26*M26</f>
         <v/>
       </c>
-      <c r="Q26" s="22">
+      <c r="Q26" s="23">
         <f>$K26*N26</f>
         <v/>
       </c>
@@ -26078,7 +26225,7 @@
         <f>'가정'!B42</f>
         <v/>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>하한</t>
         </is>
@@ -26099,7 +26246,7 @@
         <f>IF(SUMPRODUCT(K12:K18,J12:J18-I12:I18)=0,0,($B30*K19-SUMPRODUCT(K12:K18,I12:I18))*'가정'!$B$10/SUMPRODUCT(K12:K18,J12:J18-I12:I18))</f>
         <v/>
       </c>
-      <c r="P30" s="21" t="inlineStr">
+      <c r="P30" s="22" t="inlineStr">
         <is>
           <t>← 하한 달성에 필요한 행사일수(현재 예산 기준)</t>
         </is>
@@ -26115,7 +26262,7 @@
         <f>'가정'!C42</f>
         <v/>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>하한</t>
         </is>
@@ -26136,7 +26283,7 @@
         <f>IF(SUMPRODUCT(K20:K26,J20:J26-I20:I26)=0,0,($B31*K27-SUMPRODUCT(K20:K26,I20:I26))*'가정'!$B$10/SUMPRODUCT(K20:K26,J20:J26-I20:I26))</f>
         <v/>
       </c>
-      <c r="P31" s="21" t="inlineStr">
+      <c r="P31" s="22" t="inlineStr">
         <is>
           <t>← 하한 달성에 필요한 행사일수(현재 예산 기준)</t>
         </is>
@@ -26271,39 +26418,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A36,'점검'!$B$14:$B$14,$B36)</f>
         <v/>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="17">
         <f>IF(C36-G36&gt;0,(D36-H36)/(C36-G36),IF(E36&gt;0,F36/E36,0))</f>
         <v/>
       </c>
-      <c r="J36" s="16">
+      <c r="J36" s="17">
         <f>IF(E36&gt;0,F36/E36,I36)</f>
         <v/>
       </c>
-      <c r="K36" s="22">
+      <c r="K36" s="23">
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A36,'가정'!$B$16:$B$27,$B36)</f>
         <v/>
       </c>
-      <c r="L36" s="16">
+      <c r="L36" s="17">
         <f>($B$7*$J36+('가정'!$B$11-$B$7)*$I36)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="M36" s="16">
+      <c r="M36" s="17">
         <f>($C$7*$J36+('가정'!$B$11-$C$7)*$I36)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="N36" s="16">
+      <c r="N36" s="17">
         <f>($D$7*$J36+('가정'!$B$11-$D$7)*$I36)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="O36" s="22">
+      <c r="O36" s="23">
         <f>$K36*L36</f>
         <v/>
       </c>
-      <c r="P36" s="22">
+      <c r="P36" s="23">
         <f>$K36*M36</f>
         <v/>
       </c>
-      <c r="Q36" s="22">
+      <c r="Q36" s="23">
         <f>$K36*N36</f>
         <v/>
       </c>
@@ -26343,39 +26490,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A37,'점검'!$B$14:$B$14,$B37)</f>
         <v/>
       </c>
-      <c r="I37" s="16">
+      <c r="I37" s="17">
         <f>IF(C37-G37&gt;0,(D37-H37)/(C37-G37),IF(E37&gt;0,F37/E37,0))</f>
         <v/>
       </c>
-      <c r="J37" s="16">
+      <c r="J37" s="17">
         <f>IF(E37&gt;0,F37/E37,I37)</f>
         <v/>
       </c>
-      <c r="K37" s="22">
+      <c r="K37" s="23">
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A37,'가정'!$B$16:$B$27,$B37)</f>
         <v/>
       </c>
-      <c r="L37" s="16">
+      <c r="L37" s="17">
         <f>($B$7*$J37+('가정'!$B$11-$B$7)*$I37)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="M37" s="16">
+      <c r="M37" s="17">
         <f>($C$7*$J37+('가정'!$B$11-$C$7)*$I37)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="N37" s="16">
+      <c r="N37" s="17">
         <f>($D$7*$J37+('가정'!$B$11-$D$7)*$I37)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="O37" s="22">
+      <c r="O37" s="23">
         <f>$K37*L37</f>
         <v/>
       </c>
-      <c r="P37" s="22">
+      <c r="P37" s="23">
         <f>$K37*M37</f>
         <v/>
       </c>
-      <c r="Q37" s="22">
+      <c r="Q37" s="23">
         <f>$K37*N37</f>
         <v/>
       </c>
@@ -26415,39 +26562,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A38,'점검'!$B$14:$B$14,$B38)</f>
         <v/>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="17">
         <f>IF(C38-G38&gt;0,(D38-H38)/(C38-G38),IF(E38&gt;0,F38/E38,0))</f>
         <v/>
       </c>
-      <c r="J38" s="16">
+      <c r="J38" s="17">
         <f>IF(E38&gt;0,F38/E38,I38)</f>
         <v/>
       </c>
-      <c r="K38" s="22">
+      <c r="K38" s="23">
         <f>'가정'!$B$38*'가정'!$B$11/10000</f>
         <v/>
       </c>
-      <c r="L38" s="16">
+      <c r="L38" s="17">
         <f>($B$7*$J38+('가정'!$B$11-$B$7)*$I38)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="M38" s="16">
+      <c r="M38" s="17">
         <f>($C$7*$J38+('가정'!$B$11-$C$7)*$I38)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="N38" s="16">
+      <c r="N38" s="17">
         <f>($D$7*$J38+('가정'!$B$11-$D$7)*$I38)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="O38" s="22">
+      <c r="O38" s="23">
         <f>$K38*L38</f>
         <v/>
       </c>
-      <c r="P38" s="22">
+      <c r="P38" s="23">
         <f>$K38*M38</f>
         <v/>
       </c>
-      <c r="Q38" s="22">
+      <c r="Q38" s="23">
         <f>$K38*N38</f>
         <v/>
       </c>
@@ -26487,39 +26634,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A39,'점검'!$B$14:$B$14,$B39)</f>
         <v/>
       </c>
-      <c r="I39" s="16">
+      <c r="I39" s="17">
         <f>IF(C39-G39&gt;0,(D39-H39)/(C39-G39),IF(E39&gt;0,F39/E39,0))</f>
         <v/>
       </c>
-      <c r="J39" s="16">
+      <c r="J39" s="17">
         <f>IF(E39&gt;0,F39/E39,I39)</f>
         <v/>
       </c>
-      <c r="K39" s="22">
+      <c r="K39" s="23">
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A39,'가정'!$B$16:$B$27,$B39)</f>
         <v/>
       </c>
-      <c r="L39" s="16">
+      <c r="L39" s="17">
         <f>($B$7*$J39+('가정'!$B$11-$B$7)*$I39)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="M39" s="16">
+      <c r="M39" s="17">
         <f>($C$7*$J39+('가정'!$B$11-$C$7)*$I39)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="N39" s="16">
+      <c r="N39" s="17">
         <f>($D$7*$J39+('가정'!$B$11-$D$7)*$I39)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="O39" s="22">
+      <c r="O39" s="23">
         <f>$K39*L39</f>
         <v/>
       </c>
-      <c r="P39" s="22">
+      <c r="P39" s="23">
         <f>$K39*M39</f>
         <v/>
       </c>
-      <c r="Q39" s="22">
+      <c r="Q39" s="23">
         <f>$K39*N39</f>
         <v/>
       </c>
@@ -26559,39 +26706,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A40,'점검'!$B$14:$B$14,$B40)</f>
         <v/>
       </c>
-      <c r="I40" s="16">
+      <c r="I40" s="17">
         <f>IF(C40-G40&gt;0,(D40-H40)/(C40-G40),IF(E40&gt;0,F40/E40,0))</f>
         <v/>
       </c>
-      <c r="J40" s="16">
+      <c r="J40" s="17">
         <f>IF(E40&gt;0,F40/E40,I40)</f>
         <v/>
       </c>
-      <c r="K40" s="22">
+      <c r="K40" s="23">
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A40,'가정'!$B$16:$B$27,$B40)</f>
         <v/>
       </c>
-      <c r="L40" s="16">
+      <c r="L40" s="17">
         <f>($B$7*$J40+('가정'!$B$11-$B$7)*$I40)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="M40" s="16">
+      <c r="M40" s="17">
         <f>($C$7*$J40+('가정'!$B$11-$C$7)*$I40)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="N40" s="16">
+      <c r="N40" s="17">
         <f>($D$7*$J40+('가정'!$B$11-$D$7)*$I40)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="O40" s="22">
+      <c r="O40" s="23">
         <f>$K40*L40</f>
         <v/>
       </c>
-      <c r="P40" s="22">
+      <c r="P40" s="23">
         <f>$K40*M40</f>
         <v/>
       </c>
-      <c r="Q40" s="22">
+      <c r="Q40" s="23">
         <f>$K40*N40</f>
         <v/>
       </c>
@@ -26631,39 +26778,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A41,'점검'!$B$14:$B$14,$B41)</f>
         <v/>
       </c>
-      <c r="I41" s="16">
+      <c r="I41" s="17">
         <f>IF(C41-G41&gt;0,(D41-H41)/(C41-G41),IF(E41&gt;0,F41/E41,0))</f>
         <v/>
       </c>
-      <c r="J41" s="16">
+      <c r="J41" s="17">
         <f>IF(E41&gt;0,F41/E41,I41)</f>
         <v/>
       </c>
-      <c r="K41" s="22">
+      <c r="K41" s="23">
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A41,'가정'!$B$16:$B$27,$B41)</f>
         <v/>
       </c>
-      <c r="L41" s="16">
+      <c r="L41" s="17">
         <f>($B$7*$J41+('가정'!$B$11-$B$7)*$I41)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="M41" s="16">
+      <c r="M41" s="17">
         <f>($C$7*$J41+('가정'!$B$11-$C$7)*$I41)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="N41" s="16">
+      <c r="N41" s="17">
         <f>($D$7*$J41+('가정'!$B$11-$D$7)*$I41)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="O41" s="22">
+      <c r="O41" s="23">
         <f>$K41*L41</f>
         <v/>
       </c>
-      <c r="P41" s="22">
+      <c r="P41" s="23">
         <f>$K41*M41</f>
         <v/>
       </c>
-      <c r="Q41" s="22">
+      <c r="Q41" s="23">
         <f>$K41*N41</f>
         <v/>
       </c>
@@ -26703,39 +26850,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A42,'점검'!$B$14:$B$14,$B42)</f>
         <v/>
       </c>
-      <c r="I42" s="16">
+      <c r="I42" s="17">
         <f>IF(C42-G42&gt;0,(D42-H42)/(C42-G42),IF(E42&gt;0,F42/E42,0))</f>
         <v/>
       </c>
-      <c r="J42" s="16">
+      <c r="J42" s="17">
         <f>IF(E42&gt;0,F42/E42,I42)</f>
         <v/>
       </c>
-      <c r="K42" s="22">
+      <c r="K42" s="23">
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A42,'가정'!$B$16:$B$27,$B42)</f>
         <v/>
       </c>
-      <c r="L42" s="16">
+      <c r="L42" s="17">
         <f>($B$7*$J42+('가정'!$B$11-$B$7)*$I42)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="M42" s="16">
+      <c r="M42" s="17">
         <f>($C$7*$J42+('가정'!$B$11-$C$7)*$I42)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="N42" s="16">
+      <c r="N42" s="17">
         <f>($D$7*$J42+('가정'!$B$11-$D$7)*$I42)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="O42" s="22">
+      <c r="O42" s="23">
         <f>$K42*L42</f>
         <v/>
       </c>
-      <c r="P42" s="22">
+      <c r="P42" s="23">
         <f>$K42*M42</f>
         <v/>
       </c>
-      <c r="Q42" s="22">
+      <c r="Q42" s="23">
         <f>$K42*N42</f>
         <v/>
       </c>
@@ -26823,39 +26970,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A44,'점검'!$B$14:$B$14,$B44)</f>
         <v/>
       </c>
-      <c r="I44" s="16">
+      <c r="I44" s="17">
         <f>IF(C44-G44&gt;0,(D44-H44)/(C44-G44),IF(E44&gt;0,F44/E44,0))</f>
         <v/>
       </c>
-      <c r="J44" s="16">
+      <c r="J44" s="17">
         <f>IF(E44&gt;0,F44/E44,I44)</f>
         <v/>
       </c>
-      <c r="K44" s="22">
+      <c r="K44" s="23">
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A44,'가정'!$B$16:$B$27,$B44)</f>
         <v/>
       </c>
-      <c r="L44" s="16">
+      <c r="L44" s="17">
         <f>($B$7*$J44+('가정'!$B$11-$B$7)*$I44)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="M44" s="16">
+      <c r="M44" s="17">
         <f>($C$7*$J44+('가정'!$B$11-$C$7)*$I44)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="N44" s="16">
+      <c r="N44" s="17">
         <f>($D$7*$J44+('가정'!$B$11-$D$7)*$I44)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="O44" s="22">
+      <c r="O44" s="23">
         <f>$K44*L44</f>
         <v/>
       </c>
-      <c r="P44" s="22">
+      <c r="P44" s="23">
         <f>$K44*M44</f>
         <v/>
       </c>
-      <c r="Q44" s="22">
+      <c r="Q44" s="23">
         <f>$K44*N44</f>
         <v/>
       </c>
@@ -26895,39 +27042,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A45,'점검'!$B$14:$B$14,$B45)</f>
         <v/>
       </c>
-      <c r="I45" s="16">
+      <c r="I45" s="17">
         <f>IF(C45-G45&gt;0,(D45-H45)/(C45-G45),IF(E45&gt;0,F45/E45,0))</f>
         <v/>
       </c>
-      <c r="J45" s="16">
+      <c r="J45" s="17">
         <f>IF(E45&gt;0,F45/E45,I45)</f>
         <v/>
       </c>
-      <c r="K45" s="22">
+      <c r="K45" s="23">
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A45,'가정'!$B$16:$B$27,$B45)</f>
         <v/>
       </c>
-      <c r="L45" s="16">
+      <c r="L45" s="17">
         <f>($B$7*$J45+('가정'!$B$11-$B$7)*$I45)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="M45" s="16">
+      <c r="M45" s="17">
         <f>($C$7*$J45+('가정'!$B$11-$C$7)*$I45)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="N45" s="16">
+      <c r="N45" s="17">
         <f>($D$7*$J45+('가정'!$B$11-$D$7)*$I45)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="O45" s="22">
+      <c r="O45" s="23">
         <f>$K45*L45</f>
         <v/>
       </c>
-      <c r="P45" s="22">
+      <c r="P45" s="23">
         <f>$K45*M45</f>
         <v/>
       </c>
-      <c r="Q45" s="22">
+      <c r="Q45" s="23">
         <f>$K45*N45</f>
         <v/>
       </c>
@@ -26967,39 +27114,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A46,'점검'!$B$14:$B$14,$B46)</f>
         <v/>
       </c>
-      <c r="I46" s="16">
+      <c r="I46" s="17">
         <f>IF(C46-G46&gt;0,(D46-H46)/(C46-G46),IF(E46&gt;0,F46/E46,0))</f>
         <v/>
       </c>
-      <c r="J46" s="16">
+      <c r="J46" s="17">
         <f>IF(E46&gt;0,F46/E46,I46)</f>
         <v/>
       </c>
-      <c r="K46" s="22">
+      <c r="K46" s="23">
         <f>'가정'!$B$38*'가정'!$B$11/10000</f>
         <v/>
       </c>
-      <c r="L46" s="16">
+      <c r="L46" s="17">
         <f>($B$7*$J46+('가정'!$B$11-$B$7)*$I46)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="M46" s="16">
+      <c r="M46" s="17">
         <f>($C$7*$J46+('가정'!$B$11-$C$7)*$I46)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="N46" s="16">
+      <c r="N46" s="17">
         <f>($D$7*$J46+('가정'!$B$11-$D$7)*$I46)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="O46" s="22">
+      <c r="O46" s="23">
         <f>$K46*L46</f>
         <v/>
       </c>
-      <c r="P46" s="22">
+      <c r="P46" s="23">
         <f>$K46*M46</f>
         <v/>
       </c>
-      <c r="Q46" s="22">
+      <c r="Q46" s="23">
         <f>$K46*N46</f>
         <v/>
       </c>
@@ -27039,39 +27186,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A47,'점검'!$B$14:$B$14,$B47)</f>
         <v/>
       </c>
-      <c r="I47" s="16">
+      <c r="I47" s="17">
         <f>IF(C47-G47&gt;0,(D47-H47)/(C47-G47),IF(E47&gt;0,F47/E47,0))</f>
         <v/>
       </c>
-      <c r="J47" s="16">
+      <c r="J47" s="17">
         <f>IF(E47&gt;0,F47/E47,I47)</f>
         <v/>
       </c>
-      <c r="K47" s="22">
+      <c r="K47" s="23">
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A47,'가정'!$B$16:$B$27,$B47)</f>
         <v/>
       </c>
-      <c r="L47" s="16">
+      <c r="L47" s="17">
         <f>($B$7*$J47+('가정'!$B$11-$B$7)*$I47)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="M47" s="16">
+      <c r="M47" s="17">
         <f>($C$7*$J47+('가정'!$B$11-$C$7)*$I47)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="N47" s="16">
+      <c r="N47" s="17">
         <f>($D$7*$J47+('가정'!$B$11-$D$7)*$I47)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="O47" s="22">
+      <c r="O47" s="23">
         <f>$K47*L47</f>
         <v/>
       </c>
-      <c r="P47" s="22">
+      <c r="P47" s="23">
         <f>$K47*M47</f>
         <v/>
       </c>
-      <c r="Q47" s="22">
+      <c r="Q47" s="23">
         <f>$K47*N47</f>
         <v/>
       </c>
@@ -27111,39 +27258,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A48,'점검'!$B$14:$B$14,$B48)</f>
         <v/>
       </c>
-      <c r="I48" s="16">
+      <c r="I48" s="17">
         <f>IF(C48-G48&gt;0,(D48-H48)/(C48-G48),IF(E48&gt;0,F48/E48,0))</f>
         <v/>
       </c>
-      <c r="J48" s="16">
+      <c r="J48" s="17">
         <f>IF(E48&gt;0,F48/E48,I48)</f>
         <v/>
       </c>
-      <c r="K48" s="22">
+      <c r="K48" s="23">
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A48,'가정'!$B$16:$B$27,$B48)</f>
         <v/>
       </c>
-      <c r="L48" s="16">
+      <c r="L48" s="17">
         <f>($B$7*$J48+('가정'!$B$11-$B$7)*$I48)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="M48" s="16">
+      <c r="M48" s="17">
         <f>($C$7*$J48+('가정'!$B$11-$C$7)*$I48)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="N48" s="16">
+      <c r="N48" s="17">
         <f>($D$7*$J48+('가정'!$B$11-$D$7)*$I48)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="O48" s="22">
+      <c r="O48" s="23">
         <f>$K48*L48</f>
         <v/>
       </c>
-      <c r="P48" s="22">
+      <c r="P48" s="23">
         <f>$K48*M48</f>
         <v/>
       </c>
-      <c r="Q48" s="22">
+      <c r="Q48" s="23">
         <f>$K48*N48</f>
         <v/>
       </c>
@@ -27183,39 +27330,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A49,'점검'!$B$14:$B$14,$B49)</f>
         <v/>
       </c>
-      <c r="I49" s="16">
+      <c r="I49" s="17">
         <f>IF(C49-G49&gt;0,(D49-H49)/(C49-G49),IF(E49&gt;0,F49/E49,0))</f>
         <v/>
       </c>
-      <c r="J49" s="16">
+      <c r="J49" s="17">
         <f>IF(E49&gt;0,F49/E49,I49)</f>
         <v/>
       </c>
-      <c r="K49" s="22">
+      <c r="K49" s="23">
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A49,'가정'!$B$16:$B$27,$B49)</f>
         <v/>
       </c>
-      <c r="L49" s="16">
+      <c r="L49" s="17">
         <f>($B$7*$J49+('가정'!$B$11-$B$7)*$I49)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="M49" s="16">
+      <c r="M49" s="17">
         <f>($C$7*$J49+('가정'!$B$11-$C$7)*$I49)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="N49" s="16">
+      <c r="N49" s="17">
         <f>($D$7*$J49+('가정'!$B$11-$D$7)*$I49)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="O49" s="22">
+      <c r="O49" s="23">
         <f>$K49*L49</f>
         <v/>
       </c>
-      <c r="P49" s="22">
+      <c r="P49" s="23">
         <f>$K49*M49</f>
         <v/>
       </c>
-      <c r="Q49" s="22">
+      <c r="Q49" s="23">
         <f>$K49*N49</f>
         <v/>
       </c>
@@ -27255,39 +27402,39 @@
         <f>$B$8*SUMIFS('점검'!$E$14:$E$14,'점검'!$A$14:$A$14,$A50,'점검'!$B$14:$B$14,$B50)</f>
         <v/>
       </c>
-      <c r="I50" s="16">
+      <c r="I50" s="17">
         <f>IF(C50-G50&gt;0,(D50-H50)/(C50-G50),IF(E50&gt;0,F50/E50,0))</f>
         <v/>
       </c>
-      <c r="J50" s="16">
+      <c r="J50" s="17">
         <f>IF(E50&gt;0,F50/E50,I50)</f>
         <v/>
       </c>
-      <c r="K50" s="22">
+      <c r="K50" s="23">
         <f>SUMIFS('가정'!$E$16:$E$27,'가정'!$A$16:$A$27,$A50,'가정'!$B$16:$B$27,$B50)</f>
         <v/>
       </c>
-      <c r="L50" s="16">
+      <c r="L50" s="17">
         <f>($B$7*$J50+('가정'!$B$11-$B$7)*$I50)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="M50" s="16">
+      <c r="M50" s="17">
         <f>($C$7*$J50+('가정'!$B$11-$C$7)*$I50)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="N50" s="16">
+      <c r="N50" s="17">
         <f>($D$7*$J50+('가정'!$B$11-$D$7)*$I50)/'가정'!$B$11</f>
         <v/>
       </c>
-      <c r="O50" s="22">
+      <c r="O50" s="23">
         <f>$K50*L50</f>
         <v/>
       </c>
-      <c r="P50" s="22">
+      <c r="P50" s="23">
         <f>$K50*M50</f>
         <v/>
       </c>
-      <c r="Q50" s="22">
+      <c r="Q50" s="23">
         <f>$K50*N50</f>
         <v/>
       </c>
@@ -27377,7 +27524,7 @@
         <f>'가정'!B42</f>
         <v/>
       </c>
-      <c r="C54" s="21" t="inlineStr">
+      <c r="C54" s="22" t="inlineStr">
         <is>
           <t>하한</t>
         </is>
@@ -27398,7 +27545,7 @@
         <f>IF(SUMPRODUCT(K36:K42,J36:J42-I36:I42)=0,0,($B54*K43-SUMPRODUCT(K36:K42,I36:I42))*'가정'!$B$11/SUMPRODUCT(K36:K42,J36:J42-I36:I42))</f>
         <v/>
       </c>
-      <c r="P54" s="21" t="inlineStr">
+      <c r="P54" s="22" t="inlineStr">
         <is>
           <t>← 하한 달성에 필요한 행사일수(현재 예산 기준)</t>
         </is>
@@ -27414,7 +27561,7 @@
         <f>'가정'!C42</f>
         <v/>
       </c>
-      <c r="C55" s="21" t="inlineStr">
+      <c r="C55" s="22" t="inlineStr">
         <is>
           <t>하한</t>
         </is>
@@ -27435,7 +27582,7 @@
         <f>IF(SUMPRODUCT(K44:K50,J44:J50-I44:I50)=0,0,($B55*K51-SUMPRODUCT(K44:K50,I44:I50))*'가정'!$B$11/SUMPRODUCT(K44:K50,J44:J50-I44:I50))</f>
         <v/>
       </c>
-      <c r="P55" s="21" t="inlineStr">
+      <c r="P55" s="22" t="inlineStr">
         <is>
           <t>← 하한 달성에 필요한 행사일수(현재 예산 기준)</t>
         </is>
@@ -27516,7 +27663,7 @@
           <t>11월</t>
         </is>
       </c>
-      <c r="C60" s="22">
+      <c r="C60" s="23">
         <f>K19-K18</f>
         <v/>
       </c>
@@ -27564,7 +27711,7 @@
           <t>12월</t>
         </is>
       </c>
-      <c r="C61" s="22">
+      <c r="C61" s="23">
         <f>K43-K42</f>
         <v/>
       </c>
@@ -27612,7 +27759,7 @@
           <t>11월</t>
         </is>
       </c>
-      <c r="C62" s="22">
+      <c r="C62" s="23">
         <f>K27-K26</f>
         <v/>
       </c>
@@ -27660,7 +27807,7 @@
           <t>12월</t>
         </is>
       </c>
-      <c r="C63" s="22">
+      <c r="C63" s="23">
         <f>K51-K50</f>
         <v/>
       </c>
@@ -27698,21 +27845,21 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="21" t="inlineStr">
+      <c r="A64" s="22" t="inlineStr">
         <is>
           <t>통합 ROAS = 스마트스토어 일반상품 순매출 ÷ 스스향 광고비(메타 자사몰 제외). 로지오가닉은 상시 구간에 이상치 이틀이 그대로 포함되어 목표 순매출이 다소 높게 산출될 가능성.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="21" t="inlineStr">
+      <c r="A65" s="22" t="inlineStr">
         <is>
           <t>목표 매출·순매출은 예산 100% 사용 가정 값. 10월 예산 소진율은 아넬라 약 84%, 로지오가닉 약 80%(10월_실적 시트).</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="21" t="inlineStr">
+      <c r="A66" s="22" t="inlineStr">
         <is>
           <t>아넬라 GFA 전환의 행사 ROAS는 귀속 지연·뷰스루 영향으로 높게 산출되었을 가능성(점검 시트 4번). 해당 매체 목표 매출은 보수적 접근 권장.</t>
         </is>
